--- a/research/traditional_assets/database/data/switzerland/switzerland_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1605311288906078</v>
       </c>
       <c r="X2">
-        <v>0.07911422685773076</v>
+        <v>0.07909280877184684</v>
       </c>
       <c r="Y2">
-        <v>0.08141690203287702</v>
+        <v>0.08143832011876094</v>
       </c>
       <c r="Z2">
         <v>0.8493934806479071</v>
@@ -662,10 +662,10 @@
         <v>0.1421632632710825</v>
       </c>
       <c r="AB2">
-        <v>0.06792687128766886</v>
+        <v>0.06791277137250951</v>
       </c>
       <c r="AC2">
-        <v>0.07423639198341364</v>
+        <v>0.074250491898573</v>
       </c>
       <c r="AD2">
         <v>14968.5</v>
@@ -787,10 +787,10 @@
         <v>0.1605311288906078</v>
       </c>
       <c r="X3">
-        <v>0.07911422685773076</v>
+        <v>0.07909280877184684</v>
       </c>
       <c r="Y3">
-        <v>0.08141690203287702</v>
+        <v>0.08143832011876094</v>
       </c>
       <c r="Z3">
         <v>0.8493934806479071</v>
@@ -799,10 +799,10 @@
         <v>0.1421632632710825</v>
       </c>
       <c r="AB3">
-        <v>0.06792687128766886</v>
+        <v>0.06791277137250951</v>
       </c>
       <c r="AC3">
-        <v>0.07423639198341364</v>
+        <v>0.074250491898573</v>
       </c>
       <c r="AD3">
         <v>14968.5</v>
@@ -1139,49 +1139,49 @@
         <v>8.668156979632389</v>
       </c>
       <c r="F2">
-        <v>6.85784293778462</v>
+        <v>8.79839889168391</v>
       </c>
       <c r="G2">
         <v>3.29789812285185</v>
       </c>
       <c r="H2">
-        <v>1.06171521106901</v>
+        <v>0.868676081783731</v>
       </c>
       <c r="I2">
         <v>0.341681827416266</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K2">
         <v>28839.8</v>
       </c>
       <c r="L2">
-        <v>38455.348291707</v>
+        <v>39447.2556795076</v>
       </c>
       <c r="M2">
         <v>39958.5</v>
       </c>
       <c r="N2">
-        <v>39424.461291707</v>
+        <v>39540.2026795076</v>
       </c>
       <c r="O2">
         <v>14968.5</v>
       </c>
       <c r="P2">
-        <v>4818.913</v>
+        <v>3942.747</v>
       </c>
       <c r="Q2">
-        <v>0.0679268712876689</v>
+        <v>0.06791277137250951</v>
       </c>
       <c r="R2">
-        <v>0.0684341833798809</v>
+        <v>0.0683089661098934</v>
       </c>
       <c r="S2">
         <v>0.0463722</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0429562</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.0791142268577308</v>
+        <v>0.0790928087718468</v>
       </c>
       <c r="X2">
-        <v>0.0713192712133494</v>
+        <v>0.0708163825383443</v>
       </c>
       <c r="Y2">
         <v>0.768887038610781</v>
       </c>
       <c r="Z2">
-        <v>0.588980706487093</v>
+        <v>0.577745555158068</v>
       </c>
       <c r="AA2">
         <v>14968.5</v>
@@ -1236,7 +1236,7 @@
         <v>28839.8</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="C2">
-        <v>42813.70120732699</v>
+        <v>42814.43946562433</v>
       </c>
       <c r="D2">
-        <v>38963.90120732699</v>
+        <v>38964.63946562433</v>
       </c>
       <c r="E2">
         <v>-14968.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06883267916721171</v>
+        <v>0.06880590460589436</v>
       </c>
       <c r="C3">
-        <v>42426.59490523759</v>
+        <v>42439.47912356703</v>
       </c>
       <c r="D3">
-        <v>39014.87790523759</v>
+        <v>39027.76212356702</v>
       </c>
       <c r="E3">
         <v>-14530.417</v>
@@ -1539,37 +1539,37 @@
         <v>1744.9</v>
       </c>
       <c r="M3">
-        <v>22.6488911</v>
+        <v>22.0355749</v>
       </c>
       <c r="N3">
-        <v>1722.2511089</v>
+        <v>1722.8644251</v>
       </c>
       <c r="O3">
-        <v>251.4486618994</v>
+        <v>251.5382060646</v>
       </c>
       <c r="P3">
-        <v>1470.8024470006</v>
+        <v>1471.3262190354</v>
       </c>
       <c r="Q3">
-        <v>4264.7024470006</v>
+        <v>4265.2262190354</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06908198097698152</v>
+        <v>0.06906701273322663</v>
       </c>
       <c r="T3">
         <v>0.5373444049244024</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.04129938617612</v>
+        <v>79.18559002515519</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06878249618847863</v>
+        <v>0.06874378729389423</v>
       </c>
       <c r="C4">
-        <v>42039.62216410576</v>
+        <v>42064.72363058879</v>
       </c>
       <c r="D4">
-        <v>39065.98816410575</v>
+        <v>39091.08963058878</v>
       </c>
       <c r="E4">
         <v>-14092.334</v>
@@ -1621,37 +1621,37 @@
         <v>1744.9</v>
       </c>
       <c r="M4">
-        <v>45.29778220000001</v>
+        <v>44.0711498</v>
       </c>
       <c r="N4">
-        <v>1699.6022178</v>
+        <v>1700.8288502</v>
       </c>
       <c r="O4">
-        <v>248.1419237988</v>
+        <v>248.3210121292</v>
       </c>
       <c r="P4">
-        <v>1451.4602940012</v>
+        <v>1452.5078380708</v>
       </c>
       <c r="Q4">
-        <v>4245.360294001201</v>
+        <v>4246.4078380708</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06928516345763126</v>
+        <v>0.06927006458560636</v>
       </c>
       <c r="T4">
         <v>0.5420338241479529</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.52064969308806</v>
+        <v>39.5927950125776</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06873231320974556</v>
+        <v>0.06868166998189409</v>
       </c>
       <c r="C5">
-        <v>41652.78350952249</v>
+        <v>41690.1739854913</v>
       </c>
       <c r="D5">
-        <v>39117.23250952249</v>
+        <v>39154.6229854913</v>
       </c>
       <c r="E5">
         <v>-13654.251</v>
@@ -1703,37 +1703,37 @@
         <v>1744.9</v>
       </c>
       <c r="M5">
-        <v>67.9466733</v>
+        <v>66.1067247</v>
       </c>
       <c r="N5">
-        <v>1676.9533267</v>
+        <v>1678.7932753</v>
       </c>
       <c r="O5">
-        <v>244.8351856982</v>
+        <v>245.1038181938</v>
       </c>
       <c r="P5">
-        <v>1432.1181410018</v>
+        <v>1433.6894571062</v>
       </c>
       <c r="Q5">
-        <v>4226.0181410018</v>
+        <v>4227.5894571062</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06949253526777892</v>
+        <v>0.06947730307411763</v>
       </c>
       <c r="T5">
         <v>0.5468199324276589</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.68043312872538</v>
+        <v>26.39519667505173</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06868213023101247</v>
+        <v>0.06861955266989397</v>
       </c>
       <c r="C6">
-        <v>41266.07946984018</v>
+        <v>41315.83119358015</v>
       </c>
       <c r="D6">
-        <v>39168.61146984018</v>
+        <v>39218.36319358015</v>
       </c>
       <c r="E6">
         <v>-13216.168</v>
@@ -1785,37 +1785,37 @@
         <v>1744.9</v>
       </c>
       <c r="M6">
-        <v>90.59556440000001</v>
+        <v>88.1422996</v>
       </c>
       <c r="N6">
-        <v>1654.3044356</v>
+        <v>1656.7577004</v>
       </c>
       <c r="O6">
-        <v>241.5284475976</v>
+        <v>241.8866242584</v>
       </c>
       <c r="P6">
-        <v>1412.7759880024</v>
+        <v>1414.8710761416</v>
       </c>
       <c r="Q6">
-        <v>4206.6759880024</v>
+        <v>4208.7710761416</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06970422732397133</v>
+        <v>0.06968885903113956</v>
       </c>
       <c r="T6">
         <v>0.5517057512965257</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.26032484654403</v>
+        <v>19.79639750628879</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06863194725227939</v>
+        <v>0.06855743535789385</v>
       </c>
       <c r="C7">
-        <v>40879.5105761907</v>
+        <v>40941.69626671774</v>
       </c>
       <c r="D7">
-        <v>39220.12557619069</v>
+        <v>39282.31126671774</v>
       </c>
       <c r="E7">
         <v>-12778.085</v>
@@ -1867,37 +1867,37 @@
         <v>1744.9</v>
       </c>
       <c r="M7">
-        <v>113.2444555</v>
+        <v>110.1778745</v>
       </c>
       <c r="N7">
-        <v>1631.6555445</v>
+        <v>1634.7221255</v>
       </c>
       <c r="O7">
-        <v>238.221709497</v>
+        <v>238.669430323</v>
       </c>
       <c r="P7">
-        <v>1393.433835003</v>
+        <v>1396.052695177</v>
       </c>
       <c r="Q7">
-        <v>4187.333835003001</v>
+        <v>4189.952695177</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06992037605503094</v>
+        <v>0.069904868797783</v>
       </c>
       <c r="T7">
         <v>0.5566944295100001</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.40825987723522</v>
+        <v>15.83711800503104</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06858176427354631</v>
+        <v>0.06849531804589373</v>
       </c>
       <c r="C8">
-        <v>40493.07736250379</v>
+        <v>40567.77022337692</v>
       </c>
       <c r="D8">
-        <v>39271.77536250379</v>
+        <v>39346.46822337692</v>
       </c>
       <c r="E8">
         <v>-12340.002</v>
@@ -1949,37 +1949,37 @@
         <v>1744.9</v>
       </c>
       <c r="M8">
-        <v>135.8933466</v>
+        <v>132.2134494</v>
       </c>
       <c r="N8">
-        <v>1609.0066534</v>
+        <v>1612.6865506</v>
       </c>
       <c r="O8">
-        <v>234.9149713964</v>
+        <v>235.4522363876</v>
       </c>
       <c r="P8">
-        <v>1374.0916820036</v>
+        <v>1377.2343142124</v>
       </c>
       <c r="Q8">
-        <v>4167.9916820036</v>
+        <v>4171.134314212401</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07014112369526204</v>
+        <v>0.07012547451690823</v>
       </c>
       <c r="T8">
         <v>0.5617892498131229</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.84021656436269</v>
+        <v>13.19759833752587</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06853158129481324</v>
+        <v>0.06843320073389361</v>
       </c>
       <c r="C9">
-        <v>40106.78036552546</v>
+        <v>40194.054088695</v>
       </c>
       <c r="D9">
-        <v>39323.56136552546</v>
+        <v>39410.83508869499</v>
       </c>
       <c r="E9">
         <v>-11901.919</v>
@@ -2031,37 +2031,37 @@
         <v>1744.9</v>
       </c>
       <c r="M9">
-        <v>158.5422377</v>
+        <v>154.2490243</v>
       </c>
       <c r="N9">
-        <v>1586.3577623</v>
+        <v>1590.6509757</v>
       </c>
       <c r="O9">
-        <v>231.6082332958</v>
+        <v>232.2350424522</v>
       </c>
       <c r="P9">
-        <v>1354.7495290042</v>
+        <v>1358.4159332478</v>
       </c>
       <c r="Q9">
-        <v>4148.6495290042</v>
+        <v>4152.315933247801</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07036661859657338</v>
+        <v>0.07035082444504689</v>
       </c>
       <c r="T9">
         <v>0.5669936361442699</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.00589991231087</v>
+        <v>11.31222714645074</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06848139831608016</v>
+        <v>0.06837108342189348</v>
       </c>
       <c r="C10">
-        <v>39720.62012483661</v>
+        <v>39820.54889452837</v>
       </c>
       <c r="D10">
-        <v>39375.4841248366</v>
+        <v>39475.41289452837</v>
       </c>
       <c r="E10">
         <v>-11463.836</v>
@@ -2113,37 +2113,37 @@
         <v>1744.9</v>
       </c>
       <c r="M10">
-        <v>181.1911288</v>
+        <v>176.2845992</v>
       </c>
       <c r="N10">
-        <v>1563.7088712</v>
+        <v>1568.6154008</v>
       </c>
       <c r="O10">
-        <v>228.3014951952</v>
+        <v>229.0178485168</v>
       </c>
       <c r="P10">
-        <v>1335.4073760048</v>
+        <v>1339.5975522832</v>
       </c>
       <c r="Q10">
-        <v>4129.3073760048</v>
+        <v>4133.4975522832</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0705970155609567</v>
+        <v>0.07058107328466683</v>
       </c>
       <c r="T10">
         <v>0.5723111613087026</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.630162423272015</v>
+        <v>9.898198753144399</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06851576133734708</v>
+        <v>0.06830896610989336</v>
       </c>
       <c r="C11">
-        <v>39246.96799485219</v>
+        <v>39447.25567950761</v>
       </c>
       <c r="D11">
-        <v>39339.91499485219</v>
+        <v>39540.20267950761</v>
       </c>
       <c r="E11">
         <v>-11025.753</v>
@@ -2195,45 +2195,45 @@
         <v>1744.9</v>
       </c>
       <c r="M11">
-        <v>208.1770416</v>
+        <v>198.3201741</v>
       </c>
       <c r="N11">
-        <v>1536.7229584</v>
+        <v>1546.5798259</v>
       </c>
       <c r="O11">
-        <v>224.3615519264</v>
+        <v>225.8006545814</v>
       </c>
       <c r="P11">
-        <v>1312.3614064736</v>
+        <v>1320.7791713186</v>
       </c>
       <c r="Q11">
-        <v>4106.261406473601</v>
+        <v>4114.6791713186</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0708324761948869</v>
+        <v>0.07081638253834434</v>
       </c>
       <c r="T11">
         <v>0.5777455551580679</v>
       </c>
       <c r="U11">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0450912</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.381808035070087</v>
+        <v>8.79839889168391</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06847497235861401</v>
+        <v>0.06837494879789323</v>
       </c>
       <c r="C12">
-        <v>38851.1127669518</v>
+        <v>38940.35823505937</v>
       </c>
       <c r="D12">
-        <v>39382.1427669518</v>
+        <v>39471.38823505937</v>
       </c>
       <c r="E12">
         <v>-10587.67</v>
@@ -2277,37 +2277,37 @@
         <v>1744.9</v>
       </c>
       <c r="M12">
-        <v>231.307824</v>
+        <v>226.926994</v>
       </c>
       <c r="N12">
-        <v>1513.592176</v>
+        <v>1517.973006</v>
       </c>
       <c r="O12">
-        <v>220.984457696</v>
+        <v>221.624058876</v>
       </c>
       <c r="P12">
-        <v>1292.607718304</v>
+        <v>1296.348947124</v>
       </c>
       <c r="Q12">
-        <v>4086.507718304</v>
+        <v>4090.248947124001</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07107316928734889</v>
+        <v>0.07105692088654803</v>
       </c>
       <c r="T12">
         <v>0.5833007133151968</v>
       </c>
       <c r="U12">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.543627231563079</v>
+        <v>7.689257100898273</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06843418337988093</v>
+        <v>0.0683256414858931</v>
       </c>
       <c r="C13">
-        <v>38455.348291707</v>
+        <v>38553.67600500773</v>
       </c>
       <c r="D13">
-        <v>39424.461291707</v>
+        <v>39522.78900500773</v>
       </c>
       <c r="E13">
         <v>-10149.587</v>
@@ -2359,37 +2359,37 @@
         <v>1744.9</v>
       </c>
       <c r="M13">
-        <v>254.4386064</v>
+        <v>249.6196934</v>
       </c>
       <c r="N13">
-        <v>1490.4613936</v>
+        <v>1495.2803066</v>
       </c>
       <c r="O13">
-        <v>217.6073634656</v>
+        <v>218.3109247636</v>
       </c>
       <c r="P13">
-        <v>1272.8540301344</v>
+        <v>1276.9693818364</v>
       </c>
       <c r="Q13">
-        <v>4066.7540301344</v>
+        <v>4070.8693818364</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07131927121334936</v>
+        <v>0.07130286459089112</v>
       </c>
       <c r="T13">
         <v>0.5889807064870929</v>
       </c>
       <c r="U13">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.857842937784617</v>
+        <v>6.99023372808934</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06861885040114785</v>
+        <v>0.06845055017389297</v>
       </c>
       <c r="C14">
-        <v>37826.39613158075</v>
+        <v>37985.64015983387</v>
       </c>
       <c r="D14">
-        <v>39233.59213158074</v>
+        <v>39392.83615983387</v>
       </c>
       <c r="E14">
         <v>-9711.504000000001</v>
@@ -2441,37 +2441,37 @@
         <v>1744.9</v>
       </c>
       <c r="M14">
-        <v>289.13478</v>
+        <v>281.249286</v>
       </c>
       <c r="N14">
-        <v>1455.76522</v>
+        <v>1463.650714</v>
       </c>
       <c r="O14">
-        <v>212.54172212</v>
+        <v>213.693004244</v>
       </c>
       <c r="P14">
-        <v>1243.22349788</v>
+        <v>1249.957709756</v>
       </c>
       <c r="Q14">
-        <v>4037.12349788</v>
+        <v>4043.857709756</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07157096636494073</v>
+        <v>0.07155439792487837</v>
       </c>
       <c r="T14">
         <v>0.5947897904128955</v>
       </c>
       <c r="U14">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.034901785250463</v>
+        <v>6.204104639042534</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06876337942241476</v>
+        <v>0.06841576086189284</v>
       </c>
       <c r="C15">
-        <v>37240.21440941116</v>
+        <v>37583.66541911712</v>
       </c>
       <c r="D15">
-        <v>39085.49340941116</v>
+        <v>39428.94441911711</v>
       </c>
       <c r="E15">
         <v>-9273.420999999998</v>
@@ -2523,45 +2523,45 @@
         <v>1744.9</v>
       </c>
       <c r="M15">
-        <v>321.7719635</v>
+        <v>304.6867265</v>
       </c>
       <c r="N15">
-        <v>1423.1280365</v>
+        <v>1440.2132735</v>
       </c>
       <c r="O15">
-        <v>207.776693329</v>
+        <v>210.271137931</v>
       </c>
       <c r="P15">
-        <v>1215.351343171</v>
+        <v>1229.942135569</v>
       </c>
       <c r="Q15">
-        <v>4009.251343171</v>
+        <v>4023.842135569</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07182844761197099</v>
+        <v>0.07181171363435959</v>
       </c>
       <c r="T15">
         <v>0.6007324164979121</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>5.422784449646434</v>
+        <v>5.726865820654645</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06875418844368168</v>
+        <v>0.06847661954989272</v>
       </c>
       <c r="C16">
-        <v>36811.51609659928</v>
+        <v>37082.45974781476</v>
       </c>
       <c r="D16">
-        <v>39094.87809659928</v>
+        <v>39365.82174781476</v>
       </c>
       <c r="E16">
         <v>-8835.338</v>
@@ -2605,37 +2605,37 @@
         <v>1744.9</v>
       </c>
       <c r="M16">
-        <v>346.5236530000001</v>
+        <v>333.0306966000001</v>
       </c>
       <c r="N16">
-        <v>1398.376347</v>
+        <v>1411.8693034</v>
       </c>
       <c r="O16">
-        <v>204.162946662</v>
+        <v>206.1329182964</v>
       </c>
       <c r="P16">
-        <v>1194.213400338</v>
+        <v>1205.7363851036</v>
       </c>
       <c r="Q16">
-        <v>3988.113400338</v>
+        <v>3999.6363851036</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0720919167949787</v>
+        <v>0.0720750134301078</v>
       </c>
       <c r="T16">
         <v>0.6068132431895569</v>
       </c>
       <c r="U16">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.035442703243116</v>
+        <v>5.239456956413188</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0687449974649486</v>
+        <v>0.06844866223789259</v>
       </c>
       <c r="C17">
-        <v>36382.8222915215</v>
+        <v>36673.34897488674</v>
       </c>
       <c r="D17">
-        <v>39104.2672915215</v>
+        <v>39394.79397488674</v>
       </c>
       <c r="E17">
         <v>-8397.255000000001</v>
@@ -2687,37 +2687,37 @@
         <v>1744.9</v>
       </c>
       <c r="M17">
-        <v>371.2753425</v>
+        <v>356.8186035</v>
       </c>
       <c r="N17">
-        <v>1373.6246575</v>
+        <v>1388.0813965</v>
       </c>
       <c r="O17">
-        <v>200.549199995</v>
+        <v>202.659883889</v>
       </c>
       <c r="P17">
-        <v>1173.075457505</v>
+        <v>1185.421512611</v>
       </c>
       <c r="Q17">
-        <v>3966.975457505</v>
+        <v>3979.321512611</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07236158525288071</v>
+        <v>0.07234450851516776</v>
       </c>
       <c r="T17">
         <v>0.6130371481562993</v>
       </c>
       <c r="U17">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.69974652302691</v>
+        <v>4.890159825985643</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06873580648621552</v>
+        <v>0.06842070492589247</v>
       </c>
       <c r="C18">
-        <v>35954.13299742636</v>
+        <v>36264.28087898811</v>
       </c>
       <c r="D18">
-        <v>39113.66099742636</v>
+        <v>39423.80887898811</v>
       </c>
       <c r="E18">
         <v>-7959.172</v>
@@ -2769,37 +2769,37 @@
         <v>1744.9</v>
       </c>
       <c r="M18">
-        <v>396.027032</v>
+        <v>380.6065104</v>
       </c>
       <c r="N18">
-        <v>1348.872968</v>
+        <v>1364.2934896</v>
       </c>
       <c r="O18">
-        <v>196.935453328</v>
+        <v>199.1868494816</v>
       </c>
       <c r="P18">
-        <v>1151.937514672</v>
+        <v>1165.1066401184</v>
       </c>
       <c r="Q18">
-        <v>3945.837514672</v>
+        <v>3959.0066401184</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07263767438835181</v>
+        <v>0.07262042014987199</v>
       </c>
       <c r="T18">
         <v>0.6194092413365355</v>
       </c>
       <c r="U18">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.406012365337729</v>
+        <v>4.58452483686154</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06892986750748244</v>
+        <v>0.06839274761389234</v>
       </c>
       <c r="C19">
-        <v>35318.66206410671</v>
+        <v>35855.25555448535</v>
       </c>
       <c r="D19">
-        <v>38916.27306410671</v>
+        <v>39452.86655448535</v>
       </c>
       <c r="E19">
         <v>-7521.088999999999</v>
@@ -2851,45 +2851,45 @@
         <v>1744.9</v>
       </c>
       <c r="M19">
-        <v>431.2050969000001</v>
+        <v>404.3944173</v>
       </c>
       <c r="N19">
-        <v>1313.6949031</v>
+        <v>1340.5055827</v>
       </c>
       <c r="O19">
-        <v>191.7994558526</v>
+        <v>195.7138150742</v>
       </c>
       <c r="P19">
-        <v>1121.8954472474</v>
+        <v>1144.7917676258</v>
       </c>
       <c r="Q19">
-        <v>3915.7954472474</v>
+        <v>3938.6917676258</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07292041627407524</v>
+        <v>0.07290298025770162</v>
       </c>
       <c r="T19">
         <v>0.6259348789307533</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.046566268683638</v>
+        <v>4.314846905281449</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06893263252874937</v>
+        <v>0.06851851030189222</v>
       </c>
       <c r="C20">
-        <v>34877.78103446039</v>
+        <v>35286.79594079889</v>
       </c>
       <c r="D20">
-        <v>38913.47503446038</v>
+        <v>39322.48994079889</v>
       </c>
       <c r="E20">
         <v>-7083.005999999999</v>
@@ -2933,37 +2933,37 @@
         <v>1744.9</v>
       </c>
       <c r="M20">
-        <v>456.5701026</v>
+        <v>436.0678182</v>
       </c>
       <c r="N20">
-        <v>1288.3298974</v>
+        <v>1308.8321818</v>
       </c>
       <c r="O20">
-        <v>188.0961650204</v>
+        <v>191.0894985428</v>
       </c>
       <c r="P20">
-        <v>1100.2337323796</v>
+        <v>1117.7426832572</v>
       </c>
       <c r="Q20">
-        <v>3894.1337323796</v>
+        <v>3911.6426832572</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07321005430335288</v>
+        <v>0.07319243207547832</v>
       </c>
       <c r="T20">
         <v>0.632619678417513</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.821757031534548</v>
+        <v>4.001441810594038</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06893539755001628</v>
+        <v>0.0684990929898921</v>
       </c>
       <c r="C21">
-        <v>34436.90040713457</v>
+        <v>34868.78634749899</v>
       </c>
       <c r="D21">
-        <v>38910.67740713457</v>
+        <v>39342.56334749898</v>
       </c>
       <c r="E21">
         <v>-6644.922999999999</v>
@@ -3015,37 +3015,37 @@
         <v>1744.9</v>
       </c>
       <c r="M21">
-        <v>481.9351083000001</v>
+        <v>460.2938081000001</v>
       </c>
       <c r="N21">
-        <v>1262.9648917</v>
+        <v>1284.6061919</v>
       </c>
       <c r="O21">
-        <v>184.3928741882</v>
+        <v>187.5525040174</v>
       </c>
       <c r="P21">
-        <v>1078.5720175118</v>
+        <v>1097.0536878826</v>
       </c>
       <c r="Q21">
-        <v>3872.4720175118</v>
+        <v>3890.9536878826</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07350684388890899</v>
+        <v>0.07348903085171864</v>
       </c>
       <c r="T21">
         <v>0.6394695346817236</v>
       </c>
       <c r="U21">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.620611924611676</v>
+        <v>3.790839610036457</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06893816257128321</v>
+        <v>0.06847967567789195</v>
       </c>
       <c r="C22">
-        <v>33996.02018204246</v>
+        <v>34450.79725887499</v>
       </c>
       <c r="D22">
-        <v>38907.88018204246</v>
+        <v>39362.65725887499</v>
       </c>
       <c r="E22">
         <v>-6206.839999999998</v>
@@ -3097,37 +3097,37 @@
         <v>1744.9</v>
       </c>
       <c r="M22">
-        <v>507.3001140000001</v>
+        <v>484.5197980000001</v>
       </c>
       <c r="N22">
-        <v>1237.599886</v>
+        <v>1260.380202</v>
       </c>
       <c r="O22">
-        <v>180.689583356</v>
+        <v>184.015509492</v>
       </c>
       <c r="P22">
-        <v>1056.910302644</v>
+        <v>1076.364692508</v>
       </c>
       <c r="Q22">
-        <v>3850.810302644</v>
+        <v>3870.264692508</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.073811053214104</v>
+        <v>0.07379304459736495</v>
       </c>
       <c r="T22">
         <v>0.6464906373525394</v>
       </c>
       <c r="U22">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.439581328381093</v>
+        <v>3.601297629534634</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06894092759255013</v>
+        <v>0.06846025836589183</v>
       </c>
       <c r="C23">
-        <v>33555.14035909735</v>
+        <v>34032.82870636075</v>
       </c>
       <c r="D23">
-        <v>38905.08335909735</v>
+        <v>39382.77170636075</v>
       </c>
       <c r="E23">
         <v>-5768.757</v>
@@ -3179,37 +3179,37 @@
         <v>1744.9</v>
       </c>
       <c r="M23">
-        <v>532.6651197</v>
+        <v>508.7457879</v>
       </c>
       <c r="N23">
-        <v>1212.2348803</v>
+        <v>1236.1542121</v>
       </c>
       <c r="O23">
-        <v>176.9862925238</v>
+        <v>180.4785149666</v>
       </c>
       <c r="P23">
-        <v>1035.2485877762</v>
+        <v>1055.6756971334</v>
       </c>
       <c r="Q23">
-        <v>3829.1485877762</v>
+        <v>3849.5756971334</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07412296404120269</v>
+        <v>0.07410475489353396</v>
       </c>
       <c r="T23">
         <v>0.6536894894580594</v>
       </c>
       <c r="U23">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.275791741315327</v>
+        <v>3.429807266223461</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06894369261381705</v>
+        <v>0.06844084105389171</v>
       </c>
       <c r="C24">
-        <v>33114.2609382125</v>
+        <v>33614.88072145443</v>
       </c>
       <c r="D24">
-        <v>38902.2869382125</v>
+        <v>39402.90672145443</v>
       </c>
       <c r="E24">
         <v>-5330.673999999999</v>
@@ -3261,37 +3261,37 @@
         <v>1744.9</v>
       </c>
       <c r="M24">
-        <v>558.0301254000001</v>
+        <v>532.9717778</v>
       </c>
       <c r="N24">
-        <v>1186.8698746</v>
+        <v>1211.9282222</v>
       </c>
       <c r="O24">
-        <v>173.2830016916</v>
+        <v>176.9415204412</v>
       </c>
       <c r="P24">
-        <v>1013.5868729084</v>
+        <v>1034.9867017588</v>
       </c>
       <c r="Q24">
-        <v>3807.4868729084</v>
+        <v>3828.8867017588</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07444287258181673</v>
+        <v>0.07442445776139964</v>
       </c>
       <c r="T24">
         <v>0.661072927515003</v>
       </c>
       <c r="U24">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.126892116710084</v>
+        <v>3.273906935940577</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06945714963508397</v>
+        <v>0.0684214237418916</v>
       </c>
       <c r="C25">
-        <v>32163.7668541618</v>
+        <v>33196.95333571864</v>
       </c>
       <c r="D25">
-        <v>38389.87585416179</v>
+        <v>39423.06233571863</v>
       </c>
       <c r="E25">
         <v>-4892.590999999999</v>
@@ -3343,45 +3343,45 @@
         <v>1744.9</v>
       </c>
       <c r="M25">
-        <v>609.5924945</v>
+        <v>557.1977677000001</v>
       </c>
       <c r="N25">
-        <v>1135.3075055</v>
+        <v>1187.7022323</v>
       </c>
       <c r="O25">
-        <v>165.754895803</v>
+        <v>173.4045259158</v>
       </c>
       <c r="P25">
-        <v>969.552609697</v>
+        <v>1014.2977063842</v>
       </c>
       <c r="Q25">
-        <v>3763.452609697</v>
+        <v>3808.1977063842</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07477109043517398</v>
+        <v>0.07475246459985921</v>
       </c>
       <c r="T25">
         <v>0.6686481431838153</v>
       </c>
       <c r="U25">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.862404008814449</v>
+        <v>3.131563156117073</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06948211865635089</v>
+        <v>0.06840200642989146</v>
       </c>
       <c r="C26">
-        <v>31701.10965225803</v>
+        <v>32779.04658078062</v>
       </c>
       <c r="D26">
-        <v>38365.30165225803</v>
+        <v>39443.23858078061</v>
       </c>
       <c r="E26">
         <v>-4454.508</v>
@@ -3425,45 +3425,45 @@
         <v>1744.9</v>
       </c>
       <c r="M26">
-        <v>636.096516</v>
+        <v>581.4237576</v>
       </c>
       <c r="N26">
-        <v>1108.803484</v>
+        <v>1163.4762424</v>
       </c>
       <c r="O26">
-        <v>161.885308664</v>
+        <v>169.8675313904</v>
       </c>
       <c r="P26">
-        <v>946.918175336</v>
+        <v>993.6087110096</v>
       </c>
       <c r="Q26">
-        <v>3740.818175336</v>
+        <v>3787.5087110096</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07510794560046169</v>
+        <v>0.0750891031972256</v>
       </c>
       <c r="T26">
         <v>0.6764227066333858</v>
       </c>
       <c r="U26">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.743137175113847</v>
+        <v>3.001081357945529</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.0695070876776178</v>
+        <v>0.06891633911789133</v>
       </c>
       <c r="C27">
-        <v>31238.4838912</v>
+        <v>31813.40627367533</v>
       </c>
       <c r="D27">
-        <v>38340.7588912</v>
+        <v>38915.68127367533</v>
       </c>
       <c r="E27">
         <v>-4016.424999999999</v>
@@ -3507,37 +3507,37 @@
         <v>1744.9</v>
       </c>
       <c r="M27">
-        <v>662.6005375</v>
+        <v>633.0299350000001</v>
       </c>
       <c r="N27">
-        <v>1082.2994625</v>
+        <v>1111.870065</v>
       </c>
       <c r="O27">
-        <v>158.015721525</v>
+        <v>162.33302949</v>
       </c>
       <c r="P27">
-        <v>924.2837409750001</v>
+        <v>949.5370355100001</v>
       </c>
       <c r="Q27">
-        <v>3718.183740975</v>
+        <v>3743.43703551</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07545378357015707</v>
+        <v>0.07543471882385511</v>
       </c>
       <c r="T27">
         <v>0.6844045917749448</v>
       </c>
       <c r="U27">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.633411688109294</v>
+        <v>2.756425728903325</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06953205669888472</v>
+        <v>0.0689182718058912</v>
       </c>
       <c r="C28">
-        <v>30775.88951068699</v>
+        <v>31373.36750488717</v>
       </c>
       <c r="D28">
-        <v>38316.24751068699</v>
+        <v>38913.72550488717</v>
       </c>
       <c r="E28">
         <v>-3578.341999999999</v>
@@ -3589,37 +3589,37 @@
         <v>1744.9</v>
       </c>
       <c r="M28">
-        <v>689.1045590000001</v>
+        <v>658.3511324000001</v>
       </c>
       <c r="N28">
-        <v>1055.795441</v>
+        <v>1086.5488676</v>
       </c>
       <c r="O28">
-        <v>154.146134386</v>
+        <v>158.6361346696</v>
       </c>
       <c r="P28">
-        <v>901.649306614</v>
+        <v>927.9127329304</v>
       </c>
       <c r="Q28">
-        <v>3695.549306614</v>
+        <v>3721.8127329304</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07580896851200639</v>
+        <v>0.07578967541336649</v>
       </c>
       <c r="T28">
         <v>0.6926022035419515</v>
       </c>
       <c r="U28">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.532126623182013</v>
+        <v>2.650409354714736</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07017959172015165</v>
+        <v>0.06892020449389108</v>
       </c>
       <c r="C29">
-        <v>29712.90658241385</v>
+        <v>30933.3289326696</v>
       </c>
       <c r="D29">
-        <v>37691.34758241385</v>
+        <v>38911.7699326696</v>
       </c>
       <c r="E29">
         <v>-3140.258999999998</v>
@@ -3671,45 +3671,45 @@
         <v>1744.9</v>
       </c>
       <c r="M29">
-        <v>747.5448312000002</v>
+        <v>683.6723298000002</v>
       </c>
       <c r="N29">
-        <v>997.3551687999999</v>
+        <v>1061.2276702</v>
       </c>
       <c r="O29">
-        <v>145.6138546448</v>
+        <v>154.9392398492</v>
       </c>
       <c r="P29">
-        <v>851.7413141551999</v>
+        <v>906.2884303507999</v>
       </c>
       <c r="Q29">
-        <v>3645.6413141552</v>
+        <v>3700.1884303508</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07617388454815295</v>
+        <v>0.07615435684094669</v>
       </c>
       <c r="T29">
         <v>0.7010244074121638</v>
       </c>
       <c r="U29">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.334174389513189</v>
+        <v>2.552246045280857</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07022761874141857</v>
+        <v>0.06975905718189095</v>
       </c>
       <c r="C30">
-        <v>29229.28635916368</v>
+        <v>29664.62093835983</v>
       </c>
       <c r="D30">
-        <v>37645.81035916368</v>
+        <v>38081.14493835983</v>
       </c>
       <c r="E30">
         <v>-2702.175999999998</v>
@@ -3753,37 +3753,37 @@
         <v>1744.9</v>
       </c>
       <c r="M30">
-        <v>775.2316768000002</v>
+        <v>751.9256612000001</v>
       </c>
       <c r="N30">
-        <v>969.6683231999999</v>
+        <v>992.9743387999999</v>
       </c>
       <c r="O30">
-        <v>141.5715751872</v>
+        <v>144.9742534648</v>
       </c>
       <c r="P30">
-        <v>828.0967480127999</v>
+        <v>848.0000853352</v>
       </c>
       <c r="Q30">
-        <v>3621.9967480128</v>
+        <v>3641.9000853352</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07654893714085913</v>
+        <v>0.07652916830818188</v>
       </c>
       <c r="T30">
         <v>0.7096805613898819</v>
       </c>
       <c r="U30">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.250811018459146</v>
+        <v>2.320575144643035</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07143964776268549</v>
+        <v>0.07048432786989084</v>
       </c>
       <c r="C31">
-        <v>27677.35705384584</v>
+        <v>28536.44728428614</v>
       </c>
       <c r="D31">
-        <v>36531.96405384583</v>
+        <v>37391.05428428614</v>
       </c>
       <c r="E31">
         <v>-2264.093000000001</v>
@@ -3835,37 +3835,37 @@
         <v>1744.9</v>
       </c>
       <c r="M31">
-        <v>862.6292353</v>
+        <v>814.3524887</v>
       </c>
       <c r="N31">
-        <v>882.2707647000001</v>
+        <v>930.5475113000001</v>
       </c>
       <c r="O31">
-        <v>128.8115316462</v>
+        <v>135.8599366498</v>
       </c>
       <c r="P31">
-        <v>753.4592330538001</v>
+        <v>794.6875746502001</v>
       </c>
       <c r="Q31">
-        <v>3547.3592330538</v>
+        <v>3588.5875746502</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07693455459533168</v>
+        <v>0.07691453784491667</v>
       </c>
       <c r="T31">
         <v>0.7185805506909161</v>
       </c>
       <c r="U31">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.022769375991725</v>
+        <v>2.142683941183122</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0751146127839524</v>
+        <v>0.07054006255789072</v>
       </c>
       <c r="C32">
-        <v>24231.74217102362</v>
+        <v>28046.3664881758</v>
       </c>
       <c r="D32">
-        <v>33524.43217102362</v>
+        <v>37339.0564881758</v>
       </c>
       <c r="E32">
         <v>-1826.01</v>
@@ -3917,45 +3917,45 @@
         <v>1744.9</v>
       </c>
       <c r="M32">
-        <v>1076.369931</v>
+        <v>842.433609</v>
       </c>
       <c r="N32">
-        <v>668.5300690000001</v>
+        <v>902.466391</v>
       </c>
       <c r="O32">
-        <v>97.60539007400001</v>
+        <v>131.760093086</v>
       </c>
       <c r="P32">
-        <v>570.9246789260001</v>
+        <v>770.7062979140001</v>
       </c>
       <c r="Q32">
-        <v>3364.824678926</v>
+        <v>3564.606297914</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07733118969136059</v>
+        <v>0.07731091793984388</v>
       </c>
       <c r="T32">
         <v>0.7277348254005512</v>
       </c>
       <c r="U32">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.621096938650918</v>
+        <v>2.071261143143685</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07532233780521934</v>
+        <v>0.07059579724589057</v>
       </c>
       <c r="C33">
-        <v>23638.37829171842</v>
+        <v>27556.43011249331</v>
       </c>
       <c r="D33">
-        <v>33369.15129171842</v>
+        <v>37287.20311249331</v>
       </c>
       <c r="E33">
         <v>-1387.927</v>
@@ -3999,45 +3999,45 @@
         <v>1744.9</v>
       </c>
       <c r="M33">
-        <v>1112.2489287</v>
+        <v>870.5147293000001</v>
       </c>
       <c r="N33">
-        <v>632.6510713</v>
+        <v>874.3852707</v>
       </c>
       <c r="O33">
-        <v>92.3670564098</v>
+        <v>127.6602495222</v>
       </c>
       <c r="P33">
-        <v>540.2840148902001</v>
+        <v>746.7250211778</v>
       </c>
       <c r="Q33">
-        <v>3334.1840148902</v>
+        <v>3540.6250211778</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07773932145683962</v>
+        <v>0.0777187873128849</v>
       </c>
       <c r="T33">
         <v>0.7371544414061179</v>
       </c>
       <c r="U33">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.568803489017017</v>
+        <v>2.004446267558404</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07553006282648625</v>
+        <v>0.07384890793389046</v>
       </c>
       <c r="C34">
-        <v>23046.44626258617</v>
+        <v>24322.59640478434</v>
       </c>
       <c r="D34">
-        <v>33215.30226258617</v>
+        <v>34491.45240478434</v>
       </c>
       <c r="E34">
         <v>-949.8439999999991</v>
@@ -4081,37 +4081,37 @@
         <v>1744.9</v>
       </c>
       <c r="M34">
-        <v>1148.1279264</v>
+        <v>1062.6141248</v>
       </c>
       <c r="N34">
-        <v>596.7720736000001</v>
+        <v>682.2858752</v>
       </c>
       <c r="O34">
-        <v>87.12872274560002</v>
+        <v>99.61373777919999</v>
       </c>
       <c r="P34">
-        <v>509.6433508544001</v>
+        <v>582.6721374208</v>
       </c>
       <c r="Q34">
-        <v>3303.5433508544</v>
+        <v>3376.5721374208</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.0781594570977739</v>
+        <v>0.07813865284395655</v>
       </c>
       <c r="T34">
         <v>0.7468511049412598</v>
       </c>
       <c r="U34">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.519778379985236</v>
+        <v>1.642082444865314</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09012517483582391</v>
+        <v>0.07400456062189033</v>
       </c>
       <c r="C35">
-        <v>14481.23276096352</v>
+        <v>23761.21636707167</v>
       </c>
       <c r="D35">
-        <v>25088.17176096352</v>
+        <v>34368.15536707167</v>
       </c>
       <c r="E35">
         <v>-511.7609999999986</v>
@@ -4163,45 +4163,45 @@
         <v>1744.9</v>
       </c>
       <c r="M35">
-        <v>1892.3871351</v>
+        <v>1095.8208162</v>
       </c>
       <c r="N35">
-        <v>-147.4871350999999</v>
+        <v>649.0791837999998</v>
       </c>
       <c r="O35">
-        <v>-21.53312172459999</v>
+        <v>94.76556083479996</v>
       </c>
       <c r="P35">
-        <v>-125.9540133753999</v>
+        <v>554.3136229651998</v>
       </c>
       <c r="Q35">
-        <v>2667.9459866246</v>
+        <v>3348.2136229652</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07872150178521085</v>
+        <v>0.07857105167446318</v>
       </c>
       <c r="T35">
-        <v>0.7598230066196575</v>
+        <v>0.756837221119242</v>
       </c>
       <c r="U35">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
-        <v>0.1346211857366796</v>
+        <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.1132780867870686</v>
+        <v>0.0647332</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.9220629160046545</v>
+        <v>1.592322370778486</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09097617483582392</v>
+        <v>0.0741602133098902</v>
       </c>
       <c r="C36">
-        <v>13690.2608325316</v>
+        <v>23200.7146924703</v>
       </c>
       <c r="D36">
-        <v>24735.2828325316</v>
+        <v>34245.73669247029</v>
       </c>
       <c r="E36">
         <v>-73.67799999999806</v>
@@ -4245,45 +4245,45 @@
         <v>1744.9</v>
       </c>
       <c r="M36">
-        <v>1949.7321998</v>
+        <v>1129.0275076</v>
       </c>
       <c r="N36">
-        <v>-204.8321997999999</v>
+        <v>615.8724923999998</v>
       </c>
       <c r="O36">
-        <v>-29.90550117079998</v>
+        <v>89.91738389039998</v>
       </c>
       <c r="P36">
-        <v>-174.9266986291999</v>
+        <v>525.9551085095999</v>
       </c>
       <c r="Q36">
-        <v>2618.9733013708</v>
+        <v>3319.8551085096</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07922031241832012</v>
+        <v>0.07901655349983364</v>
       </c>
       <c r="T36">
-        <v>0.771335476416925</v>
+        <v>0.7671259468783751</v>
       </c>
       <c r="U36">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
-        <v>0.1306617390973654</v>
+        <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.1137963783521549</v>
+        <v>0.0647332</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8949434184751058</v>
+        <v>1.545489359873236</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09182717483582392</v>
+        <v>0.07431586599789007</v>
       </c>
       <c r="C37">
-        <v>12909.07863710887</v>
+        <v>22641.08202815987</v>
       </c>
       <c r="D37">
-        <v>24392.18363710887</v>
+        <v>34124.18702815987</v>
       </c>
       <c r="E37">
         <v>364.4050000000025</v>
@@ -4327,45 +4327,45 @@
         <v>1744.9</v>
       </c>
       <c r="M37">
-        <v>2007.0772645</v>
+        <v>1162.234199</v>
       </c>
       <c r="N37">
-        <v>-262.1772645000001</v>
+        <v>582.6658009999999</v>
       </c>
       <c r="O37">
-        <v>-38.27788061700001</v>
+        <v>85.06920694599998</v>
       </c>
       <c r="P37">
-        <v>-223.8993838830001</v>
+        <v>497.5965940539999</v>
       </c>
       <c r="Q37">
-        <v>2570.000616117</v>
+        <v>3291.496594054</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07973447107090964</v>
+        <v>0.07947576307367704</v>
       </c>
       <c r="T37">
-        <v>0.7832021760541086</v>
+        <v>0.7777312488147122</v>
       </c>
       <c r="U37">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
-        <v>0.1269285465517264</v>
+        <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.114285053256379</v>
+        <v>0.0647332</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8693736065186741</v>
+        <v>1.501332521019715</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09267817483582391</v>
+        <v>0.08812971227367879</v>
       </c>
       <c r="C38">
-        <v>12137.28437251585</v>
+        <v>14028.84010762305</v>
       </c>
       <c r="D38">
-        <v>24058.47237251585</v>
+        <v>25950.02810762305</v>
       </c>
       <c r="E38">
         <v>802.4880000000012</v>
@@ -4409,37 +4409,37 @@
         <v>1744.9</v>
       </c>
       <c r="M38">
-        <v>2064.4223292</v>
+        <v>1870.4391768</v>
       </c>
       <c r="N38">
-        <v>-319.5223292000001</v>
+        <v>-125.5391768000002</v>
       </c>
       <c r="O38">
-        <v>-46.65026006320001</v>
+        <v>-18.32871981280002</v>
       </c>
       <c r="P38">
-        <v>-272.8720691368001</v>
+        <v>-107.2104569872002</v>
       </c>
       <c r="Q38">
-        <v>2521.0279308632</v>
+        <v>2686.6895430128</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08026469718139262</v>
+        <v>0.08007647442804083</v>
       </c>
       <c r="T38">
-        <v>0.795439710054954</v>
+        <v>0.7916044902549846</v>
       </c>
       <c r="U38">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.1234027535919563</v>
+        <v>0.1362008469240057</v>
       </c>
       <c r="W38">
-        <v>0.1147465795548129</v>
+        <v>0.1024465795548129</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8452243396709332</v>
+        <v>0.932882513178121</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09352917483582393</v>
+        <v>0.08885771227367879</v>
       </c>
       <c r="C39">
-        <v>11374.49792815007</v>
+        <v>13267.24753681334</v>
       </c>
       <c r="D39">
-        <v>23733.76892815008</v>
+        <v>25626.51853681334</v>
       </c>
       <c r="E39">
         <v>1240.571000000002</v>
@@ -4491,37 +4491,37 @@
         <v>1744.9</v>
       </c>
       <c r="M39">
-        <v>2121.7673939</v>
+        <v>1922.3958206</v>
       </c>
       <c r="N39">
-        <v>-376.8673939</v>
+        <v>-177.4958206000003</v>
       </c>
       <c r="O39">
-        <v>-55.0226395094</v>
+        <v>-25.91438980760005</v>
       </c>
       <c r="P39">
-        <v>-321.8447543906</v>
+        <v>-151.5814307924003</v>
       </c>
       <c r="Q39">
-        <v>2472.0552456094</v>
+        <v>2642.3185692076</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08081175586681155</v>
+        <v>0.08062054545070815</v>
       </c>
       <c r="T39">
-        <v>0.8080657371986835</v>
+        <v>0.8041696408939526</v>
       </c>
       <c r="U39">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.1200675440354169</v>
+        <v>0.1325197429530866</v>
       </c>
       <c r="W39">
-        <v>0.1151831584857639</v>
+        <v>0.1028831584857639</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8223804385987459</v>
+        <v>0.9076694722814149</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09438017483582392</v>
+        <v>0.08958571227367879</v>
       </c>
       <c r="C40">
-        <v>10620.35944068498</v>
+        <v>12513.6217989202</v>
       </c>
       <c r="D40">
-        <v>23417.71344068499</v>
+        <v>25310.9757989202</v>
       </c>
       <c r="E40">
         <v>1678.654000000002</v>
@@ -4573,37 +4573,37 @@
         <v>1744.9</v>
       </c>
       <c r="M40">
-        <v>2179.1124586</v>
+        <v>1974.3524644</v>
       </c>
       <c r="N40">
-        <v>-434.2124586</v>
+        <v>-229.4524644000003</v>
       </c>
       <c r="O40">
-        <v>-63.39501895559999</v>
+        <v>-33.50005980240004</v>
       </c>
       <c r="P40">
-        <v>-370.8174396444</v>
+        <v>-195.9524045976002</v>
       </c>
       <c r="Q40">
-        <v>2423.0825603556</v>
+        <v>2597.9475954024</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08137646160659882</v>
+        <v>0.08118216715152601</v>
       </c>
       <c r="T40">
-        <v>0.8210990555405976</v>
+        <v>0.8171401189728873</v>
       </c>
       <c r="U40">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.1169078718239586</v>
+        <v>0.1290323812964264</v>
       </c>
       <c r="W40">
-        <v>0.1155967595782438</v>
+        <v>0.1032967595782438</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8007388481093052</v>
+        <v>0.8837834335371673</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1287456095445476</v>
+        <v>0.09031371227367879</v>
       </c>
       <c r="C41">
-        <v>1993.01586048177</v>
+        <v>11767.67218347413</v>
       </c>
       <c r="D41">
-        <v>15228.45286048177</v>
+        <v>25003.10918347413</v>
       </c>
       <c r="E41">
         <v>2116.737000000001</v>
@@ -4655,45 +4655,45 @@
         <v>1744.9</v>
       </c>
       <c r="M41">
-        <v>3686.994144600001</v>
+        <v>2026.3091082</v>
       </c>
       <c r="N41">
-        <v>-1942.094144600001</v>
+        <v>-281.4091082000002</v>
       </c>
       <c r="O41">
-        <v>-283.5457451116001</v>
+        <v>-41.08572979720003</v>
       </c>
       <c r="P41">
-        <v>-1658.5483994884</v>
+        <v>-240.3233784028002</v>
       </c>
       <c r="Q41">
-        <v>1135.3516005116</v>
+        <v>2553.5766215972</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08262105066363103</v>
+        <v>0.08176220267860021</v>
       </c>
       <c r="T41">
-        <v>0.8498239723287178</v>
+        <v>0.8305358586281805</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.06909568879384217</v>
+        <v>0.1257238586990821</v>
       </c>
       <c r="W41">
-        <v>0.2008891503582889</v>
+        <v>0.1036891503582889</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.4732581424235766</v>
+        <v>0.861122319856727</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1304456095445476</v>
+        <v>0.0910417122736788</v>
       </c>
       <c r="C42">
-        <v>1295.971873594091</v>
+        <v>11029.12195410281</v>
       </c>
       <c r="D42">
-        <v>14969.49187359409</v>
+        <v>24702.64195410281</v>
       </c>
       <c r="E42">
         <v>2554.820000000003</v>
@@ -4737,45 +4737,45 @@
         <v>1744.9</v>
       </c>
       <c r="M42">
-        <v>3781.532456000001</v>
+        <v>2078.265752000001</v>
       </c>
       <c r="N42">
-        <v>-2036.632456000001</v>
+        <v>-333.3657520000006</v>
       </c>
       <c r="O42">
-        <v>-297.3483385760002</v>
+        <v>-48.67139979200009</v>
       </c>
       <c r="P42">
-        <v>-1739.284117424001</v>
+        <v>-284.6943522080005</v>
       </c>
       <c r="Q42">
-        <v>1054.615882575999</v>
+        <v>2509.205647792</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08323473484135821</v>
+        <v>0.08236157272324356</v>
       </c>
       <c r="T42">
-        <v>0.863987705200863</v>
+        <v>0.8443781229386502</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V42">
-        <v>0.06736829657399611</v>
+        <v>0.1225807622316051</v>
       </c>
       <c r="W42">
-        <v>0.2012619215993317</v>
+        <v>0.1040619215993316</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.4614266888629871</v>
+        <v>0.8395942618603087</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1321456095445476</v>
+        <v>0.09176971227367881</v>
       </c>
       <c r="C43">
-        <v>607.5879242557166</v>
+        <v>10297.70751885428</v>
       </c>
       <c r="D43">
-        <v>14719.19092425572</v>
+        <v>24409.31051885428</v>
       </c>
       <c r="E43">
         <v>2992.903000000002</v>
@@ -4819,45 +4819,45 @@
         <v>1744.9</v>
       </c>
       <c r="M43">
-        <v>3876.070767400001</v>
+        <v>2130.2223958</v>
       </c>
       <c r="N43">
-        <v>-2131.170767400001</v>
+        <v>-385.3223958000003</v>
       </c>
       <c r="O43">
-        <v>-311.1509320404001</v>
+        <v>-56.25706978680005</v>
       </c>
       <c r="P43">
-        <v>-1820.019835359601</v>
+        <v>-329.0653260132003</v>
       </c>
       <c r="Q43">
-        <v>973.8801646403995</v>
+        <v>2464.8346739868</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08386922187256766</v>
+        <v>0.08298126039651887</v>
       </c>
       <c r="T43">
-        <v>0.8786315646110471</v>
+        <v>0.8586896165477799</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V43">
-        <v>0.06572516738926451</v>
+        <v>0.1195909875430294</v>
       </c>
       <c r="W43">
-        <v>0.2016165088773967</v>
+        <v>0.1044165088773967</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.4501723793785241</v>
+        <v>0.8191163530344476</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1338456095445476</v>
+        <v>0.1274847333640202</v>
       </c>
       <c r="C44">
-        <v>-72.56325004182872</v>
+        <v>874.3314994079919</v>
       </c>
       <c r="D44">
-        <v>14477.12274995817</v>
+        <v>15424.01749940799</v>
       </c>
       <c r="E44">
         <v>3430.986000000001</v>
@@ -4901,37 +4901,37 @@
         <v>1744.9</v>
       </c>
       <c r="M44">
-        <v>3970.609078800001</v>
+        <v>3694.6167888</v>
       </c>
       <c r="N44">
-        <v>-2225.7090788</v>
+        <v>-1949.7167888</v>
       </c>
       <c r="O44">
-        <v>-324.9535255048</v>
+        <v>-284.6586511648001</v>
       </c>
       <c r="P44">
-        <v>-1900.755553295201</v>
+        <v>-1665.0581376352</v>
       </c>
       <c r="Q44">
-        <v>893.1444467047995</v>
+        <v>1128.8418623648</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08452558776692227</v>
+        <v>0.08442062883497851</v>
       </c>
       <c r="T44">
-        <v>0.8937803846905479</v>
+        <v>0.8919313818701735</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06416028245142488</v>
+        <v>0.06895313223614287</v>
       </c>
       <c r="W44">
-        <v>0.2019542110469825</v>
+        <v>0.1869542110469825</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4394539893933211</v>
+        <v>0.4722817276448142</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1355456095445476</v>
+        <v>0.1290347333640202</v>
       </c>
       <c r="C45">
-        <v>-744.8812599483572</v>
+        <v>193.7149930583291</v>
       </c>
       <c r="D45">
-        <v>14242.88774005164</v>
+        <v>15181.48399305833</v>
       </c>
       <c r="E45">
         <v>3869.069</v>
@@ -4983,37 +4983,37 @@
         <v>1744.9</v>
       </c>
       <c r="M45">
-        <v>4065.1473902</v>
+        <v>3782.5838552</v>
       </c>
       <c r="N45">
-        <v>-2320.2473902</v>
+        <v>-2037.6838552</v>
       </c>
       <c r="O45">
-        <v>-338.7561189692</v>
+        <v>-297.5018428592</v>
       </c>
       <c r="P45">
-        <v>-1981.4912712308</v>
+        <v>-1740.1820123408</v>
       </c>
       <c r="Q45">
-        <v>812.4087287692</v>
+        <v>1053.7179876592</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08520498404353495</v>
+        <v>0.08509818372682024</v>
       </c>
       <c r="T45">
-        <v>0.9094607423166979</v>
+        <v>0.907579300850352</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.06266818285953128</v>
+        <v>0.06734957102134886</v>
       </c>
       <c r="W45">
-        <v>0.2022762061389132</v>
+        <v>0.1872762061389132</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4292341291748718</v>
+        <v>0.4612984316530745</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1372456095445476</v>
+        <v>0.1305847333640202</v>
       </c>
       <c r="C46">
-        <v>-1409.740265626795</v>
+        <v>-479.3922023165542</v>
       </c>
       <c r="D46">
-        <v>14016.11173437321</v>
+        <v>14946.45979768345</v>
       </c>
       <c r="E46">
         <v>4307.152000000002</v>
@@ -5065,37 +5065,37 @@
         <v>1744.9</v>
       </c>
       <c r="M46">
-        <v>4159.6857016</v>
+        <v>3870.5509216</v>
       </c>
       <c r="N46">
-        <v>-2414.7857016</v>
+        <v>-2125.6509216</v>
       </c>
       <c r="O46">
-        <v>-352.5587124336</v>
+        <v>-310.3450345536</v>
       </c>
       <c r="P46">
-        <v>-2062.2269891664</v>
+        <v>-1815.3058870464</v>
       </c>
       <c r="Q46">
-        <v>731.6730108336001</v>
+        <v>978.5941129535997</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08590864447288379</v>
+        <v>0.08579993700765631</v>
       </c>
       <c r="T46">
-        <v>0.9257011127152104</v>
+        <v>0.9237860740798227</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.06124390597636012</v>
+        <v>0.06581889895268184</v>
       </c>
       <c r="W46">
-        <v>0.2025835650903015</v>
+        <v>0.1875835650903015</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4194788080572611</v>
+        <v>0.4508143763882319</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1389456095445476</v>
+        <v>0.1321347333640202</v>
       </c>
       <c r="C47">
-        <v>-2067.490971118688</v>
+        <v>-1145.333524364429</v>
       </c>
       <c r="D47">
-        <v>13796.44402888131</v>
+        <v>14718.60147563557</v>
       </c>
       <c r="E47">
         <v>4745.235000000001</v>
@@ -5147,37 +5147,37 @@
         <v>1744.9</v>
       </c>
       <c r="M47">
-        <v>4254.224013000001</v>
+        <v>3958.517988</v>
       </c>
       <c r="N47">
-        <v>-2509.324013000001</v>
+        <v>-2213.617988</v>
       </c>
       <c r="O47">
-        <v>-366.3613058980001</v>
+        <v>-323.188226248</v>
       </c>
       <c r="P47">
-        <v>-2142.962707102001</v>
+        <v>-1890.429761752</v>
       </c>
       <c r="Q47">
-        <v>650.9372928979992</v>
+        <v>903.470238248</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08663789255420895</v>
+        <v>0.08652720858961371</v>
       </c>
       <c r="T47">
-        <v>0.9425320420373051</v>
+        <v>0.9405821845176376</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05988293028799655</v>
+        <v>0.06435625675373335</v>
       </c>
       <c r="W47">
-        <v>0.2028772636438504</v>
+        <v>0.1878772636438504</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4101570567670997</v>
+        <v>0.4407962791351601</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1406456095445476</v>
+        <v>0.1336847333640202</v>
       </c>
       <c r="C48">
-        <v>-2718.462434063331</v>
+        <v>-1804.431782425261</v>
       </c>
       <c r="D48">
-        <v>13583.55556593667</v>
+        <v>14497.58621757474</v>
       </c>
       <c r="E48">
         <v>5183.318000000003</v>
@@ -5229,37 +5229,37 @@
         <v>1744.9</v>
       </c>
       <c r="M48">
-        <v>4348.762324400001</v>
+        <v>4046.485054400001</v>
       </c>
       <c r="N48">
-        <v>-2603.8623244</v>
+        <v>-2301.5850544</v>
       </c>
       <c r="O48">
-        <v>-380.1638993624001</v>
+        <v>-336.0314179424</v>
       </c>
       <c r="P48">
-        <v>-2223.6984250376</v>
+        <v>-1965.553636457601</v>
       </c>
       <c r="Q48">
-        <v>570.2015749623997</v>
+        <v>828.3463635423996</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08739414982373134</v>
+        <v>0.08728141615608803</v>
       </c>
       <c r="T48">
-        <v>0.95998633911207</v>
+        <v>0.9580003731198161</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.05858112745564881</v>
+        <v>0.06295720769386959</v>
       </c>
       <c r="W48">
-        <v>0.203158192695071</v>
+        <v>0.188158192695071</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4012405990112933</v>
+        <v>0.4312137513278739</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1423456095445476</v>
+        <v>0.1352347333640202</v>
       </c>
       <c r="C49">
-        <v>-3362.963710411801</v>
+        <v>-2456.990683397296</v>
       </c>
       <c r="D49">
-        <v>13377.1372895882</v>
+        <v>14283.11031660271</v>
       </c>
       <c r="E49">
         <v>5621.401000000002</v>
@@ -5311,37 +5311,37 @@
         <v>1744.9</v>
       </c>
       <c r="M49">
-        <v>4443.300635800001</v>
+        <v>4134.452120800001</v>
       </c>
       <c r="N49">
-        <v>-2698.400635800001</v>
+        <v>-2389.5521208</v>
       </c>
       <c r="O49">
-        <v>-393.9664928268001</v>
+        <v>-348.8746096368001</v>
       </c>
       <c r="P49">
-        <v>-2304.434142973201</v>
+        <v>-2040.677511163201</v>
       </c>
       <c r="Q49">
-        <v>489.4658570267993</v>
+        <v>753.2224888367996</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08817894510342439</v>
+        <v>0.08806408438544819</v>
       </c>
       <c r="T49">
-        <v>0.9780992889066373</v>
+        <v>0.9760758518579259</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05733472048850734</v>
+        <v>0.06161769263655321</v>
       </c>
       <c r="W49">
-        <v>0.2034271673185802</v>
+        <v>0.1884271673185801</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3927035649897763</v>
+        <v>0.4220389906613233</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1440456095445476</v>
+        <v>0.1367847333640202</v>
       </c>
       <c r="C50">
-        <v>-4001.285351425493</v>
+        <v>-3103.296224136469</v>
       </c>
       <c r="D50">
-        <v>13176.89864857451</v>
+        <v>14074.88777586353</v>
       </c>
       <c r="E50">
         <v>6059.484</v>
@@ -5393,37 +5393,37 @@
         <v>1744.9</v>
       </c>
       <c r="M50">
-        <v>4537.838947200001</v>
+        <v>4222.4191872</v>
       </c>
       <c r="N50">
-        <v>-2792.938947200001</v>
+        <v>-2477.5191872</v>
       </c>
       <c r="O50">
-        <v>-407.7690862912001</v>
+        <v>-361.7178013312</v>
       </c>
       <c r="P50">
-        <v>-2385.169860908801</v>
+        <v>-2115.8013858688</v>
       </c>
       <c r="Q50">
-        <v>408.7301390911994</v>
+        <v>678.0986141312001</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08899392481695177</v>
+        <v>0.08887685523901451</v>
       </c>
       <c r="T50">
-        <v>0.9969088906163803</v>
+        <v>0.9948465413167321</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05614024714499677</v>
+        <v>0.06033399070662502</v>
       </c>
       <c r="W50">
-        <v>0.2036849346661097</v>
+        <v>0.1886849346661097</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.384522240719156</v>
+        <v>0.4132465116892126</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1457456095445476</v>
+        <v>0.1383347333640202</v>
       </c>
       <c r="C51">
-        <v>-4633.700768208542</v>
+        <v>-3743.617963813493</v>
       </c>
       <c r="D51">
-        <v>12982.56623179146</v>
+        <v>13872.64903618651</v>
       </c>
       <c r="E51">
         <v>6497.567000000003</v>
@@ -5475,37 +5475,37 @@
         <v>1744.9</v>
       </c>
       <c r="M51">
-        <v>4632.377258600001</v>
+        <v>4310.386253600001</v>
       </c>
       <c r="N51">
-        <v>-2887.477258600001</v>
+        <v>-2565.486253600001</v>
       </c>
       <c r="O51">
-        <v>-421.5716797556001</v>
+        <v>-374.5609930256001</v>
       </c>
       <c r="P51">
-        <v>-2465.905578844401</v>
+        <v>-2190.9252605744</v>
       </c>
       <c r="Q51">
-        <v>327.994421155599</v>
+        <v>602.9747394255996</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08984086451924495</v>
+        <v>0.08972149945938733</v>
       </c>
       <c r="T51">
-        <v>1.016456123765721</v>
+        <v>1.014353336244511</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05499452781550703</v>
+        <v>0.05910268477383675</v>
       </c>
       <c r="W51">
-        <v>0.2039321808974136</v>
+        <v>0.1889321808974136</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.376674848051418</v>
+        <v>0.4048129094098408</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1474456095445476</v>
+        <v>0.1398847333640202</v>
       </c>
       <c r="C52">
-        <v>-5260.46747725059</v>
+        <v>-4378.210188131572</v>
       </c>
       <c r="D52">
-        <v>12793.88252274941</v>
+        <v>13676.13981186843</v>
       </c>
       <c r="E52">
         <v>6935.650000000001</v>
@@ -5557,37 +5557,37 @@
         <v>1744.9</v>
       </c>
       <c r="M52">
-        <v>4726.915570000001</v>
+        <v>4398.35332</v>
       </c>
       <c r="N52">
-        <v>-2982.015570000001</v>
+        <v>-2653.45332</v>
       </c>
       <c r="O52">
-        <v>-435.3742732200001</v>
+        <v>-387.40418472</v>
       </c>
       <c r="P52">
-        <v>-2546.641296780001</v>
+        <v>-2266.04913528</v>
       </c>
       <c r="Q52">
-        <v>247.2587032199995</v>
+        <v>527.8508647200001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09072168180962985</v>
+        <v>0.09059992944857509</v>
       </c>
       <c r="T52">
-        <v>1.036785246241036</v>
+        <v>1.034640402969401</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.0538946372591969</v>
+        <v>0.05792063107836002</v>
       </c>
       <c r="W52">
-        <v>0.2041695372794653</v>
+        <v>0.1891695372794653</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3691413510903897</v>
+        <v>0.396716651221644</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1491456095445476</v>
+        <v>0.1414347333640202</v>
       </c>
       <c r="C53">
-        <v>-5881.828238912127</v>
+        <v>-5007.312975977755</v>
       </c>
       <c r="D53">
-        <v>12610.60476108787</v>
+        <v>13485.12002402224</v>
       </c>
       <c r="E53">
         <v>7373.733</v>
@@ -5639,37 +5639,37 @@
         <v>1744.9</v>
       </c>
       <c r="M53">
-        <v>4821.453881400001</v>
+        <v>4486.3203864</v>
       </c>
       <c r="N53">
-        <v>-3076.553881400001</v>
+        <v>-2741.4203864</v>
       </c>
       <c r="O53">
-        <v>-449.1768666844001</v>
+        <v>-400.2473764143999</v>
       </c>
       <c r="P53">
-        <v>-2627.377014715601</v>
+        <v>-2341.173009985599</v>
       </c>
       <c r="Q53">
-        <v>166.5229852843995</v>
+        <v>452.7269900144006</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09163845082615291</v>
+        <v>0.09151421372303579</v>
       </c>
       <c r="T53">
-        <v>1.057944128817383</v>
+        <v>1.055755513234083</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05283787966587932</v>
+        <v>0.05678493242976473</v>
       </c>
       <c r="W53">
-        <v>0.2043975855681033</v>
+        <v>0.1893975855681033</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3619032853827351</v>
+        <v>0.388937893354553</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1508456095445476</v>
+        <v>0.1429847333640202</v>
       </c>
       <c r="C54">
-        <v>-6498.012099436062</v>
+        <v>-5631.153177915636</v>
       </c>
       <c r="D54">
-        <v>12432.50390056394</v>
+        <v>13299.36282208437</v>
       </c>
       <c r="E54">
         <v>7811.816000000003</v>
@@ -5721,37 +5721,37 @@
         <v>1744.9</v>
       </c>
       <c r="M54">
-        <v>4915.992192800001</v>
+        <v>4574.2874528</v>
       </c>
       <c r="N54">
-        <v>-3171.092192800001</v>
+        <v>-2829.3874528</v>
       </c>
       <c r="O54">
-        <v>-462.9794601488001</v>
+        <v>-413.0905681088</v>
       </c>
       <c r="P54">
-        <v>-2708.112732651201</v>
+        <v>-2416.2968846912</v>
       </c>
       <c r="Q54">
-        <v>85.78726734879911</v>
+        <v>377.6031153088002</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09259341855169777</v>
+        <v>0.09246659317559905</v>
       </c>
       <c r="T54">
-        <v>1.079984631501079</v>
+        <v>1.077750419759793</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.05182176659538163</v>
+        <v>0.0556929144984231</v>
       </c>
       <c r="W54">
-        <v>0.2046168627687167</v>
+        <v>0.1896168627687166</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3549436068176824</v>
+        <v>0.38145831848235</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1525456095445476</v>
+        <v>0.1445347333640202</v>
       </c>
       <c r="C55">
-        <v>-7109.235345890371</v>
+        <v>-6249.945314904726</v>
       </c>
       <c r="D55">
-        <v>12259.36365410963</v>
+        <v>13118.65368509527</v>
       </c>
       <c r="E55">
         <v>8249.899000000001</v>
@@ -5803,37 +5803,37 @@
         <v>1744.9</v>
       </c>
       <c r="M55">
-        <v>5010.530504200001</v>
+        <v>4662.254519200001</v>
       </c>
       <c r="N55">
-        <v>-3265.630504200001</v>
+        <v>-2917.354519200001</v>
       </c>
       <c r="O55">
-        <v>-476.7820536132001</v>
+        <v>-425.9337598032001</v>
       </c>
       <c r="P55">
-        <v>-2788.848450586801</v>
+        <v>-2491.4207593968</v>
       </c>
       <c r="Q55">
-        <v>5.051549413199155</v>
+        <v>302.4792406031997</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09358902320173387</v>
+        <v>0.09345949941337775</v>
       </c>
       <c r="T55">
-        <v>1.102963027915995</v>
+        <v>1.100681279754682</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.0508439974143367</v>
+        <v>0.05464210479090568</v>
       </c>
       <c r="W55">
-        <v>0.2048278653579862</v>
+        <v>0.1898278653579862</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3482465576324432</v>
+        <v>0.374260991718532</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1542456095445476</v>
+        <v>0.1460847333640202</v>
       </c>
       <c r="C56">
-        <v>-7715.702382413227</v>
+        <v>-6863.89240473228</v>
       </c>
       <c r="D56">
-        <v>12090.97961758678</v>
+        <v>12942.78959526772</v>
       </c>
       <c r="E56">
         <v>8687.982000000004</v>
@@ -5885,37 +5885,37 @@
         <v>1744.9</v>
       </c>
       <c r="M56">
-        <v>5105.068815600001</v>
+        <v>4750.221585600001</v>
       </c>
       <c r="N56">
-        <v>-3360.168815600001</v>
+        <v>-3005.321585600001</v>
       </c>
       <c r="O56">
-        <v>-490.5846470776002</v>
+        <v>-438.7769514976001</v>
       </c>
       <c r="P56">
-        <v>-2869.584168522401</v>
+        <v>-2566.544634102401</v>
       </c>
       <c r="Q56">
-        <v>-75.68416852240125</v>
+        <v>227.3553658975993</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09462791501046722</v>
+        <v>0.09449557548758161</v>
       </c>
       <c r="T56">
-        <v>1.126940485044604</v>
+        <v>1.124609133662393</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.04990244190666379</v>
+        <v>0.05363021396144445</v>
       </c>
       <c r="W56">
-        <v>0.205031053036542</v>
+        <v>0.190031053036542</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3417975473059164</v>
+        <v>0.3673302326126333</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1559456095445476</v>
+        <v>0.1476347333640202</v>
       </c>
       <c r="C57">
-        <v>-8317.60653522432</v>
+        <v>-7473.186722851293</v>
       </c>
       <c r="D57">
-        <v>11927.15846477568</v>
+        <v>12771.57827714871</v>
       </c>
       <c r="E57">
         <v>9126.065000000002</v>
@@ -5967,37 +5967,37 @@
         <v>1744.9</v>
       </c>
       <c r="M57">
-        <v>5199.607127000001</v>
+        <v>4838.188652000001</v>
       </c>
       <c r="N57">
-        <v>-3454.707127000001</v>
+        <v>-3093.288652000001</v>
       </c>
       <c r="O57">
-        <v>-504.3872405420001</v>
+        <v>-451.6201431920001</v>
       </c>
       <c r="P57">
-        <v>-2950.319886458001</v>
+        <v>-2641.668508808001</v>
       </c>
       <c r="Q57">
-        <v>-156.4198864580007</v>
+        <v>152.2314911919993</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09571297978847762</v>
+        <v>0.09557769938730565</v>
       </c>
       <c r="T57">
-        <v>1.151983606934484</v>
+        <v>1.14960044774378</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.04899512478108808</v>
+        <v>0.05265511916214546</v>
       </c>
       <c r="W57">
-        <v>0.2052268520722412</v>
+        <v>0.1902268520722412</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3355830464458088</v>
+        <v>0.3606515011105854</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1576456095445476</v>
+        <v>0.1491847333640202</v>
       </c>
       <c r="C58">
-        <v>-8915.130793068343</v>
+        <v>-8078.010503619334</v>
       </c>
       <c r="D58">
-        <v>11767.71720693166</v>
+        <v>12604.83749638067</v>
       </c>
       <c r="E58">
         <v>9564.148000000005</v>
@@ -6049,37 +6049,37 @@
         <v>1744.9</v>
       </c>
       <c r="M58">
-        <v>5294.145438400002</v>
+        <v>4926.155718400001</v>
       </c>
       <c r="N58">
-        <v>-3549.245438400002</v>
+        <v>-3181.255718400001</v>
       </c>
       <c r="O58">
-        <v>-518.1898340064002</v>
+        <v>-464.4633348864002</v>
       </c>
       <c r="P58">
-        <v>-3031.055604393601</v>
+        <v>-2716.792383513601</v>
       </c>
       <c r="Q58">
-        <v>-237.1556043936012</v>
+        <v>77.10761648639937</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09684736569276119</v>
+        <v>0.09670901073701713</v>
       </c>
       <c r="T58">
-        <v>1.178165052546631</v>
+        <v>1.175727730647047</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.04812021183856866</v>
+        <v>0.05171484917710716</v>
       </c>
       <c r="W58">
-        <v>0.2054156582852369</v>
+        <v>0.1904156582852369</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3295904920449908</v>
+        <v>0.3542112957336107</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1593456095445476</v>
+        <v>0.1507347333640202</v>
       </c>
       <c r="C59">
-        <v>-9508.448489052738</v>
+        <v>-8678.536587314557</v>
       </c>
       <c r="D59">
-        <v>11612.48251094727</v>
+        <v>12442.39441268545</v>
       </c>
       <c r="E59">
         <v>10002.231</v>
@@ -6131,37 +6131,37 @@
         <v>1744.9</v>
       </c>
       <c r="M59">
-        <v>5388.683749800001</v>
+        <v>5014.122784800001</v>
       </c>
       <c r="N59">
-        <v>-3643.783749800001</v>
+        <v>-3269.222784800001</v>
       </c>
       <c r="O59">
-        <v>-531.9924274708002</v>
+        <v>-477.3065265808001</v>
       </c>
       <c r="P59">
-        <v>-3111.791322329201</v>
+        <v>-2791.916258219201</v>
       </c>
       <c r="Q59">
-        <v>-317.8913223292011</v>
+        <v>1.983741780799392</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09803451373212774</v>
+        <v>0.09789294121927335</v>
       </c>
       <c r="T59">
-        <v>1.205564239815158</v>
+        <v>1.203070236010932</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04727599759578675</v>
+        <v>0.05080757112136844</v>
       </c>
       <c r="W59">
-        <v>0.2055978397188293</v>
+        <v>0.1905978397188292</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3238082027108682</v>
+        <v>0.3479970624751263</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1610456095445476</v>
+        <v>0.1522847333640202</v>
       </c>
       <c r="C60">
-        <v>-10097.72392922101</v>
+        <v>-9274.929017758423</v>
       </c>
       <c r="D60">
-        <v>11461.29007077898</v>
+        <v>12284.08498224158</v>
       </c>
       <c r="E60">
         <v>10440.314</v>
@@ -6213,37 +6213,37 @@
         <v>1744.9</v>
       </c>
       <c r="M60">
-        <v>5483.2220612</v>
+        <v>5102.089851199999</v>
       </c>
       <c r="N60">
-        <v>-3738.3220612</v>
+        <v>-3357.189851199999</v>
       </c>
       <c r="O60">
-        <v>-545.7950209352</v>
+        <v>-490.1497182751999</v>
       </c>
       <c r="P60">
-        <v>-3192.5270402648</v>
+        <v>-2867.040132924799</v>
       </c>
       <c r="Q60">
-        <v>-398.6270402648001</v>
+        <v>-73.14013292479922</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09927819263051171</v>
+        <v>0.09913324934354176</v>
       </c>
       <c r="T60">
-        <v>1.234268150286947</v>
+        <v>1.231714765439764</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04646089418896285</v>
+        <v>0.04993157851582761</v>
       </c>
       <c r="W60">
-        <v>0.2057737390340219</v>
+        <v>0.1907737390340218</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3182253026641292</v>
+        <v>0.341997113122107</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1627456095445476</v>
+        <v>0.1538347333640202</v>
       </c>
       <c r="C61">
-        <v>-10683.11297265375</v>
+        <v>-9867.343594888785</v>
       </c>
       <c r="D61">
-        <v>11313.98402734625</v>
+        <v>12129.75340511121</v>
       </c>
       <c r="E61">
         <v>10878.397</v>
@@ -6295,37 +6295,37 @@
         <v>1744.9</v>
       </c>
       <c r="M61">
-        <v>5577.760372600001</v>
+        <v>5190.0569176</v>
       </c>
       <c r="N61">
-        <v>-3832.860372600001</v>
+        <v>-3445.1569176</v>
       </c>
       <c r="O61">
-        <v>-559.5976143996</v>
+        <v>-502.9929099696</v>
       </c>
       <c r="P61">
-        <v>-3273.262758200401</v>
+        <v>-2942.1640076304</v>
       </c>
       <c r="Q61">
-        <v>-479.3627582004005</v>
+        <v>-148.2640076303996</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1005825387922315</v>
+        <v>0.1004340603031403</v>
       </c>
       <c r="T61">
-        <v>1.264372251513458</v>
+        <v>1.261756588987075</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.04567342140609907</v>
+        <v>0.04908528057488137</v>
       </c>
       <c r="W61">
-        <v>0.2059436756605638</v>
+        <v>0.1909436756605638</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.312831653466432</v>
+        <v>0.3362005518827492</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1644456095445476</v>
+        <v>0.1553847333640202</v>
       </c>
       <c r="C62">
-        <v>-11264.76356740271</v>
+        <v>-10455.92838619619</v>
       </c>
       <c r="D62">
-        <v>11170.41643259729</v>
+        <v>11979.25161380381</v>
       </c>
       <c r="E62">
         <v>11316.48</v>
@@ -6377,37 +6377,37 @@
         <v>1744.9</v>
       </c>
       <c r="M62">
-        <v>5672.298684</v>
+        <v>5278.023984</v>
       </c>
       <c r="N62">
-        <v>-3927.398684</v>
+        <v>-3533.123984</v>
       </c>
       <c r="O62">
-        <v>-573.400207864</v>
+        <v>-515.836101664</v>
       </c>
       <c r="P62">
-        <v>-3353.998476136</v>
+        <v>-3017.287882336</v>
       </c>
       <c r="Q62">
-        <v>-560.098476136</v>
+        <v>-223.3878823360001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1019521022620373</v>
+        <v>0.1017999118107188</v>
       </c>
       <c r="T62">
-        <v>1.295981557801294</v>
+        <v>1.293300503711752</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04491219771599742</v>
+        <v>0.04826719256530002</v>
       </c>
       <c r="W62">
-        <v>0.2061079477328878</v>
+        <v>0.1911079477328878</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3076177925753248</v>
+        <v>0.33059720935137</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1661456095445476</v>
+        <v>0.1569347333640202</v>
       </c>
       <c r="C63">
-        <v>-11842.8162461323</v>
+        <v>-11040.82420055247</v>
       </c>
       <c r="D63">
-        <v>11030.4467538677</v>
+        <v>11832.43879944753</v>
       </c>
       <c r="E63">
         <v>11754.563</v>
@@ -6459,37 +6459,37 @@
         <v>1744.9</v>
       </c>
       <c r="M63">
-        <v>5766.836995400001</v>
+        <v>5365.991050400001</v>
       </c>
       <c r="N63">
-        <v>-4021.936995400001</v>
+        <v>-3621.091050400001</v>
       </c>
       <c r="O63">
-        <v>-587.2028013284</v>
+        <v>-528.6792933584001</v>
       </c>
       <c r="P63">
-        <v>-3434.734194071601</v>
+        <v>-3092.411757041601</v>
       </c>
       <c r="Q63">
-        <v>-640.8341940716005</v>
+        <v>-298.5117570416005</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1033918997559357</v>
+        <v>0.1032358069853527</v>
       </c>
       <c r="T63">
-        <v>1.329211854155174</v>
+        <v>1.326462055088976</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04417593217966959</v>
+        <v>0.04747592711340985</v>
       </c>
       <c r="W63">
-        <v>0.2062668338356273</v>
+        <v>0.1912668338356273</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3025748779429425</v>
+        <v>0.3251775829685606</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1678456095445476</v>
+        <v>0.1584847333640202</v>
       </c>
       <c r="C64">
-        <v>-12417.40458495857</v>
+        <v>-11622.16502761887</v>
       </c>
       <c r="D64">
-        <v>10893.94141504143</v>
+        <v>11689.18097238113</v>
       </c>
       <c r="E64">
         <v>12192.646</v>
@@ -6541,37 +6541,37 @@
         <v>1744.9</v>
       </c>
       <c r="M64">
-        <v>5861.375306800001</v>
+        <v>5453.9581168</v>
       </c>
       <c r="N64">
-        <v>-4116.475306800001</v>
+        <v>-3709.0581168</v>
       </c>
       <c r="O64">
-        <v>-601.0053947928001</v>
+        <v>-541.5224850528</v>
       </c>
       <c r="P64">
-        <v>-3515.469912007201</v>
+        <v>-3167.535631747201</v>
       </c>
       <c r="Q64">
-        <v>-721.5699120072009</v>
+        <v>-373.6356317472005</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1049074760653024</v>
+        <v>0.1047472755902304</v>
       </c>
       <c r="T64">
-        <v>1.364191113475047</v>
+        <v>1.361368951275528</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.04346341714451363</v>
+        <v>0.04671018635351615</v>
       </c>
       <c r="W64">
-        <v>0.206420594580214</v>
+        <v>0.191420594580214</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2976946379761207</v>
+        <v>0.3199327832432612</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1695456095445476</v>
+        <v>0.1600347333640202</v>
       </c>
       <c r="C65">
-        <v>-12988.65562863513</v>
+        <v>-12200.07844571596</v>
       </c>
       <c r="D65">
-        <v>10760.77337136488</v>
+        <v>11549.35055428405</v>
       </c>
       <c r="E65">
         <v>12630.729</v>
@@ -6623,37 +6623,37 @@
         <v>1744.9</v>
       </c>
       <c r="M65">
-        <v>5955.913618200001</v>
+        <v>5541.925183200001</v>
       </c>
       <c r="N65">
-        <v>-4211.013618200001</v>
+        <v>-3797.025183200001</v>
       </c>
       <c r="O65">
-        <v>-614.8079882572</v>
+        <v>-554.3656767472</v>
       </c>
       <c r="P65">
-        <v>-3596.2056299428</v>
+        <v>-3242.659506452801</v>
       </c>
       <c r="Q65">
-        <v>-802.3056299428004</v>
+        <v>-448.7595064528009</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1065049754184187</v>
+        <v>0.1063404452007771</v>
       </c>
       <c r="T65">
-        <v>1.401061143568967</v>
+        <v>1.398162706715407</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04277352163428325</v>
+        <v>0.04596875482409525</v>
       </c>
       <c r="W65">
-        <v>0.2065694740313217</v>
+        <v>0.1915694740313217</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2929693262622142</v>
+        <v>0.3148544850965428</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1712456095445476</v>
+        <v>0.1615847333640202</v>
       </c>
       <c r="C66">
-        <v>-13556.69028493055</v>
+        <v>-12774.68600076501</v>
       </c>
       <c r="D66">
-        <v>10630.82171506945</v>
+        <v>11412.82599923499</v>
       </c>
       <c r="E66">
         <v>13068.812</v>
@@ -6705,37 +6705,37 @@
         <v>1744.9</v>
       </c>
       <c r="M66">
-        <v>6050.451929600001</v>
+        <v>5629.8922496</v>
       </c>
       <c r="N66">
-        <v>-4305.5519296</v>
+        <v>-3884.9922496</v>
       </c>
       <c r="O66">
-        <v>-628.6105817215999</v>
+        <v>-567.2088684416</v>
       </c>
       <c r="P66">
-        <v>-3676.9413478784</v>
+        <v>-3317.783381158401</v>
       </c>
       <c r="Q66">
-        <v>-883.0413478784003</v>
+        <v>-523.8833811584004</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.108191224735597</v>
+        <v>0.1080221242341321</v>
       </c>
       <c r="T66">
-        <v>1.439979508668105</v>
+        <v>1.437000559679724</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.04210518535874758</v>
+        <v>0.04525049302996877</v>
       </c>
       <c r="W66">
-        <v>0.2067137009995823</v>
+        <v>0.1917137009995823</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.288391680539367</v>
+        <v>0.3099348837669094</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1729456095445476</v>
+        <v>0.1631347333640202</v>
       </c>
       <c r="C67">
-        <v>-14121.62369077093</v>
+        <v>-13346.10355866676</v>
       </c>
       <c r="D67">
-        <v>10503.97130922907</v>
+        <v>11279.49144133325</v>
       </c>
       <c r="E67">
         <v>13506.895</v>
@@ -6787,37 +6787,37 @@
         <v>1744.9</v>
       </c>
       <c r="M67">
-        <v>6144.990241000001</v>
+        <v>5717.859316000001</v>
       </c>
       <c r="N67">
-        <v>-4400.090241000002</v>
+        <v>-3972.959316000001</v>
       </c>
       <c r="O67">
-        <v>-642.4131751860002</v>
+        <v>-580.0520601360001</v>
       </c>
       <c r="P67">
-        <v>-3757.677065814001</v>
+        <v>-3392.907255864001</v>
       </c>
       <c r="Q67">
-        <v>-963.7770658140012</v>
+        <v>-599.0072558640009</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1099738311566141</v>
+        <v>0.1097998992122501</v>
       </c>
       <c r="T67">
-        <v>1.481121780344337</v>
+        <v>1.478057718527716</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0414574132763053</v>
+        <v>0.04455433159873847</v>
       </c>
       <c r="W67">
-        <v>0.2068534902149733</v>
+        <v>0.1918534902149733</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2839548854541458</v>
+        <v>0.30516665478588</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1746456095445476</v>
+        <v>0.1646847333640202</v>
       </c>
       <c r="C68">
-        <v>-14683.56555247777</v>
+        <v>-13914.44163326444</v>
       </c>
       <c r="D68">
-        <v>10380.11244752223</v>
+        <v>11149.23636673556</v>
       </c>
       <c r="E68">
         <v>13944.978</v>
@@ -6869,37 +6869,37 @@
         <v>1744.9</v>
       </c>
       <c r="M68">
-        <v>6239.528552400001</v>
+        <v>5805.826382400001</v>
       </c>
       <c r="N68">
-        <v>-4494.628552400001</v>
+        <v>-4060.9263824</v>
       </c>
       <c r="O68">
-        <v>-656.2157686504002</v>
+        <v>-592.8952518304001</v>
       </c>
       <c r="P68">
-        <v>-3838.412783749601</v>
+        <v>-3468.0311305696</v>
       </c>
       <c r="Q68">
-        <v>-1044.512783749601</v>
+        <v>-674.1311305696004</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1118612967788674</v>
+        <v>0.111682249189081</v>
       </c>
       <c r="T68">
-        <v>1.524684185648582</v>
+        <v>1.521530004366767</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.04082927065090675</v>
+        <v>0.04387926596845457</v>
       </c>
       <c r="W68">
-        <v>0.2069890433935343</v>
+        <v>0.1919890433935343</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2796525387048406</v>
+        <v>0.3005429175921546</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1763456095445476</v>
+        <v>0.1662347333640202</v>
       </c>
       <c r="C69">
-        <v>-15242.62046221483</v>
+        <v>-14479.80569184261</v>
       </c>
       <c r="D69">
-        <v>10259.14053778518</v>
+        <v>11021.95530815739</v>
       </c>
       <c r="E69">
         <v>14383.06100000001</v>
@@ -6951,37 +6951,37 @@
         <v>1744.9</v>
       </c>
       <c r="M69">
-        <v>6334.066863800002</v>
+        <v>5893.793448800001</v>
       </c>
       <c r="N69">
-        <v>-4589.166863800001</v>
+        <v>-4148.893448800001</v>
       </c>
       <c r="O69">
-        <v>-670.0183621148001</v>
+        <v>-605.7384435248001</v>
       </c>
       <c r="P69">
-        <v>-3919.148501685201</v>
+        <v>-3543.155005275201</v>
       </c>
       <c r="Q69">
-        <v>-1125.248501685201</v>
+        <v>-749.2550052752013</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1138631542570149</v>
+        <v>0.1136786809826895</v>
       </c>
       <c r="T69">
-        <v>1.570886736728842</v>
+        <v>1.567636974196063</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.04021987855163948</v>
+        <v>0.04322435155101494</v>
       </c>
       <c r="W69">
-        <v>0.2071205502085562</v>
+        <v>0.1921205502085562</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2754786202167088</v>
+        <v>0.2960572024042118</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1780456095445476</v>
+        <v>0.1677847333640202</v>
       </c>
       <c r="C70">
-        <v>-15798.88819256211</v>
+        <v>-15042.2964399364</v>
       </c>
       <c r="D70">
-        <v>10140.9558074379</v>
+        <v>10897.54756006361</v>
       </c>
       <c r="E70">
         <v>14821.144</v>
@@ -7033,37 +7033,37 @@
         <v>1744.9</v>
       </c>
       <c r="M70">
-        <v>6428.605175200001</v>
+        <v>5981.760515200001</v>
       </c>
       <c r="N70">
-        <v>-4683.705175200001</v>
+        <v>-4236.8605152</v>
       </c>
       <c r="O70">
-        <v>-683.8209555792</v>
+        <v>-618.5816352191999</v>
       </c>
       <c r="P70">
-        <v>-3999.884219620801</v>
+        <v>-3618.2788799808</v>
       </c>
       <c r="Q70">
-        <v>-1205.984219620801</v>
+        <v>-824.3788799807999</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1159901278275466</v>
+        <v>0.1157998897633986</v>
       </c>
       <c r="T70">
-        <v>1.619976947251618</v>
+        <v>1.61662562963969</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.03962840974940948</v>
+        <v>0.04258869932232354</v>
       </c>
       <c r="W70">
-        <v>0.2072481891760775</v>
+        <v>0.1922481891760774</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2714274640370513</v>
+        <v>0.2917034200159148</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1797456095445476</v>
+        <v>0.1693347333640202</v>
       </c>
       <c r="C71">
-        <v>-16352.46397096101</v>
+        <v>-15602.01008706771</v>
       </c>
       <c r="D71">
-        <v>10025.463029039</v>
+        <v>10775.91691293229</v>
       </c>
       <c r="E71">
         <v>15259.22700000001</v>
@@ -7115,37 +7115,37 @@
         <v>1744.9</v>
       </c>
       <c r="M71">
-        <v>6523.143486600002</v>
+        <v>6069.727581600001</v>
       </c>
       <c r="N71">
-        <v>-4778.243486600002</v>
+        <v>-4324.8275816</v>
       </c>
       <c r="O71">
-        <v>-697.6235490436003</v>
+        <v>-631.4248269136</v>
       </c>
       <c r="P71">
-        <v>-4080.619937556402</v>
+        <v>-3693.4027546864</v>
       </c>
       <c r="Q71">
-        <v>-1286.719937556402</v>
+        <v>-899.5027546864003</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.118254325499403</v>
+        <v>0.1180579507235082</v>
       </c>
       <c r="T71">
-        <v>1.672234268130703</v>
+        <v>1.668774843499035</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.03905408497043254</v>
+        <v>0.04197147179591305</v>
       </c>
       <c r="W71">
-        <v>0.2073721284633807</v>
+        <v>0.1923721284633806</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2674937326741954</v>
+        <v>0.2874758342185827</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1814456095445476</v>
+        <v>0.1708847333640202</v>
       </c>
       <c r="C72">
-        <v>-16903.43873561704</v>
+        <v>-16159.03859488221</v>
       </c>
       <c r="D72">
-        <v>9912.571264382959</v>
+        <v>10656.9714051178</v>
       </c>
       <c r="E72">
         <v>15697.31</v>
@@ -7197,37 +7197,37 @@
         <v>1744.9</v>
       </c>
       <c r="M72">
-        <v>6617.681798000001</v>
+        <v>6157.694648000002</v>
       </c>
       <c r="N72">
-        <v>-4872.781798000002</v>
+        <v>-4412.794648000001</v>
       </c>
       <c r="O72">
-        <v>-711.4261425080002</v>
+        <v>-644.2680186080001</v>
       </c>
       <c r="P72">
-        <v>-4161.355655492001</v>
+        <v>-3768.526629392001</v>
       </c>
       <c r="Q72">
-        <v>-1367.455655492001</v>
+        <v>-974.6266293920007</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1206694696827164</v>
+        <v>0.1204665490809585</v>
       </c>
       <c r="T72">
-        <v>1.727975410401726</v>
+        <v>1.724400671615669</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.03849616947085493</v>
+        <v>0.04137187934168572</v>
       </c>
       <c r="W72">
-        <v>0.2074925266281895</v>
+        <v>0.1924925266281895</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2636723936359926</v>
+        <v>0.2833690365868886</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1831456095445476</v>
+        <v>0.1724347333640202</v>
       </c>
       <c r="C73">
-        <v>-17451.89937430562</v>
+        <v>-16713.46990903186</v>
       </c>
       <c r="D73">
-        <v>9802.193625694385</v>
+        <v>10540.62309096814</v>
       </c>
       <c r="E73">
         <v>16135.393</v>
@@ -7279,37 +7279,37 @@
         <v>1744.9</v>
       </c>
       <c r="M73">
-        <v>6712.2201094</v>
+        <v>6245.6617144</v>
       </c>
       <c r="N73">
-        <v>-4967.3201094</v>
+        <v>-4500.7617144</v>
       </c>
       <c r="O73">
-        <v>-725.2287359723999</v>
+        <v>-657.1112103023999</v>
       </c>
       <c r="P73">
-        <v>-4242.0913734276</v>
+        <v>-3843.6505040976</v>
       </c>
       <c r="Q73">
-        <v>-1448.1913734276</v>
+        <v>-1049.7505040976</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1232511755338445</v>
+        <v>0.123041257669957</v>
       </c>
       <c r="T73">
-        <v>1.787560769381096</v>
+        <v>1.783862763740347</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0379539699008429</v>
+        <v>0.04078917681574649</v>
       </c>
       <c r="W73">
-        <v>0.2076095332953981</v>
+        <v>0.1926095332953981</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2599586979509788</v>
+        <v>0.279377923395524</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1848456095445476</v>
+        <v>0.1739847333640202</v>
       </c>
       <c r="C74">
-        <v>-17997.92894739857</v>
+        <v>-17265.38817603204</v>
       </c>
       <c r="D74">
-        <v>9694.247052601435</v>
+        <v>10426.78782396797</v>
       </c>
       <c r="E74">
         <v>16573.476</v>
@@ -7361,37 +7361,37 @@
         <v>1744.9</v>
       </c>
       <c r="M74">
-        <v>6806.758420800001</v>
+        <v>6333.628780800001</v>
       </c>
       <c r="N74">
-        <v>-5061.858420800001</v>
+        <v>-4588.7287808</v>
       </c>
       <c r="O74">
-        <v>-739.0313294368001</v>
+        <v>-669.9544019968</v>
       </c>
       <c r="P74">
-        <v>-4322.827091363201</v>
+        <v>-3918.7743788032</v>
       </c>
       <c r="Q74">
-        <v>-1528.927091363201</v>
+        <v>-1124.8743788032</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1260172889457676</v>
+        <v>0.1257998740153126</v>
       </c>
       <c r="T74">
-        <v>1.851402225430421</v>
+        <v>1.847572148159645</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.03742683142999785</v>
+        <v>0.04022266047108335</v>
       </c>
       <c r="W74">
-        <v>0.2077232897774065</v>
+        <v>0.1927232897774065</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2563481604794373</v>
+        <v>0.275497674459475</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1865456095445476</v>
+        <v>0.1755347333640202</v>
       </c>
       <c r="C75">
-        <v>-18541.60689631491</v>
+        <v>-17814.87394621677</v>
       </c>
       <c r="D75">
-        <v>9588.652103685092</v>
+        <v>10315.38505378323</v>
       </c>
       <c r="E75">
         <v>17011.559</v>
@@ -7443,37 +7443,37 @@
         <v>1744.9</v>
       </c>
       <c r="M75">
-        <v>6901.296732200001</v>
+        <v>6421.5958472</v>
       </c>
       <c r="N75">
-        <v>-5156.396732200001</v>
+        <v>-4676.695847200001</v>
       </c>
       <c r="O75">
-        <v>-752.8339229012</v>
+        <v>-682.7975936912001</v>
       </c>
       <c r="P75">
-        <v>-4403.562809298801</v>
+        <v>-3993.898253508801</v>
       </c>
       <c r="Q75">
-        <v>-1609.662809298801</v>
+        <v>-1199.998253508801</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1289882996474627</v>
+        <v>0.1287628323121761</v>
       </c>
       <c r="T75">
-        <v>1.91997267822414</v>
+        <v>1.916000746239632</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.03691413510903897</v>
+        <v>0.0396716651221644</v>
       </c>
       <c r="W75">
-        <v>0.2078339296434694</v>
+        <v>0.1928339296434694</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2528365418427327</v>
+        <v>0.2717237337134547</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1882456095445476</v>
+        <v>0.1770847333640202</v>
       </c>
       <c r="C76">
-        <v>-19083.00923849496</v>
+        <v>-18362.00436382101</v>
       </c>
       <c r="D76">
-        <v>9485.332761505048</v>
+        <v>10206.33763617899</v>
       </c>
       <c r="E76">
         <v>17449.642</v>
@@ -7525,37 +7525,37 @@
         <v>1744.9</v>
       </c>
       <c r="M76">
-        <v>6995.835043600001</v>
+        <v>6509.562913600001</v>
       </c>
       <c r="N76">
-        <v>-5250.9350436</v>
+        <v>-4764.662913600001</v>
       </c>
       <c r="O76">
-        <v>-766.6365163656</v>
+        <v>-695.6407853856001</v>
       </c>
       <c r="P76">
-        <v>-4484.2985272344</v>
+        <v>-4069.022128214401</v>
       </c>
       <c r="Q76">
-        <v>-1690.3985272344</v>
+        <v>-1275.122128214401</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1321878496339035</v>
+        <v>0.131953710478029</v>
       </c>
       <c r="T76">
-        <v>1.99381778123276</v>
+        <v>1.989693082633464</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03641529544540331</v>
+        <v>0.03913556153943245</v>
       </c>
       <c r="W76">
-        <v>0.207941579242882</v>
+        <v>0.192941579242882</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.249419831817831</v>
+        <v>0.2680517913659756</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1899456095445476</v>
+        <v>0.1786347333640202</v>
       </c>
       <c r="C77">
-        <v>-19622.20874990355</v>
+        <v>-18906.85334513243</v>
       </c>
       <c r="D77">
-        <v>9384.216250096457</v>
+        <v>10099.57165486758</v>
       </c>
       <c r="E77">
         <v>17887.72500000001</v>
@@ -7607,37 +7607,37 @@
         <v>1744.9</v>
       </c>
       <c r="M77">
-        <v>7090.373355000002</v>
+        <v>6597.529980000001</v>
       </c>
       <c r="N77">
-        <v>-5345.473355000002</v>
+        <v>-4852.629980000002</v>
       </c>
       <c r="O77">
-        <v>-780.4391098300002</v>
+        <v>-708.4839770800002</v>
       </c>
       <c r="P77">
-        <v>-4565.034245170002</v>
+        <v>-4144.146002920002</v>
       </c>
       <c r="Q77">
-        <v>-1771.134245170002</v>
+        <v>-1350.246002920002</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1356433636192597</v>
+        <v>0.1353998588971502</v>
       </c>
       <c r="T77">
-        <v>2.073570492482071</v>
+        <v>2.069280805938803</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.03592975817279793</v>
+        <v>0.03861375405224001</v>
       </c>
       <c r="W77">
-        <v>0.2080463581863102</v>
+        <v>0.1930463581863102</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2460942340602598</v>
+        <v>0.2644777674810959</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1916456095445476</v>
+        <v>0.1801847333640202</v>
       </c>
       <c r="C78">
-        <v>-20159.27513598318</v>
+        <v>-19449.49174557737</v>
       </c>
       <c r="D78">
-        <v>9285.232864016827</v>
+        <v>9995.016254422631</v>
       </c>
       <c r="E78">
         <v>18325.808</v>
@@ -7689,37 +7689,37 @@
         <v>1744.9</v>
       </c>
       <c r="M78">
-        <v>7184.911666400001</v>
+        <v>6685.497046400001</v>
       </c>
       <c r="N78">
-        <v>-5440.011666400002</v>
+        <v>-4940.5970464</v>
       </c>
       <c r="O78">
-        <v>-794.2417032944002</v>
+        <v>-721.3271687744</v>
       </c>
       <c r="P78">
-        <v>-4645.769963105601</v>
+        <v>-4219.2698776256</v>
       </c>
       <c r="Q78">
-        <v>-1851.869963105601</v>
+        <v>-1425.3698776256</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1393868371033955</v>
+        <v>0.1391331863511981</v>
       </c>
       <c r="T78">
-        <v>2.159969263002158</v>
+        <v>2.155500839519587</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03545699819684006</v>
+        <v>0.03810567834102633</v>
       </c>
       <c r="W78">
-        <v>0.208148379789122</v>
+        <v>0.1931483797891219</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2428561520331511</v>
+        <v>0.2609977968563448</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1933456095445476</v>
+        <v>0.1817347333640202</v>
       </c>
       <c r="C79">
-        <v>-20694.2751919009</v>
+        <v>-19989.98751653467</v>
       </c>
       <c r="D79">
-        <v>9188.315808099105</v>
+        <v>9892.603483465331</v>
       </c>
       <c r="E79">
         <v>18763.891</v>
@@ -7771,37 +7771,37 @@
         <v>1744.9</v>
       </c>
       <c r="M79">
-        <v>7279.449977800002</v>
+        <v>6773.464112800001</v>
       </c>
       <c r="N79">
-        <v>-5534.549977800001</v>
+        <v>-5028.564112800001</v>
       </c>
       <c r="O79">
-        <v>-808.0442967588001</v>
+        <v>-734.1703604688</v>
       </c>
       <c r="P79">
-        <v>-4726.505681041201</v>
+        <v>-4294.393752331201</v>
       </c>
       <c r="Q79">
-        <v>-1932.605681041201</v>
+        <v>-1500.493752331201</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1434558300209345</v>
+        <v>0.1431911509751632</v>
       </c>
       <c r="T79">
-        <v>2.253880970089208</v>
+        <v>2.249218267324786</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0349965177007772</v>
+        <v>0.03761079940153247</v>
       </c>
       <c r="W79">
-        <v>0.2082477514801723</v>
+        <v>0.1932477514801723</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2397021760327207</v>
+        <v>0.2576082150789897</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1950456095445476</v>
+        <v>0.1832847333640202</v>
       </c>
       <c r="C80">
-        <v>-21227.27295286322</v>
+        <v>-20528.40585260656</v>
       </c>
       <c r="D80">
-        <v>9093.401047136786</v>
+        <v>9792.268147393446</v>
       </c>
       <c r="E80">
         <v>19201.974</v>
@@ -7853,37 +7853,37 @@
         <v>1744.9</v>
       </c>
       <c r="M80">
-        <v>7373.988289200001</v>
+        <v>6861.431179200001</v>
       </c>
       <c r="N80">
-        <v>-5629.088289200001</v>
+        <v>-5116.531179200001</v>
       </c>
       <c r="O80">
-        <v>-821.8468902232</v>
+        <v>-747.0135521632001</v>
       </c>
       <c r="P80">
-        <v>-4807.241398976801</v>
+        <v>-4369.517627036801</v>
       </c>
       <c r="Q80">
-        <v>-2013.341398976801</v>
+        <v>-1575.617627036801</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1478947313855224</v>
+        <v>0.1476180214740343</v>
       </c>
       <c r="T80">
-        <v>2.356330105093263</v>
+        <v>2.351455461294094</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03454784439692109</v>
+        <v>0.0371286096656154</v>
       </c>
       <c r="W80">
-        <v>0.2083445751791445</v>
+        <v>0.1933445751791444</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2366290712117883</v>
+        <v>0.2543055456548999</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1967456095445476</v>
+        <v>0.1848347333640202</v>
       </c>
       <c r="C81">
-        <v>-21758.32983520973</v>
+        <v>-21064.80933001745</v>
       </c>
       <c r="D81">
-        <v>9000.42716479027</v>
+        <v>9693.947669982554</v>
       </c>
       <c r="E81">
         <v>19640.057</v>
@@ -7935,37 +7935,37 @@
         <v>1744.9</v>
       </c>
       <c r="M81">
-        <v>7468.526600600001</v>
+        <v>6949.3982456</v>
       </c>
       <c r="N81">
-        <v>-5723.626600600001</v>
+        <v>-5204.4982456</v>
       </c>
       <c r="O81">
-        <v>-835.6494836876001</v>
+        <v>-759.8567438575999</v>
       </c>
       <c r="P81">
-        <v>-4887.977116912401</v>
+        <v>-4444.6415017424</v>
       </c>
       <c r="Q81">
-        <v>-2094.0771169124</v>
+        <v>-1650.7415017424</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1527563852610234</v>
+        <v>0.1524664986870835</v>
       </c>
       <c r="T81">
-        <v>2.468536300573895</v>
+        <v>2.463429530879528</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.03411052991088411</v>
+        <v>0.03665862726478483</v>
       </c>
       <c r="W81">
-        <v>0.2084389476452312</v>
+        <v>0.1934389476452312</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.233633766512905</v>
+        <v>0.2510864881149646</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1984456095445476</v>
+        <v>0.1863847333640202</v>
       </c>
       <c r="C82">
-        <v>-22287.50476893888</v>
+        <v>-21599.25803675796</v>
       </c>
       <c r="D82">
-        <v>8909.335231061123</v>
+        <v>9597.581963242048</v>
       </c>
       <c r="E82">
         <v>20078.14000000001</v>
@@ -8017,37 +8017,37 @@
         <v>1744.9</v>
       </c>
       <c r="M82">
-        <v>7563.064912000003</v>
+        <v>7037.365312000002</v>
       </c>
       <c r="N82">
-        <v>-5818.164912000002</v>
+        <v>-5292.465312000002</v>
       </c>
       <c r="O82">
-        <v>-849.4520771520002</v>
+        <v>-772.6999355520003</v>
       </c>
       <c r="P82">
-        <v>-4968.712834848002</v>
+        <v>-4519.765376448002</v>
       </c>
       <c r="Q82">
-        <v>-2174.812834848002</v>
+        <v>-1725.865376448002</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1581042045240746</v>
+        <v>0.1577998236214377</v>
       </c>
       <c r="T82">
-        <v>2.59196311560259</v>
+        <v>2.586601007423504</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03368414828699805</v>
+        <v>0.036200394423975</v>
       </c>
       <c r="W82">
-        <v>0.2085309607996658</v>
+        <v>0.1935309607996658</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2307133444314936</v>
+        <v>0.2479479070135274</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2001456095445476</v>
+        <v>0.1879347333640202</v>
       </c>
       <c r="C83">
-        <v>-22814.85432226667</v>
+        <v>-22131.80969504286</v>
       </c>
       <c r="D83">
-        <v>8820.068677733334</v>
+        <v>9503.113304957145</v>
       </c>
       <c r="E83">
         <v>20516.22300000001</v>
@@ -8099,37 +8099,37 @@
         <v>1744.9</v>
       </c>
       <c r="M83">
-        <v>7657.603223400002</v>
+        <v>7125.332378400001</v>
       </c>
       <c r="N83">
-        <v>-5912.703223400002</v>
+        <v>-5380.432378400001</v>
       </c>
       <c r="O83">
-        <v>-863.2546706164002</v>
+        <v>-785.5431272464001</v>
       </c>
       <c r="P83">
-        <v>-5049.448552783601</v>
+        <v>-4594.889251153601</v>
       </c>
       <c r="Q83">
-        <v>-2255.548552783601</v>
+        <v>-1800.9892511536</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1640149521306049</v>
+        <v>0.1636945511804608</v>
       </c>
       <c r="T83">
-        <v>2.728382226950095</v>
+        <v>2.722737902551057</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03326829460444253</v>
+        <v>0.0357534759742963</v>
       </c>
       <c r="W83">
-        <v>0.2086207020243613</v>
+        <v>0.1936207020243613</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2278650315372777</v>
+        <v>0.2448868217417556</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2018456095445476</v>
+        <v>0.1894847333640202</v>
       </c>
       <c r="C84">
-        <v>-23340.43281877164</v>
+        <v>-22662.5197766075</v>
       </c>
       <c r="D84">
-        <v>8732.573181228365</v>
+        <v>9410.486223392509</v>
       </c>
       <c r="E84">
         <v>20954.306</v>
@@ -8181,37 +8181,37 @@
         <v>1744.9</v>
       </c>
       <c r="M84">
-        <v>7752.141534800002</v>
+        <v>7213.299444800001</v>
       </c>
       <c r="N84">
-        <v>-6007.241534800001</v>
+        <v>-5468.399444800001</v>
       </c>
       <c r="O84">
-        <v>-877.0572640808001</v>
+        <v>-798.3863189408002</v>
       </c>
       <c r="P84">
-        <v>-5130.184270719201</v>
+        <v>-4670.013125859201</v>
       </c>
       <c r="Q84">
-        <v>-2336.284270719201</v>
+        <v>-1876.113125859201</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1705824494711941</v>
+        <v>0.1702442484682641</v>
       </c>
       <c r="T84">
-        <v>2.879959017336211</v>
+        <v>2.874001119359449</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03286258369463226</v>
+        <v>0.03531745797460977</v>
       </c>
       <c r="W84">
-        <v>0.2087082544386984</v>
+        <v>0.1937082544386984</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2250861896892621</v>
+        <v>0.2419003970863682</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2035456095445476</v>
+        <v>0.1910347333640202</v>
       </c>
       <c r="C85">
-        <v>-23864.29244763583</v>
+        <v>-23191.44161132642</v>
       </c>
       <c r="D85">
-        <v>8646.796552364174</v>
+        <v>9319.64738867358</v>
       </c>
       <c r="E85">
         <v>21392.389</v>
@@ -8263,37 +8263,37 @@
         <v>1744.9</v>
       </c>
       <c r="M85">
-        <v>7846.679846200002</v>
+        <v>7301.2665112</v>
       </c>
       <c r="N85">
-        <v>-6101.779846200001</v>
+        <v>-5556.3665112</v>
       </c>
       <c r="O85">
-        <v>-890.8598575452</v>
+        <v>-811.2295106352</v>
       </c>
       <c r="P85">
-        <v>-5210.919988654801</v>
+        <v>-4745.1370005648</v>
       </c>
       <c r="Q85">
-        <v>-2417.019988654801</v>
+        <v>-1951.237000564799</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1779225935577349</v>
+        <v>0.1775644983781621</v>
       </c>
       <c r="T85">
-        <v>3.049368371297164</v>
+        <v>3.043060008733535</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03246664895132343</v>
+        <v>0.034891946432747</v>
       </c>
       <c r="W85">
-        <v>0.2087936971563044</v>
+        <v>0.1937936971563044</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2223743078857771</v>
+        <v>0.2389859344708699</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2052456095445476</v>
+        <v>0.1925847333640202</v>
       </c>
       <c r="C86">
-        <v>-24386.48336745178</v>
+        <v>-23718.62648960135</v>
       </c>
       <c r="D86">
-        <v>8562.688632548225</v>
+        <v>9230.54551039865</v>
       </c>
       <c r="E86">
         <v>21830.472</v>
@@ -8345,37 +8345,37 @@
         <v>1744.9</v>
       </c>
       <c r="M86">
-        <v>7941.218157600001</v>
+        <v>7389.233577600001</v>
       </c>
       <c r="N86">
-        <v>-6196.318157600001</v>
+        <v>-5644.3335776</v>
       </c>
       <c r="O86">
-        <v>-904.6624510096001</v>
+        <v>-824.0727023296</v>
       </c>
       <c r="P86">
-        <v>-5291.655706590401</v>
+        <v>-4820.2608752704</v>
       </c>
       <c r="Q86">
-        <v>-2497.755706590401</v>
+        <v>-2026.3608752704</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1861802556550932</v>
+        <v>0.1857997795267971</v>
       </c>
       <c r="T86">
-        <v>3.239953894503236</v>
+        <v>3.233251259279379</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03208014122571244</v>
+        <v>0.03447656611807143</v>
       </c>
       <c r="W86">
-        <v>0.2088771055234913</v>
+        <v>0.1938771055234912</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2197269946966607</v>
+        <v>0.2361408638224072</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2069456095445476</v>
+        <v>0.1941347333640202</v>
       </c>
       <c r="C87">
-        <v>-24907.05380402953</v>
+        <v>-24244.12375893128</v>
       </c>
       <c r="D87">
-        <v>8480.201195970476</v>
+        <v>9143.131241068719</v>
       </c>
       <c r="E87">
         <v>22268.555</v>
@@ -8427,37 +8427,37 @@
         <v>1744.9</v>
       </c>
       <c r="M87">
-        <v>8035.756469000001</v>
+        <v>7477.200644</v>
       </c>
       <c r="N87">
-        <v>-6290.856469</v>
+        <v>-5732.300644000001</v>
       </c>
       <c r="O87">
-        <v>-918.465044474</v>
+        <v>-836.9158940240001</v>
       </c>
       <c r="P87">
-        <v>-5372.391424526</v>
+        <v>-4895.384749976</v>
       </c>
       <c r="Q87">
-        <v>-2578.491424526</v>
+        <v>-2101.484749976</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1955389393654328</v>
+        <v>0.1951330981619169</v>
       </c>
       <c r="T87">
-        <v>3.455950820803452</v>
+        <v>3.448801343231338</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03170272779952759</v>
+        <v>0.03407095945785884</v>
       </c>
       <c r="W87">
-        <v>0.208958551340862</v>
+        <v>0.193958551340862</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2171419712296411</v>
+        <v>0.2333627360127317</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2086456095445476</v>
+        <v>0.1956847333640202</v>
       </c>
       <c r="C88">
-        <v>-25426.05014260423</v>
+        <v>-24767.98091504691</v>
       </c>
       <c r="D88">
-        <v>8399.287857395768</v>
+        <v>9057.357084953086</v>
       </c>
       <c r="E88">
         <v>22706.638</v>
@@ -8509,37 +8509,37 @@
         <v>1744.9</v>
       </c>
       <c r="M88">
-        <v>8130.2947804</v>
+        <v>7565.1677104</v>
       </c>
       <c r="N88">
-        <v>-6385.3947804</v>
+        <v>-5820.267710399999</v>
       </c>
       <c r="O88">
-        <v>-932.2676379384</v>
+        <v>-849.7590857183999</v>
       </c>
       <c r="P88">
-        <v>-5453.1271424616</v>
+        <v>-4970.5086246816</v>
       </c>
       <c r="Q88">
-        <v>-2659.2271424616</v>
+        <v>-2176.6086246816</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2062345778915352</v>
+        <v>0.2057997480306253</v>
       </c>
       <c r="T88">
-        <v>3.702804450860841</v>
+        <v>3.69514429631929</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03133409142976564</v>
+        <v>0.03367478551067443</v>
       </c>
       <c r="W88">
-        <v>0.2090381030694566</v>
+        <v>0.1940381030694566</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.214617064587436</v>
+        <v>0.2306492158265373</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2103456095445476</v>
+        <v>0.1972347333640202</v>
       </c>
       <c r="C89">
-        <v>-25943.51701481498</v>
+        <v>-25290.24368796309</v>
       </c>
       <c r="D89">
-        <v>8319.903985185025</v>
+        <v>8973.177312036914</v>
       </c>
       <c r="E89">
         <v>23144.72100000001</v>
@@ -8591,37 +8591,37 @@
         <v>1744.9</v>
       </c>
       <c r="M89">
-        <v>8224.833091800001</v>
+        <v>7653.134776800001</v>
       </c>
       <c r="N89">
-        <v>-6479.933091800001</v>
+        <v>-5908.234776800002</v>
       </c>
       <c r="O89">
-        <v>-946.0702314028001</v>
+        <v>-862.6022774128002</v>
       </c>
       <c r="P89">
-        <v>-5533.862860397201</v>
+        <v>-5045.632499387201</v>
       </c>
       <c r="Q89">
-        <v>-2739.962860397201</v>
+        <v>-2251.732499387201</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2185756992678071</v>
+        <v>0.218107420956058</v>
       </c>
       <c r="T89">
-        <v>3.987635562465521</v>
+        <v>3.979386165266928</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03097392945930856</v>
+        <v>0.03328771901055173</v>
       </c>
       <c r="W89">
-        <v>0.2091158260226812</v>
+        <v>0.1941158260226812</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.212150201776086</v>
+        <v>0.2279980754147378</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2120456095445476</v>
+        <v>0.1987847333640202</v>
       </c>
       <c r="C90">
-        <v>-26459.49738079736</v>
+        <v>-25810.95612327665</v>
       </c>
       <c r="D90">
-        <v>8242.006619202644</v>
+        <v>8890.547876723354</v>
       </c>
       <c r="E90">
         <v>23582.804</v>
@@ -8673,37 +8673,37 @@
         <v>1744.9</v>
       </c>
       <c r="M90">
-        <v>8319.371403200001</v>
+        <v>7741.101843200001</v>
       </c>
       <c r="N90">
-        <v>-6574.471403200001</v>
+        <v>-5996.2018432</v>
       </c>
       <c r="O90">
-        <v>-959.8728248672001</v>
+        <v>-875.4454691072</v>
       </c>
       <c r="P90">
-        <v>-5614.598578332801</v>
+        <v>-5120.756374092801</v>
       </c>
       <c r="Q90">
-        <v>-2820.698578332801</v>
+        <v>-2326.856374092801</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2329736742067911</v>
+        <v>0.2324663727023962</v>
       </c>
       <c r="T90">
-        <v>4.319938526004316</v>
+        <v>4.311001679039173</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03062195298818006</v>
+        <v>0.03290944947634092</v>
       </c>
       <c r="W90">
-        <v>0.2091917825451508</v>
+        <v>0.1941917825451508</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2097394040286304</v>
+        <v>0.225407188194116</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2137456095445476</v>
+        <v>0.2003347333640202</v>
       </c>
       <c r="C91">
-        <v>-26974.03260670717</v>
+        <v>-26330.16065901356</v>
       </c>
       <c r="D91">
-        <v>8165.554393292829</v>
+        <v>8809.426340986438</v>
       </c>
       <c r="E91">
         <v>24020.887</v>
@@ -8755,37 +8755,37 @@
         <v>1744.9</v>
       </c>
       <c r="M91">
-        <v>8413.909714600002</v>
+        <v>7829.068909600001</v>
       </c>
       <c r="N91">
-        <v>-6669.009714600003</v>
+        <v>-6084.168909600001</v>
       </c>
       <c r="O91">
-        <v>-973.6754183316003</v>
+        <v>-888.2886608016</v>
       </c>
       <c r="P91">
-        <v>-5695.334296268402</v>
+        <v>-5195.880248798401</v>
       </c>
       <c r="Q91">
-        <v>-2901.434296268402</v>
+        <v>-2401.980248798401</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2499894627710448</v>
+        <v>0.2494360429480685</v>
       </c>
       <c r="T91">
-        <v>4.712660210186526</v>
+        <v>4.702910922588188</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.03027788610067241</v>
+        <v>0.03253968038110114</v>
       </c>
       <c r="W91">
-        <v>0.2092660321794749</v>
+        <v>0.1942660321794749</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2073827815114548</v>
+        <v>0.2228745231582269</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2154456095445476</v>
+        <v>0.2018847333640202</v>
       </c>
       <c r="C92">
-        <v>-27487.16253796917</v>
+        <v>-26847.89819830695</v>
       </c>
       <c r="D92">
-        <v>8090.50746203083</v>
+        <v>8729.771801693054</v>
       </c>
       <c r="E92">
         <v>24458.97</v>
@@ -8837,37 +8837,37 @@
         <v>1744.9</v>
       </c>
       <c r="M92">
-        <v>8508.448026000002</v>
+        <v>7917.035976</v>
       </c>
       <c r="N92">
-        <v>-6763.548026000002</v>
+        <v>-6172.135976</v>
       </c>
       <c r="O92">
-        <v>-987.4780117960003</v>
+        <v>-901.1318524959999</v>
       </c>
       <c r="P92">
-        <v>-5776.070014204002</v>
+        <v>-5271.004123504</v>
       </c>
       <c r="Q92">
-        <v>-2982.170014204002</v>
+        <v>-2477.104123504</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2704084090481493</v>
+        <v>0.2697996472428754</v>
       </c>
       <c r="T92">
-        <v>5.183926231205179</v>
+        <v>5.173202014847008</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.02994146514399828</v>
+        <v>0.03217812837686668</v>
       </c>
       <c r="W92">
-        <v>0.2093386318219252</v>
+        <v>0.1943386318219252</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2050785283835498</v>
+        <v>0.22039813956758</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2171456095445476</v>
+        <v>0.2034347333640202</v>
       </c>
       <c r="C93">
-        <v>-27998.92556852332</v>
+        <v>-27364.20817816748</v>
       </c>
       <c r="D93">
-        <v>8016.827431476684</v>
+        <v>8651.544821832527</v>
       </c>
       <c r="E93">
         <v>24897.05300000001</v>
@@ -8919,37 +8919,37 @@
         <v>1744.9</v>
       </c>
       <c r="M93">
-        <v>8602.986337400002</v>
+        <v>8005.003042400002</v>
       </c>
       <c r="N93">
-        <v>-6858.086337400002</v>
+        <v>-6260.103042400002</v>
       </c>
       <c r="O93">
-        <v>-1001.2806052604</v>
+        <v>-913.9750441904002</v>
       </c>
       <c r="P93">
-        <v>-5856.805732139602</v>
+        <v>-5346.127998209602</v>
       </c>
       <c r="Q93">
-        <v>-3062.905732139602</v>
+        <v>-2552.227998209602</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2953648989423881</v>
+        <v>0.2946884969365283</v>
       </c>
       <c r="T93">
-        <v>5.759918034672421</v>
+        <v>5.748002238718898</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.02961243805450379</v>
+        <v>0.03182452257052748</v>
       </c>
       <c r="W93">
-        <v>0.2094096358678381</v>
+        <v>0.1944096358678381</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2028249181815328</v>
+        <v>0.2179761819899142</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2188456095445476</v>
+        <v>0.2049847333640202</v>
       </c>
       <c r="C94">
-        <v>-28509.35870632148</v>
+        <v>-27879.12863458917</v>
       </c>
       <c r="D94">
-        <v>7944.477293678529</v>
+        <v>8574.707365410834</v>
       </c>
       <c r="E94">
         <v>25335.13600000001</v>
@@ -9001,37 +9001,37 @@
         <v>1744.9</v>
       </c>
       <c r="M94">
-        <v>8697.524648800001</v>
+        <v>8092.970108800001</v>
       </c>
       <c r="N94">
-        <v>-6952.624648800002</v>
+        <v>-6348.070108800001</v>
       </c>
       <c r="O94">
-        <v>-1015.0831987248</v>
+        <v>-926.8182358848001</v>
       </c>
       <c r="P94">
-        <v>-5937.541450075201</v>
+        <v>-5421.251872915201</v>
       </c>
       <c r="Q94">
-        <v>-3143.641450075201</v>
+        <v>-2627.351872915201</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3265605113101867</v>
+        <v>0.3257995590535944</v>
       </c>
       <c r="T94">
-        <v>6.479907789006475</v>
+        <v>6.466502518558761</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.0292905637278244</v>
+        <v>0.03147860384693479</v>
       </c>
       <c r="W94">
-        <v>0.2094790963475355</v>
+        <v>0.1944790963475355</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2006202995056465</v>
+        <v>0.215606875663937</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2485215275153934</v>
+        <v>0.2065347333640202</v>
       </c>
       <c r="C95">
-        <v>-30028.67951006247</v>
+        <v>-28392.69626421635</v>
       </c>
       <c r="D95">
-        <v>6863.239489937535</v>
+        <v>8499.222735783651</v>
       </c>
       <c r="E95">
         <v>25773.219</v>
@@ -9083,45 +9083,45 @@
         <v>1744.9</v>
       </c>
       <c r="M95">
-        <v>10014.3145302</v>
+        <v>8180.937175200002</v>
       </c>
       <c r="N95">
-        <v>-8269.414530200002</v>
+        <v>-6436.037175200001</v>
       </c>
       <c r="O95">
-        <v>-1207.3345214092</v>
+        <v>-939.6614275792001</v>
       </c>
       <c r="P95">
-        <v>-7062.080008790801</v>
+        <v>-5496.375747620801</v>
       </c>
       <c r="Q95">
-        <v>-4268.180008790801</v>
+        <v>-2702.475747620801</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3677536982237247</v>
+        <v>0.3657994960612507</v>
       </c>
       <c r="T95">
-        <v>7.430639968148757</v>
+        <v>7.390288592638585</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.02543912508756724</v>
+        <v>0.03114012423567743</v>
       </c>
       <c r="W95">
-        <v>0.239547063053476</v>
+        <v>0.194547063053476</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.1742405827915564</v>
+        <v>0.2132885221621742</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2505215275153934</v>
+        <v>0.2080847333640202</v>
       </c>
       <c r="C96">
-        <v>-30529.14253269657</v>
+        <v>-28904.94648278186</v>
       </c>
       <c r="D96">
-        <v>6800.859467303438</v>
+        <v>8425.055517218147</v>
       </c>
       <c r="E96">
         <v>26211.302</v>
@@ -9165,45 +9165,45 @@
         <v>1744.9</v>
       </c>
       <c r="M96">
-        <v>10121.9953316</v>
+        <v>8268.904241600001</v>
       </c>
       <c r="N96">
-        <v>-8377.095331600001</v>
+        <v>-6524.004241600001</v>
       </c>
       <c r="O96">
-        <v>-1223.0559184136</v>
+        <v>-952.5046192736002</v>
       </c>
       <c r="P96">
-        <v>-7154.039413186401</v>
+        <v>-5571.499622326402</v>
       </c>
       <c r="Q96">
-        <v>-4360.139413186402</v>
+        <v>-2777.599622326401</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4214126479276789</v>
+        <v>0.4191327454047926</v>
       </c>
       <c r="T96">
-        <v>8.669079962840216</v>
+        <v>8.622003358078352</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.02516849609727397</v>
+        <v>0.0308088463182766</v>
       </c>
       <c r="W96">
-        <v>0.2396135836592901</v>
+        <v>0.19461358365929</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.1723869595703696</v>
+        <v>0.2110194953306617</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2525215275153934</v>
+        <v>0.2096347333640202</v>
       </c>
       <c r="C97">
-        <v>-31028.48182417081</v>
+        <v>-29415.91348051196</v>
       </c>
       <c r="D97">
-        <v>6739.603175829206</v>
+        <v>8352.171519488045</v>
       </c>
       <c r="E97">
         <v>26649.38500000001</v>
@@ -9247,45 +9247,45 @@
         <v>1744.9</v>
       </c>
       <c r="M97">
-        <v>10229.676133</v>
+        <v>8356.871308000002</v>
       </c>
       <c r="N97">
-        <v>-8484.776133000003</v>
+        <v>-6611.971308000002</v>
       </c>
       <c r="O97">
-        <v>-1238.777315418</v>
+        <v>-965.3478109680002</v>
       </c>
       <c r="P97">
-        <v>-7245.998817582003</v>
+        <v>-5646.623497032002</v>
       </c>
       <c r="Q97">
-        <v>-4452.098817582002</v>
+        <v>-2852.723497032002</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.496535177513215</v>
+        <v>0.4937992944857514</v>
       </c>
       <c r="T97">
-        <v>10.40289595540827</v>
+        <v>10.34640402969403</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.02490356455940793</v>
+        <v>0.03048454267282106</v>
       </c>
       <c r="W97">
-        <v>0.2396787038312976</v>
+        <v>0.1946787038312975</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.1705723599959447</v>
+        <v>0.2087982374850758</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2545215275153934</v>
+        <v>0.2111847333640202</v>
       </c>
       <c r="C98">
-        <v>-31526.72747823724</v>
+        <v>-29925.63027468017</v>
       </c>
       <c r="D98">
-        <v>6679.440521762759</v>
+        <v>8280.537725319826</v>
       </c>
       <c r="E98">
         <v>27087.468</v>
@@ -9329,45 +9329,45 @@
         <v>1744.9</v>
       </c>
       <c r="M98">
-        <v>10337.3569344</v>
+        <v>8444.8383744</v>
       </c>
       <c r="N98">
-        <v>-8592.456934400001</v>
+        <v>-6699.938374400001</v>
       </c>
       <c r="O98">
-        <v>-1254.4987124224</v>
+        <v>-978.1910026624</v>
       </c>
       <c r="P98">
-        <v>-7337.958221977601</v>
+        <v>-5721.747371737601</v>
       </c>
       <c r="Q98">
-        <v>-4544.058221977601</v>
+        <v>-2927.8473717376</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6092189718915173</v>
+        <v>0.605799118107188</v>
       </c>
       <c r="T98">
-        <v>13.0036199442603</v>
+        <v>12.93300503711751</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.02464415242858077</v>
+        <v>0.03016699535331251</v>
       </c>
       <c r="W98">
-        <v>0.2397424673330549</v>
+        <v>0.1947424673330549</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.1687955645793203</v>
+        <v>0.2066232558446062</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2565215275153934</v>
+        <v>0.2127347333640202</v>
       </c>
       <c r="C99">
-        <v>-32023.90852359954</v>
+        <v>-30434.12875947967</v>
       </c>
       <c r="D99">
-        <v>6620.342476400459</v>
+        <v>8210.122240520324</v>
       </c>
       <c r="E99">
         <v>27525.551</v>
@@ -9411,45 +9411,45 @@
         <v>1744.9</v>
       </c>
       <c r="M99">
-        <v>10445.0377358</v>
+        <v>8532.805440800001</v>
       </c>
       <c r="N99">
-        <v>-8700.137735800001</v>
+        <v>-6787.905440800001</v>
       </c>
       <c r="O99">
-        <v>-1270.2201094268</v>
+        <v>-991.0341943568001</v>
       </c>
       <c r="P99">
-        <v>-7429.917626373201</v>
+        <v>-5796.871246443201</v>
       </c>
       <c r="Q99">
-        <v>-4636.017626373201</v>
+        <v>-3002.971246443201</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7970252958553565</v>
+        <v>0.7924654908095842</v>
       </c>
       <c r="T99">
-        <v>17.33815992568041</v>
+        <v>17.24400671615668</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.024390089001482</v>
+        <v>0.02985599540121651</v>
       </c>
       <c r="W99">
-        <v>0.2398049161234357</v>
+        <v>0.1948049161234357</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.1670554041197396</v>
+        <v>0.2044931191864143</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2585215275153934</v>
+        <v>0.2142847333640202</v>
       </c>
       <c r="C100">
-        <v>-32520.05297061613</v>
+        <v>-30941.43975337251</v>
       </c>
       <c r="D100">
-        <v>6562.281029383878</v>
+        <v>8140.894246627498</v>
       </c>
       <c r="E100">
         <v>27963.63400000001</v>
@@ -9493,45 +9493,45 @@
         <v>1744.9</v>
       </c>
       <c r="M100">
-        <v>10552.7185372</v>
+        <v>8620.772507200001</v>
       </c>
       <c r="N100">
-        <v>-8807.818537200003</v>
+        <v>-6875.872507200002</v>
       </c>
       <c r="O100">
-        <v>-1285.9415064312</v>
+        <v>-1003.8773860512</v>
       </c>
       <c r="P100">
-        <v>-7521.877030768803</v>
+        <v>-5871.995121148801</v>
       </c>
       <c r="Q100">
-        <v>-4727.977030768803</v>
+        <v>-3078.095121148801</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.172637943783035</v>
+        <v>1.165798236214376</v>
       </c>
       <c r="T100">
-        <v>26.00723988852061</v>
+        <v>25.86601007423501</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.02414121054228319</v>
+        <v>0.02955134238691837</v>
       </c>
       <c r="W100">
-        <v>0.2398660904487068</v>
+        <v>0.1948660904487068</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.165350757138926</v>
+        <v>0.2024064547049204</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2605215275153934</v>
+        <v>0.2158347333640202</v>
       </c>
       <c r="C101">
-        <v>-33015.18785556717</v>
+        <v>-31447.59304406334</v>
       </c>
       <c r="D101">
-        <v>6505.229144432828</v>
+        <v>8072.823955936668</v>
       </c>
       <c r="E101">
         <v>28401.717</v>
@@ -9575,45 +9575,45 @@
         <v>1744.9</v>
       </c>
       <c r="M101">
-        <v>10660.3993386</v>
+        <v>8708.739573600002</v>
       </c>
       <c r="N101">
-        <v>-8915.499338600002</v>
+        <v>-6963.839573600002</v>
       </c>
       <c r="O101">
-        <v>-1301.6629034356</v>
+        <v>-1016.7205777456</v>
       </c>
       <c r="P101">
-        <v>-7613.836435164402</v>
+        <v>-5947.118995854402</v>
       </c>
       <c r="Q101">
-        <v>-4819.936435164402</v>
+        <v>-3153.218995854402</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.299475887566069</v>
+        <v>2.285796472428752</v>
       </c>
       <c r="T101">
-        <v>52.01447977704122</v>
+        <v>51.73202014847003</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.02389735993074498</v>
+        <v>0.0292528439789697</v>
       </c>
       <c r="W101">
-        <v>0.2399260289290229</v>
+        <v>0.1949260289290229</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.163680547470856</v>
+        <v>0.2003619450614363</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06886802191789448</v>
+        <v>0.06880590460589436</v>
       </c>
       <c r="C2">
-        <v>42814.43946562433</v>
+        <v>42439.47912356703</v>
       </c>
       <c r="D2">
-        <v>38964.63946562433</v>
+        <v>39027.76212356702</v>
       </c>
       <c r="E2">
-        <v>-14968.5</v>
+        <v>-14530.417</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>438.083</v>
       </c>
       <c r="G2">
         <v>3849.8</v>
@@ -1457,28 +1457,28 @@
         <v>1744.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>22.0355749</v>
       </c>
       <c r="N2">
-        <v>1744.9</v>
+        <v>1722.8644251</v>
       </c>
       <c r="O2">
-        <v>254.7554</v>
+        <v>251.5382060646</v>
       </c>
       <c r="P2">
-        <v>1490.1446</v>
+        <v>1471.3262190354</v>
       </c>
       <c r="Q2">
-        <v>4284.0446</v>
+        <v>4265.2262190354</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06886802191789448</v>
+        <v>0.06906701273322663</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5373444049244024</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>79.18559002515519</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06880590460589436</v>
+        <v>0.06874378729389423</v>
       </c>
       <c r="C3">
-        <v>42439.47912356703</v>
+        <v>42064.72363058879</v>
       </c>
       <c r="D3">
-        <v>39027.76212356702</v>
+        <v>39091.08963058878</v>
       </c>
       <c r="E3">
-        <v>-14530.417</v>
+        <v>-14092.334</v>
       </c>
       <c r="F3">
-        <v>438.083</v>
+        <v>876.1660000000001</v>
       </c>
       <c r="G3">
         <v>3849.8</v>
@@ -1539,28 +1539,28 @@
         <v>1744.9</v>
       </c>
       <c r="M3">
-        <v>22.0355749</v>
+        <v>44.0711498</v>
       </c>
       <c r="N3">
-        <v>1722.8644251</v>
+        <v>1700.8288502</v>
       </c>
       <c r="O3">
-        <v>251.5382060646</v>
+        <v>248.3210121292</v>
       </c>
       <c r="P3">
-        <v>1471.3262190354</v>
+        <v>1452.5078380708</v>
       </c>
       <c r="Q3">
-        <v>4265.2262190354</v>
+        <v>4246.4078380708</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06906701273322663</v>
+        <v>0.06927006458560636</v>
       </c>
       <c r="T3">
-        <v>0.5373444049244024</v>
+        <v>0.5420338241479529</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.18559002515519</v>
+        <v>39.5927950125776</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06874378729389423</v>
+        <v>0.06868166998189409</v>
       </c>
       <c r="C4">
-        <v>42064.72363058879</v>
+        <v>41690.1739854913</v>
       </c>
       <c r="D4">
-        <v>39091.08963058878</v>
+        <v>39154.6229854913</v>
       </c>
       <c r="E4">
-        <v>-14092.334</v>
+        <v>-13654.251</v>
       </c>
       <c r="F4">
-        <v>876.1660000000001</v>
+        <v>1314.249</v>
       </c>
       <c r="G4">
         <v>3849.8</v>
@@ -1621,28 +1621,28 @@
         <v>1744.9</v>
       </c>
       <c r="M4">
-        <v>44.0711498</v>
+        <v>66.1067247</v>
       </c>
       <c r="N4">
-        <v>1700.8288502</v>
+        <v>1678.7932753</v>
       </c>
       <c r="O4">
-        <v>248.3210121292</v>
+        <v>245.1038181938</v>
       </c>
       <c r="P4">
-        <v>1452.5078380708</v>
+        <v>1433.6894571062</v>
       </c>
       <c r="Q4">
-        <v>4246.4078380708</v>
+        <v>4227.5894571062</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06927006458560636</v>
+        <v>0.06947730307411763</v>
       </c>
       <c r="T4">
-        <v>0.5420338241479529</v>
+        <v>0.5468199324276589</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.5927950125776</v>
+        <v>26.39519667505173</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06868166998189409</v>
+        <v>0.06861955266989397</v>
       </c>
       <c r="C5">
-        <v>41690.1739854913</v>
+        <v>41315.83119358015</v>
       </c>
       <c r="D5">
-        <v>39154.6229854913</v>
+        <v>39218.36319358015</v>
       </c>
       <c r="E5">
-        <v>-13654.251</v>
+        <v>-13216.168</v>
       </c>
       <c r="F5">
-        <v>1314.249</v>
+        <v>1752.332</v>
       </c>
       <c r="G5">
         <v>3849.8</v>
@@ -1703,28 +1703,28 @@
         <v>1744.9</v>
       </c>
       <c r="M5">
-        <v>66.1067247</v>
+        <v>88.1422996</v>
       </c>
       <c r="N5">
-        <v>1678.7932753</v>
+        <v>1656.7577004</v>
       </c>
       <c r="O5">
-        <v>245.1038181938</v>
+        <v>241.8866242584</v>
       </c>
       <c r="P5">
-        <v>1433.6894571062</v>
+        <v>1414.8710761416</v>
       </c>
       <c r="Q5">
-        <v>4227.5894571062</v>
+        <v>4208.7710761416</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06947730307411763</v>
+        <v>0.06968885903113956</v>
       </c>
       <c r="T5">
-        <v>0.5468199324276589</v>
+        <v>0.5517057512965257</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.39519667505173</v>
+        <v>19.79639750628879</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06861955266989397</v>
+        <v>0.06855743535789385</v>
       </c>
       <c r="C6">
-        <v>41315.83119358015</v>
+        <v>40941.69626671774</v>
       </c>
       <c r="D6">
-        <v>39218.36319358015</v>
+        <v>39282.31126671774</v>
       </c>
       <c r="E6">
-        <v>-13216.168</v>
+        <v>-12778.085</v>
       </c>
       <c r="F6">
-        <v>1752.332</v>
+        <v>2190.415</v>
       </c>
       <c r="G6">
         <v>3849.8</v>
@@ -1785,28 +1785,28 @@
         <v>1744.9</v>
       </c>
       <c r="M6">
-        <v>88.1422996</v>
+        <v>110.1778745</v>
       </c>
       <c r="N6">
-        <v>1656.7577004</v>
+        <v>1634.7221255</v>
       </c>
       <c r="O6">
-        <v>241.8866242584</v>
+        <v>238.669430323</v>
       </c>
       <c r="P6">
-        <v>1414.8710761416</v>
+        <v>1396.052695177</v>
       </c>
       <c r="Q6">
-        <v>4208.7710761416</v>
+        <v>4189.952695177</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06968885903113956</v>
+        <v>0.069904868797783</v>
       </c>
       <c r="T6">
-        <v>0.5517057512965257</v>
+        <v>0.5566944295100001</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.79639750628879</v>
+        <v>15.83711800503104</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06855743535789385</v>
+        <v>0.06849531804589373</v>
       </c>
       <c r="C7">
-        <v>40941.69626671774</v>
+        <v>40567.77022337692</v>
       </c>
       <c r="D7">
-        <v>39282.31126671774</v>
+        <v>39346.46822337692</v>
       </c>
       <c r="E7">
-        <v>-12778.085</v>
+        <v>-12340.002</v>
       </c>
       <c r="F7">
-        <v>2190.415</v>
+        <v>2628.498000000001</v>
       </c>
       <c r="G7">
         <v>3849.8</v>
@@ -1867,28 +1867,28 @@
         <v>1744.9</v>
       </c>
       <c r="M7">
-        <v>110.1778745</v>
+        <v>132.2134494</v>
       </c>
       <c r="N7">
-        <v>1634.7221255</v>
+        <v>1612.6865506</v>
       </c>
       <c r="O7">
-        <v>238.669430323</v>
+        <v>235.4522363876</v>
       </c>
       <c r="P7">
-        <v>1396.052695177</v>
+        <v>1377.2343142124</v>
       </c>
       <c r="Q7">
-        <v>4189.952695177</v>
+        <v>4171.134314212401</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.069904868797783</v>
+        <v>0.07012547451690823</v>
       </c>
       <c r="T7">
-        <v>0.5566944295100001</v>
+        <v>0.5617892498131229</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.83711800503104</v>
+        <v>13.19759833752586</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06849531804589373</v>
+        <v>0.06843320073389361</v>
       </c>
       <c r="C8">
-        <v>40567.77022337692</v>
+        <v>40194.054088695</v>
       </c>
       <c r="D8">
-        <v>39346.46822337692</v>
+        <v>39410.83508869499</v>
       </c>
       <c r="E8">
-        <v>-12340.002</v>
+        <v>-11901.919</v>
       </c>
       <c r="F8">
-        <v>2628.498</v>
+        <v>3066.581</v>
       </c>
       <c r="G8">
         <v>3849.8</v>
@@ -1949,28 +1949,28 @@
         <v>1744.9</v>
       </c>
       <c r="M8">
-        <v>132.2134494</v>
+        <v>154.2490243</v>
       </c>
       <c r="N8">
-        <v>1612.6865506</v>
+        <v>1590.6509757</v>
       </c>
       <c r="O8">
-        <v>235.4522363876</v>
+        <v>232.2350424522</v>
       </c>
       <c r="P8">
-        <v>1377.2343142124</v>
+        <v>1358.4159332478</v>
       </c>
       <c r="Q8">
-        <v>4171.134314212401</v>
+        <v>4152.315933247801</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07012547451690823</v>
+        <v>0.07035082444504689</v>
       </c>
       <c r="T8">
-        <v>0.5617892498131229</v>
+        <v>0.5669936361442699</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.19759833752587</v>
+        <v>11.31222714645074</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06843320073389361</v>
+        <v>0.06837108342189348</v>
       </c>
       <c r="C9">
-        <v>40194.054088695</v>
+        <v>39820.54889452837</v>
       </c>
       <c r="D9">
-        <v>39410.83508869499</v>
+        <v>39475.41289452837</v>
       </c>
       <c r="E9">
-        <v>-11901.919</v>
+        <v>-11463.836</v>
       </c>
       <c r="F9">
-        <v>3066.581000000001</v>
+        <v>3504.664</v>
       </c>
       <c r="G9">
         <v>3849.8</v>
@@ -2031,28 +2031,28 @@
         <v>1744.9</v>
       </c>
       <c r="M9">
-        <v>154.2490243</v>
+        <v>176.2845992</v>
       </c>
       <c r="N9">
-        <v>1590.6509757</v>
+        <v>1568.6154008</v>
       </c>
       <c r="O9">
-        <v>232.2350424522</v>
+        <v>229.0178485168</v>
       </c>
       <c r="P9">
-        <v>1358.4159332478</v>
+        <v>1339.5975522832</v>
       </c>
       <c r="Q9">
-        <v>4152.315933247801</v>
+        <v>4133.4975522832</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07035082444504689</v>
+        <v>0.07058107328466683</v>
       </c>
       <c r="T9">
-        <v>0.5669936361442699</v>
+        <v>0.5723111613087026</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.31222714645074</v>
+        <v>9.898198753144399</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06837108342189348</v>
+        <v>0.06830896610989336</v>
       </c>
       <c r="C10">
-        <v>39820.54889452837</v>
+        <v>39447.25567950761</v>
       </c>
       <c r="D10">
-        <v>39475.41289452837</v>
+        <v>39540.20267950761</v>
       </c>
       <c r="E10">
-        <v>-11463.836</v>
+        <v>-11025.753</v>
       </c>
       <c r="F10">
-        <v>3504.664</v>
+        <v>3942.747</v>
       </c>
       <c r="G10">
         <v>3849.8</v>
@@ -2113,28 +2113,28 @@
         <v>1744.9</v>
       </c>
       <c r="M10">
-        <v>176.2845992</v>
+        <v>198.3201741</v>
       </c>
       <c r="N10">
-        <v>1568.6154008</v>
+        <v>1546.5798259</v>
       </c>
       <c r="O10">
-        <v>229.0178485168</v>
+        <v>225.8006545814</v>
       </c>
       <c r="P10">
-        <v>1339.5975522832</v>
+        <v>1320.7791713186</v>
       </c>
       <c r="Q10">
-        <v>4133.4975522832</v>
+        <v>4114.6791713186</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07058107328466683</v>
+        <v>0.07081638253834434</v>
       </c>
       <c r="T10">
-        <v>0.5723111613087026</v>
+        <v>0.5777455551580679</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.898198753144399</v>
+        <v>8.79839889168391</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06830896610989336</v>
+        <v>0.06837494879789321</v>
       </c>
       <c r="C11">
-        <v>39447.25567950761</v>
+        <v>38940.35823505939</v>
       </c>
       <c r="D11">
-        <v>39540.20267950761</v>
+        <v>39471.38823505938</v>
       </c>
       <c r="E11">
-        <v>-11025.753</v>
+        <v>-10587.67</v>
       </c>
       <c r="F11">
-        <v>3942.747</v>
+        <v>4380.83</v>
       </c>
       <c r="G11">
         <v>3849.8</v>
@@ -2195,45 +2195,45 @@
         <v>1744.9</v>
       </c>
       <c r="M11">
-        <v>198.3201741</v>
+        <v>226.926994</v>
       </c>
       <c r="N11">
-        <v>1546.5798259</v>
+        <v>1517.973006</v>
       </c>
       <c r="O11">
-        <v>225.8006545814</v>
+        <v>221.624058876</v>
       </c>
       <c r="P11">
-        <v>1320.7791713186</v>
+        <v>1296.348947124</v>
       </c>
       <c r="Q11">
-        <v>4114.6791713186</v>
+        <v>4090.248947124001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07081638253834434</v>
+        <v>0.07105692088654803</v>
       </c>
       <c r="T11">
-        <v>0.5777455551580679</v>
+        <v>0.5833007133151968</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.79839889168391</v>
+        <v>7.689257100898275</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06837494879789323</v>
+        <v>0.0683256414858931</v>
       </c>
       <c r="C12">
-        <v>38940.35823505937</v>
+        <v>38553.67600500773</v>
       </c>
       <c r="D12">
-        <v>39471.38823505937</v>
+        <v>39522.78900500773</v>
       </c>
       <c r="E12">
-        <v>-10587.67</v>
+        <v>-10149.587</v>
       </c>
       <c r="F12">
-        <v>4380.830000000001</v>
+        <v>4818.913</v>
       </c>
       <c r="G12">
         <v>3849.8</v>
@@ -2277,28 +2277,28 @@
         <v>1744.9</v>
       </c>
       <c r="M12">
-        <v>226.926994</v>
+        <v>249.6196934</v>
       </c>
       <c r="N12">
-        <v>1517.973006</v>
+        <v>1495.2803066</v>
       </c>
       <c r="O12">
-        <v>221.624058876</v>
+        <v>218.3109247636</v>
       </c>
       <c r="P12">
-        <v>1296.348947124</v>
+        <v>1276.9693818364</v>
       </c>
       <c r="Q12">
-        <v>4090.248947124001</v>
+        <v>4070.8693818364</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07105692088654803</v>
+        <v>0.07130286459089112</v>
       </c>
       <c r="T12">
-        <v>0.5833007133151968</v>
+        <v>0.5889807064870929</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.689257100898273</v>
+        <v>6.99023372808934</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0683256414858931</v>
+        <v>0.06845055017389297</v>
       </c>
       <c r="C13">
-        <v>38553.67600500773</v>
+        <v>37985.64015983387</v>
       </c>
       <c r="D13">
-        <v>39522.78900500773</v>
+        <v>39392.83615983387</v>
       </c>
       <c r="E13">
-        <v>-10149.587</v>
+        <v>-9711.504000000001</v>
       </c>
       <c r="F13">
-        <v>4818.913</v>
+        <v>5256.996</v>
       </c>
       <c r="G13">
         <v>3849.8</v>
@@ -2359,45 +2359,45 @@
         <v>1744.9</v>
       </c>
       <c r="M13">
-        <v>249.6196934</v>
+        <v>281.249286</v>
       </c>
       <c r="N13">
-        <v>1495.2803066</v>
+        <v>1463.650714</v>
       </c>
       <c r="O13">
-        <v>218.3109247636</v>
+        <v>213.693004244</v>
       </c>
       <c r="P13">
-        <v>1276.9693818364</v>
+        <v>1249.957709756</v>
       </c>
       <c r="Q13">
-        <v>4070.8693818364</v>
+        <v>4043.857709756</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07130286459089112</v>
+        <v>0.07155439792487837</v>
       </c>
       <c r="T13">
-        <v>0.5889807064870929</v>
+        <v>0.5947897904128955</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.99023372808934</v>
+        <v>6.204104639042534</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06845055017389297</v>
+        <v>0.06841576086189284</v>
       </c>
       <c r="C14">
-        <v>37985.64015983387</v>
+        <v>37583.66541911712</v>
       </c>
       <c r="D14">
-        <v>39392.83615983387</v>
+        <v>39428.94441911711</v>
       </c>
       <c r="E14">
-        <v>-9711.504000000001</v>
+        <v>-9273.420999999998</v>
       </c>
       <c r="F14">
-        <v>5256.996</v>
+        <v>5695.079000000001</v>
       </c>
       <c r="G14">
         <v>3849.8</v>
@@ -2441,28 +2441,28 @@
         <v>1744.9</v>
       </c>
       <c r="M14">
-        <v>281.249286</v>
+        <v>304.6867265</v>
       </c>
       <c r="N14">
-        <v>1463.650714</v>
+        <v>1440.2132735</v>
       </c>
       <c r="O14">
-        <v>213.693004244</v>
+        <v>210.271137931</v>
       </c>
       <c r="P14">
-        <v>1249.957709756</v>
+        <v>1229.942135569</v>
       </c>
       <c r="Q14">
-        <v>4043.857709756</v>
+        <v>4023.842135569</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07155439792487837</v>
+        <v>0.07181171363435959</v>
       </c>
       <c r="T14">
-        <v>0.5947897904128955</v>
+        <v>0.6007324164979121</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.204104639042534</v>
+        <v>5.726865820654645</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06841576086189284</v>
+        <v>0.06847661954989272</v>
       </c>
       <c r="C15">
-        <v>37583.66541911712</v>
+        <v>37082.45974781476</v>
       </c>
       <c r="D15">
-        <v>39428.94441911711</v>
+        <v>39365.82174781476</v>
       </c>
       <c r="E15">
-        <v>-9273.420999999998</v>
+        <v>-8835.338</v>
       </c>
       <c r="F15">
-        <v>5695.079000000001</v>
+        <v>6133.162000000001</v>
       </c>
       <c r="G15">
         <v>3849.8</v>
@@ -2523,45 +2523,45 @@
         <v>1744.9</v>
       </c>
       <c r="M15">
-        <v>304.6867265</v>
+        <v>333.0306966000001</v>
       </c>
       <c r="N15">
-        <v>1440.2132735</v>
+        <v>1411.8693034</v>
       </c>
       <c r="O15">
-        <v>210.271137931</v>
+        <v>206.1329182964</v>
       </c>
       <c r="P15">
-        <v>1229.942135569</v>
+        <v>1205.7363851036</v>
       </c>
       <c r="Q15">
-        <v>4023.842135569</v>
+        <v>3999.6363851036</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07181171363435959</v>
+        <v>0.0720750134301078</v>
       </c>
       <c r="T15">
-        <v>0.6007324164979121</v>
+        <v>0.6068132431895569</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>5.726865820654645</v>
+        <v>5.239456956413188</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06847661954989272</v>
+        <v>0.06844866223789259</v>
       </c>
       <c r="C16">
-        <v>37082.45974781476</v>
+        <v>36673.34897488674</v>
       </c>
       <c r="D16">
-        <v>39365.82174781476</v>
+        <v>39394.79397488674</v>
       </c>
       <c r="E16">
-        <v>-8835.338</v>
+        <v>-8397.254999999997</v>
       </c>
       <c r="F16">
-        <v>6133.162000000001</v>
+        <v>6571.245000000002</v>
       </c>
       <c r="G16">
         <v>3849.8</v>
@@ -2605,28 +2605,28 @@
         <v>1744.9</v>
       </c>
       <c r="M16">
-        <v>333.0306966000001</v>
+        <v>356.8186035000001</v>
       </c>
       <c r="N16">
-        <v>1411.8693034</v>
+        <v>1388.0813965</v>
       </c>
       <c r="O16">
-        <v>206.1329182964</v>
+        <v>202.659883889</v>
       </c>
       <c r="P16">
-        <v>1205.7363851036</v>
+        <v>1185.421512611</v>
       </c>
       <c r="Q16">
-        <v>3999.6363851036</v>
+        <v>3979.321512611</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0720750134301078</v>
+        <v>0.07234450851516776</v>
       </c>
       <c r="T16">
-        <v>0.6068132431895569</v>
+        <v>0.6130371481562993</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.239456956413188</v>
+        <v>4.890159825985641</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06844866223789259</v>
+        <v>0.06842070492589247</v>
       </c>
       <c r="C17">
-        <v>36673.34897488674</v>
+        <v>36264.28087898811</v>
       </c>
       <c r="D17">
-        <v>39394.79397488674</v>
+        <v>39423.80887898811</v>
       </c>
       <c r="E17">
-        <v>-8397.255000000001</v>
+        <v>-7959.172</v>
       </c>
       <c r="F17">
-        <v>6571.245</v>
+        <v>7009.328</v>
       </c>
       <c r="G17">
         <v>3849.8</v>
@@ -2687,28 +2687,28 @@
         <v>1744.9</v>
       </c>
       <c r="M17">
-        <v>356.8186035</v>
+        <v>380.6065104</v>
       </c>
       <c r="N17">
-        <v>1388.0813965</v>
+        <v>1364.2934896</v>
       </c>
       <c r="O17">
-        <v>202.659883889</v>
+        <v>199.1868494816</v>
       </c>
       <c r="P17">
-        <v>1185.421512611</v>
+        <v>1165.1066401184</v>
       </c>
       <c r="Q17">
-        <v>3979.321512611</v>
+        <v>3959.0066401184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07234450851516776</v>
+        <v>0.07262042014987199</v>
       </c>
       <c r="T17">
-        <v>0.6130371481562993</v>
+        <v>0.6194092413365355</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.890159825985643</v>
+        <v>4.58452483686154</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06842070492589247</v>
+        <v>0.06839274761389234</v>
       </c>
       <c r="C18">
-        <v>36264.28087898811</v>
+        <v>35855.25555448535</v>
       </c>
       <c r="D18">
-        <v>39423.80887898811</v>
+        <v>39452.86655448535</v>
       </c>
       <c r="E18">
-        <v>-7959.172</v>
+        <v>-7521.088999999999</v>
       </c>
       <c r="F18">
-        <v>7009.328</v>
+        <v>7447.411000000001</v>
       </c>
       <c r="G18">
         <v>3849.8</v>
@@ -2769,28 +2769,28 @@
         <v>1744.9</v>
       </c>
       <c r="M18">
-        <v>380.6065104</v>
+        <v>404.3944173</v>
       </c>
       <c r="N18">
-        <v>1364.2934896</v>
+        <v>1340.5055827</v>
       </c>
       <c r="O18">
-        <v>199.1868494816</v>
+        <v>195.7138150742</v>
       </c>
       <c r="P18">
-        <v>1165.1066401184</v>
+        <v>1144.7917676258</v>
       </c>
       <c r="Q18">
-        <v>3959.0066401184</v>
+        <v>3938.6917676258</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07262042014987199</v>
+        <v>0.07290298025770162</v>
       </c>
       <c r="T18">
-        <v>0.6194092413365355</v>
+        <v>0.6259348789307533</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.58452483686154</v>
+        <v>4.314846905281449</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06839274761389234</v>
+        <v>0.06851851030189222</v>
       </c>
       <c r="C19">
-        <v>35855.25555448535</v>
+        <v>35286.79594079889</v>
       </c>
       <c r="D19">
-        <v>39452.86655448535</v>
+        <v>39322.48994079889</v>
       </c>
       <c r="E19">
-        <v>-7521.088999999999</v>
+        <v>-7083.005999999998</v>
       </c>
       <c r="F19">
-        <v>7447.411000000001</v>
+        <v>7885.494000000002</v>
       </c>
       <c r="G19">
         <v>3849.8</v>
@@ -2851,45 +2851,45 @@
         <v>1744.9</v>
       </c>
       <c r="M19">
-        <v>404.3944173</v>
+        <v>436.0678182000001</v>
       </c>
       <c r="N19">
-        <v>1340.5055827</v>
+        <v>1308.8321818</v>
       </c>
       <c r="O19">
-        <v>195.7138150742</v>
+        <v>191.0894985428</v>
       </c>
       <c r="P19">
-        <v>1144.7917676258</v>
+        <v>1117.7426832572</v>
       </c>
       <c r="Q19">
-        <v>3938.6917676258</v>
+        <v>3911.6426832572</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07290298025770162</v>
+        <v>0.07319243207547832</v>
       </c>
       <c r="T19">
-        <v>0.6259348789307533</v>
+        <v>0.632619678417513</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.314846905281449</v>
+        <v>4.001441810594038</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06851851030189222</v>
+        <v>0.0684990929898921</v>
       </c>
       <c r="C20">
-        <v>35286.79594079889</v>
+        <v>34868.78634749899</v>
       </c>
       <c r="D20">
-        <v>39322.48994079889</v>
+        <v>39342.56334749898</v>
       </c>
       <c r="E20">
-        <v>-7083.005999999999</v>
+        <v>-6644.922999999999</v>
       </c>
       <c r="F20">
-        <v>7885.494000000001</v>
+        <v>8323.577000000001</v>
       </c>
       <c r="G20">
         <v>3849.8</v>
@@ -2933,28 +2933,28 @@
         <v>1744.9</v>
       </c>
       <c r="M20">
-        <v>436.0678182</v>
+        <v>460.2938081000001</v>
       </c>
       <c r="N20">
-        <v>1308.8321818</v>
+        <v>1284.6061919</v>
       </c>
       <c r="O20">
-        <v>191.0894985428</v>
+        <v>187.5525040174</v>
       </c>
       <c r="P20">
-        <v>1117.7426832572</v>
+        <v>1097.0536878826</v>
       </c>
       <c r="Q20">
-        <v>3911.6426832572</v>
+        <v>3890.9536878826</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07319243207547832</v>
+        <v>0.07348903085171864</v>
       </c>
       <c r="T20">
-        <v>0.632619678417513</v>
+        <v>0.6394695346817236</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.001441810594038</v>
+        <v>3.790839610036457</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0684990929898921</v>
+        <v>0.06847967567789195</v>
       </c>
       <c r="C21">
-        <v>34868.78634749899</v>
+        <v>34450.79725887499</v>
       </c>
       <c r="D21">
-        <v>39342.56334749898</v>
+        <v>39362.65725887499</v>
       </c>
       <c r="E21">
-        <v>-6644.922999999999</v>
+        <v>-6206.839999999998</v>
       </c>
       <c r="F21">
-        <v>8323.577000000001</v>
+        <v>8761.660000000002</v>
       </c>
       <c r="G21">
         <v>3849.8</v>
@@ -3015,28 +3015,28 @@
         <v>1744.9</v>
       </c>
       <c r="M21">
-        <v>460.2938081000001</v>
+        <v>484.5197980000001</v>
       </c>
       <c r="N21">
-        <v>1284.6061919</v>
+        <v>1260.380202</v>
       </c>
       <c r="O21">
-        <v>187.5525040174</v>
+        <v>184.015509492</v>
       </c>
       <c r="P21">
-        <v>1097.0536878826</v>
+        <v>1076.364692508</v>
       </c>
       <c r="Q21">
-        <v>3890.9536878826</v>
+        <v>3870.264692508</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07348903085171864</v>
+        <v>0.07379304459736495</v>
       </c>
       <c r="T21">
-        <v>0.6394695346817236</v>
+        <v>0.6464906373525394</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.790839610036457</v>
+        <v>3.601297629534634</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06847967567789195</v>
+        <v>0.06846025836589184</v>
       </c>
       <c r="C22">
-        <v>34450.79725887499</v>
+        <v>34032.82870636074</v>
       </c>
       <c r="D22">
-        <v>39362.65725887499</v>
+        <v>39382.77170636074</v>
       </c>
       <c r="E22">
-        <v>-6206.839999999998</v>
+        <v>-5768.756999999998</v>
       </c>
       <c r="F22">
-        <v>8761.660000000002</v>
+        <v>9199.743000000002</v>
       </c>
       <c r="G22">
         <v>3849.8</v>
@@ -3097,28 +3097,28 @@
         <v>1744.9</v>
       </c>
       <c r="M22">
-        <v>484.5197980000001</v>
+        <v>508.7457879000002</v>
       </c>
       <c r="N22">
-        <v>1260.380202</v>
+        <v>1236.1542121</v>
       </c>
       <c r="O22">
-        <v>184.015509492</v>
+        <v>180.4785149666</v>
       </c>
       <c r="P22">
-        <v>1076.364692508</v>
+        <v>1055.6756971334</v>
       </c>
       <c r="Q22">
-        <v>3870.264692508</v>
+        <v>3849.5756971334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07379304459736495</v>
+        <v>0.07410475489353396</v>
       </c>
       <c r="T22">
-        <v>0.6464906373525394</v>
+        <v>0.6536894894580594</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.601297629534634</v>
+        <v>3.429807266223461</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06846025836589183</v>
+        <v>0.06844084105389171</v>
       </c>
       <c r="C23">
-        <v>34032.82870636075</v>
+        <v>33614.88072145443</v>
       </c>
       <c r="D23">
-        <v>39382.77170636075</v>
+        <v>39402.90672145443</v>
       </c>
       <c r="E23">
-        <v>-5768.757</v>
+        <v>-5330.673999999999</v>
       </c>
       <c r="F23">
-        <v>9199.743</v>
+        <v>9637.826000000001</v>
       </c>
       <c r="G23">
         <v>3849.8</v>
@@ -3179,28 +3179,28 @@
         <v>1744.9</v>
       </c>
       <c r="M23">
-        <v>508.7457879</v>
+        <v>532.9717778</v>
       </c>
       <c r="N23">
-        <v>1236.1542121</v>
+        <v>1211.9282222</v>
       </c>
       <c r="O23">
-        <v>180.4785149666</v>
+        <v>176.9415204412</v>
       </c>
       <c r="P23">
-        <v>1055.6756971334</v>
+        <v>1034.9867017588</v>
       </c>
       <c r="Q23">
-        <v>3849.5756971334</v>
+        <v>3828.8867017588</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07410475489353396</v>
+        <v>0.07442445776139964</v>
       </c>
       <c r="T23">
-        <v>0.6536894894580594</v>
+        <v>0.661072927515003</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.429807266223461</v>
+        <v>3.273906935940577</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06844084105389171</v>
+        <v>0.0684214237418916</v>
       </c>
       <c r="C24">
-        <v>33614.88072145443</v>
+        <v>33196.95333571864</v>
       </c>
       <c r="D24">
-        <v>39402.90672145443</v>
+        <v>39423.06233571863</v>
       </c>
       <c r="E24">
-        <v>-5330.673999999999</v>
+        <v>-4892.590999999999</v>
       </c>
       <c r="F24">
-        <v>9637.826000000001</v>
+        <v>10075.909</v>
       </c>
       <c r="G24">
         <v>3849.8</v>
@@ -3261,28 +3261,28 @@
         <v>1744.9</v>
       </c>
       <c r="M24">
-        <v>532.9717778</v>
+        <v>557.1977677000001</v>
       </c>
       <c r="N24">
-        <v>1211.9282222</v>
+        <v>1187.7022323</v>
       </c>
       <c r="O24">
-        <v>176.9415204412</v>
+        <v>173.4045259158</v>
       </c>
       <c r="P24">
-        <v>1034.9867017588</v>
+        <v>1014.2977063842</v>
       </c>
       <c r="Q24">
-        <v>3828.8867017588</v>
+        <v>3808.1977063842</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07442445776139964</v>
+        <v>0.07475246459985921</v>
       </c>
       <c r="T24">
-        <v>0.661072927515003</v>
+        <v>0.6686481431838153</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.273906935940577</v>
+        <v>3.131563156117073</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0684214237418916</v>
+        <v>0.06840200642989146</v>
       </c>
       <c r="C25">
-        <v>33196.95333571864</v>
+        <v>32779.04658078062</v>
       </c>
       <c r="D25">
-        <v>39423.06233571863</v>
+        <v>39443.23858078061</v>
       </c>
       <c r="E25">
-        <v>-4892.590999999999</v>
+        <v>-4454.507999999998</v>
       </c>
       <c r="F25">
-        <v>10075.909</v>
+        <v>10513.992</v>
       </c>
       <c r="G25">
         <v>3849.8</v>
@@ -3343,28 +3343,28 @@
         <v>1744.9</v>
       </c>
       <c r="M25">
-        <v>557.1977677000001</v>
+        <v>581.4237576000002</v>
       </c>
       <c r="N25">
-        <v>1187.7022323</v>
+        <v>1163.4762424</v>
       </c>
       <c r="O25">
-        <v>173.4045259158</v>
+        <v>169.8675313904</v>
       </c>
       <c r="P25">
-        <v>1014.2977063842</v>
+        <v>993.6087110096</v>
       </c>
       <c r="Q25">
-        <v>3808.1977063842</v>
+        <v>3787.5087110096</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07475246459985921</v>
+        <v>0.0750891031972256</v>
       </c>
       <c r="T25">
-        <v>0.6686481431838153</v>
+        <v>0.6764227066333858</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.131563156117073</v>
+        <v>3.001081357945528</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06840200642989146</v>
+        <v>0.06891633911789133</v>
       </c>
       <c r="C26">
-        <v>32779.04658078062</v>
+        <v>31813.40627367533</v>
       </c>
       <c r="D26">
-        <v>39443.23858078061</v>
+        <v>38915.68127367533</v>
       </c>
       <c r="E26">
-        <v>-4454.508</v>
+        <v>-4016.424999999999</v>
       </c>
       <c r="F26">
-        <v>10513.992</v>
+        <v>10952.075</v>
       </c>
       <c r="G26">
         <v>3849.8</v>
@@ -3425,45 +3425,45 @@
         <v>1744.9</v>
       </c>
       <c r="M26">
-        <v>581.4237576</v>
+        <v>633.0299350000001</v>
       </c>
       <c r="N26">
-        <v>1163.4762424</v>
+        <v>1111.870065</v>
       </c>
       <c r="O26">
-        <v>169.8675313904</v>
+        <v>162.33302949</v>
       </c>
       <c r="P26">
-        <v>993.6087110096</v>
+        <v>949.5370355100001</v>
       </c>
       <c r="Q26">
-        <v>3787.5087110096</v>
+        <v>3743.43703551</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0750891031972256</v>
+        <v>0.07543471882385511</v>
       </c>
       <c r="T26">
-        <v>0.6764227066333858</v>
+        <v>0.6844045917749448</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.001081357945529</v>
+        <v>2.756425728903325</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06891633911789133</v>
+        <v>0.0689182718058912</v>
       </c>
       <c r="C27">
-        <v>31813.40627367533</v>
+        <v>31373.36750488717</v>
       </c>
       <c r="D27">
-        <v>38915.68127367533</v>
+        <v>38913.72550488717</v>
       </c>
       <c r="E27">
-        <v>-4016.424999999999</v>
+        <v>-3578.341999999999</v>
       </c>
       <c r="F27">
-        <v>10952.075</v>
+        <v>11390.158</v>
       </c>
       <c r="G27">
         <v>3849.8</v>
@@ -3507,28 +3507,28 @@
         <v>1744.9</v>
       </c>
       <c r="M27">
-        <v>633.0299350000001</v>
+        <v>658.3511324000001</v>
       </c>
       <c r="N27">
-        <v>1111.870065</v>
+        <v>1086.5488676</v>
       </c>
       <c r="O27">
-        <v>162.33302949</v>
+        <v>158.6361346696</v>
       </c>
       <c r="P27">
-        <v>949.5370355100001</v>
+        <v>927.9127329304</v>
       </c>
       <c r="Q27">
-        <v>3743.43703551</v>
+        <v>3721.8127329304</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07543471882385511</v>
+        <v>0.07578967541336649</v>
       </c>
       <c r="T27">
-        <v>0.6844045917749448</v>
+        <v>0.6926022035419515</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.756425728903325</v>
+        <v>2.650409354714736</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0689182718058912</v>
+        <v>0.06892020449389108</v>
       </c>
       <c r="C28">
-        <v>31373.36750488717</v>
+        <v>30933.3289326696</v>
       </c>
       <c r="D28">
-        <v>38913.72550488717</v>
+        <v>38911.7699326696</v>
       </c>
       <c r="E28">
-        <v>-3578.341999999999</v>
+        <v>-3140.258999999998</v>
       </c>
       <c r="F28">
-        <v>11390.158</v>
+        <v>11828.241</v>
       </c>
       <c r="G28">
         <v>3849.8</v>
@@ -3589,28 +3589,28 @@
         <v>1744.9</v>
       </c>
       <c r="M28">
-        <v>658.3511324000001</v>
+        <v>683.6723298000002</v>
       </c>
       <c r="N28">
-        <v>1086.5488676</v>
+        <v>1061.2276702</v>
       </c>
       <c r="O28">
-        <v>158.6361346696</v>
+        <v>154.9392398492</v>
       </c>
       <c r="P28">
-        <v>927.9127329304</v>
+        <v>906.2884303507999</v>
       </c>
       <c r="Q28">
-        <v>3721.8127329304</v>
+        <v>3700.1884303508</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07578967541336649</v>
+        <v>0.07615435684094669</v>
       </c>
       <c r="T28">
-        <v>0.6926022035419515</v>
+        <v>0.7010244074121638</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.650409354714736</v>
+        <v>2.552246045280857</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06892020449389108</v>
+        <v>0.06975905718189095</v>
       </c>
       <c r="C29">
-        <v>30933.3289326696</v>
+        <v>29664.62093835983</v>
       </c>
       <c r="D29">
-        <v>38911.7699326696</v>
+        <v>38081.14493835983</v>
       </c>
       <c r="E29">
-        <v>-3140.258999999998</v>
+        <v>-2702.175999999998</v>
       </c>
       <c r="F29">
-        <v>11828.241</v>
+        <v>12266.324</v>
       </c>
       <c r="G29">
         <v>3849.8</v>
@@ -3671,45 +3671,45 @@
         <v>1744.9</v>
       </c>
       <c r="M29">
-        <v>683.6723298000002</v>
+        <v>751.9256612000001</v>
       </c>
       <c r="N29">
-        <v>1061.2276702</v>
+        <v>992.9743387999999</v>
       </c>
       <c r="O29">
-        <v>154.9392398492</v>
+        <v>144.9742534648</v>
       </c>
       <c r="P29">
-        <v>906.2884303507999</v>
+        <v>848.0000853352</v>
       </c>
       <c r="Q29">
-        <v>3700.1884303508</v>
+        <v>3641.9000853352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07615435684094669</v>
+        <v>0.07652916830818188</v>
       </c>
       <c r="T29">
-        <v>0.7010244074121638</v>
+        <v>0.7096805613898819</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.552246045280857</v>
+        <v>2.320575144643035</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06975905718189095</v>
+        <v>0.07048432786989084</v>
       </c>
       <c r="C30">
-        <v>29664.62093835983</v>
+        <v>28536.44728428614</v>
       </c>
       <c r="D30">
-        <v>38081.14493835983</v>
+        <v>37391.05428428614</v>
       </c>
       <c r="E30">
-        <v>-2702.175999999998</v>
+        <v>-2264.092999999997</v>
       </c>
       <c r="F30">
-        <v>12266.324</v>
+        <v>12704.407</v>
       </c>
       <c r="G30">
         <v>3849.8</v>
@@ -3753,45 +3753,45 @@
         <v>1744.9</v>
       </c>
       <c r="M30">
-        <v>751.9256612000001</v>
+        <v>814.3524887000002</v>
       </c>
       <c r="N30">
-        <v>992.9743387999999</v>
+        <v>930.5475112999999</v>
       </c>
       <c r="O30">
-        <v>144.9742534648</v>
+        <v>135.8599366498</v>
       </c>
       <c r="P30">
-        <v>848.0000853352</v>
+        <v>794.6875746501998</v>
       </c>
       <c r="Q30">
-        <v>3641.9000853352</v>
+        <v>3588.5875746502</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07652916830818188</v>
+        <v>0.07691453784491667</v>
       </c>
       <c r="T30">
-        <v>0.7096805613898819</v>
+        <v>0.7185805506909161</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.320575144643035</v>
+        <v>2.142683941183122</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07048432786989084</v>
+        <v>0.07054006255789072</v>
       </c>
       <c r="C31">
-        <v>28536.44728428614</v>
+        <v>28046.3664881758</v>
       </c>
       <c r="D31">
-        <v>37391.05428428614</v>
+        <v>37339.0564881758</v>
       </c>
       <c r="E31">
-        <v>-2264.093000000001</v>
+        <v>-1826.01</v>
       </c>
       <c r="F31">
-        <v>12704.407</v>
+        <v>13142.49</v>
       </c>
       <c r="G31">
         <v>3849.8</v>
@@ -3835,28 +3835,28 @@
         <v>1744.9</v>
       </c>
       <c r="M31">
-        <v>814.3524887</v>
+        <v>842.433609</v>
       </c>
       <c r="N31">
-        <v>930.5475113000001</v>
+        <v>902.466391</v>
       </c>
       <c r="O31">
-        <v>135.8599366498</v>
+        <v>131.760093086</v>
       </c>
       <c r="P31">
-        <v>794.6875746502001</v>
+        <v>770.7062979140001</v>
       </c>
       <c r="Q31">
-        <v>3588.5875746502</v>
+        <v>3564.606297914</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07691453784491667</v>
+        <v>0.07731091793984388</v>
       </c>
       <c r="T31">
-        <v>0.7185805506909161</v>
+        <v>0.7277348254005512</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.142683941183122</v>
+        <v>2.071261143143685</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07054006255789072</v>
+        <v>0.07059579724589057</v>
       </c>
       <c r="C32">
-        <v>28046.3664881758</v>
+        <v>27556.43011249331</v>
       </c>
       <c r="D32">
-        <v>37339.0564881758</v>
+        <v>37287.20311249331</v>
       </c>
       <c r="E32">
-        <v>-1826.01</v>
+        <v>-1387.927</v>
       </c>
       <c r="F32">
-        <v>13142.49</v>
+        <v>13580.573</v>
       </c>
       <c r="G32">
         <v>3849.8</v>
@@ -3917,28 +3917,28 @@
         <v>1744.9</v>
       </c>
       <c r="M32">
-        <v>842.433609</v>
+        <v>870.5147293000001</v>
       </c>
       <c r="N32">
-        <v>902.466391</v>
+        <v>874.3852707</v>
       </c>
       <c r="O32">
-        <v>131.760093086</v>
+        <v>127.6602495222</v>
       </c>
       <c r="P32">
-        <v>770.7062979140001</v>
+        <v>746.7250211778</v>
       </c>
       <c r="Q32">
-        <v>3564.606297914</v>
+        <v>3540.6250211778</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07731091793984388</v>
+        <v>0.0777187873128849</v>
       </c>
       <c r="T32">
-        <v>0.7277348254005512</v>
+        <v>0.7371544414061179</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.071261143143685</v>
+        <v>2.004446267558404</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07059579724589057</v>
+        <v>0.07384890793389046</v>
       </c>
       <c r="C33">
-        <v>27556.43011249331</v>
+        <v>24322.59640478434</v>
       </c>
       <c r="D33">
-        <v>37287.20311249331</v>
+        <v>34491.45240478434</v>
       </c>
       <c r="E33">
-        <v>-1387.927</v>
+        <v>-949.8439999999991</v>
       </c>
       <c r="F33">
-        <v>13580.573</v>
+        <v>14018.656</v>
       </c>
       <c r="G33">
         <v>3849.8</v>
@@ -3999,45 +3999,45 @@
         <v>1744.9</v>
       </c>
       <c r="M33">
-        <v>870.5147293000001</v>
+        <v>1062.6141248</v>
       </c>
       <c r="N33">
-        <v>874.3852707</v>
+        <v>682.2858752</v>
       </c>
       <c r="O33">
-        <v>127.6602495222</v>
+        <v>99.61373777919999</v>
       </c>
       <c r="P33">
-        <v>746.7250211778</v>
+        <v>582.6721374208</v>
       </c>
       <c r="Q33">
-        <v>3540.6250211778</v>
+        <v>3376.5721374208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0777187873128849</v>
+        <v>0.07813865284395655</v>
       </c>
       <c r="T33">
-        <v>0.7371544414061179</v>
+        <v>0.7468511049412598</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0547414</v>
+        <v>0.0647332</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.004446267558404</v>
+        <v>1.642082444865314</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07384890793389046</v>
+        <v>0.07400456062189033</v>
       </c>
       <c r="C34">
-        <v>24322.59640478434</v>
+        <v>23761.21636707167</v>
       </c>
       <c r="D34">
-        <v>34491.45240478434</v>
+        <v>34368.15536707167</v>
       </c>
       <c r="E34">
-        <v>-949.8439999999991</v>
+        <v>-511.7609999999986</v>
       </c>
       <c r="F34">
-        <v>14018.656</v>
+        <v>14456.739</v>
       </c>
       <c r="G34">
         <v>3849.8</v>
@@ -4081,28 +4081,28 @@
         <v>1744.9</v>
       </c>
       <c r="M34">
-        <v>1062.6141248</v>
+        <v>1095.8208162</v>
       </c>
       <c r="N34">
-        <v>682.2858752</v>
+        <v>649.0791837999998</v>
       </c>
       <c r="O34">
-        <v>99.61373777919999</v>
+        <v>94.76556083479996</v>
       </c>
       <c r="P34">
-        <v>582.6721374208</v>
+        <v>554.3136229651998</v>
       </c>
       <c r="Q34">
-        <v>3376.5721374208</v>
+        <v>3348.2136229652</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07813865284395655</v>
+        <v>0.07857105167446318</v>
       </c>
       <c r="T34">
-        <v>0.7468511049412598</v>
+        <v>0.756837221119242</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.642082444865314</v>
+        <v>1.592322370778486</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07400456062189033</v>
+        <v>0.0741602133098902</v>
       </c>
       <c r="C35">
-        <v>23761.21636707167</v>
+        <v>23200.7146924703</v>
       </c>
       <c r="D35">
-        <v>34368.15536707167</v>
+        <v>34245.73669247029</v>
       </c>
       <c r="E35">
-        <v>-511.7609999999986</v>
+        <v>-73.67799999999806</v>
       </c>
       <c r="F35">
-        <v>14456.739</v>
+        <v>14894.822</v>
       </c>
       <c r="G35">
         <v>3849.8</v>
@@ -4163,28 +4163,28 @@
         <v>1744.9</v>
       </c>
       <c r="M35">
-        <v>1095.8208162</v>
+        <v>1129.0275076</v>
       </c>
       <c r="N35">
-        <v>649.0791837999998</v>
+        <v>615.8724923999998</v>
       </c>
       <c r="O35">
-        <v>94.76556083479996</v>
+        <v>89.91738389039998</v>
       </c>
       <c r="P35">
-        <v>554.3136229651998</v>
+        <v>525.9551085095999</v>
       </c>
       <c r="Q35">
-        <v>3348.2136229652</v>
+        <v>3319.8551085096</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07857105167446318</v>
+        <v>0.07901655349983364</v>
       </c>
       <c r="T35">
-        <v>0.756837221119242</v>
+        <v>0.7671259468783751</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.592322370778486</v>
+        <v>1.545489359873236</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0741602133098902</v>
+        <v>0.07431586599789007</v>
       </c>
       <c r="C36">
-        <v>23200.7146924703</v>
+        <v>22641.08202815987</v>
       </c>
       <c r="D36">
-        <v>34245.73669247029</v>
+        <v>34124.18702815987</v>
       </c>
       <c r="E36">
-        <v>-73.67799999999806</v>
+        <v>364.4050000000025</v>
       </c>
       <c r="F36">
-        <v>14894.822</v>
+        <v>15332.905</v>
       </c>
       <c r="G36">
         <v>3849.8</v>
@@ -4245,28 +4245,28 @@
         <v>1744.9</v>
       </c>
       <c r="M36">
-        <v>1129.0275076</v>
+        <v>1162.234199</v>
       </c>
       <c r="N36">
-        <v>615.8724923999998</v>
+        <v>582.6658009999999</v>
       </c>
       <c r="O36">
-        <v>89.91738389039998</v>
+        <v>85.06920694599998</v>
       </c>
       <c r="P36">
-        <v>525.9551085095999</v>
+        <v>497.5965940539999</v>
       </c>
       <c r="Q36">
-        <v>3319.8551085096</v>
+        <v>3291.496594054</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07901655349983364</v>
+        <v>0.07947576307367704</v>
       </c>
       <c r="T36">
-        <v>0.7671259468783751</v>
+        <v>0.7777312488147122</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.545489359873236</v>
+        <v>1.501332521019715</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07431586599789007</v>
+        <v>0.08812971227367877</v>
       </c>
       <c r="C37">
-        <v>22641.08202815987</v>
+        <v>14028.84010762306</v>
       </c>
       <c r="D37">
-        <v>34124.18702815987</v>
+        <v>25950.02810762306</v>
       </c>
       <c r="E37">
-        <v>364.4050000000025</v>
+        <v>802.488000000003</v>
       </c>
       <c r="F37">
-        <v>15332.905</v>
+        <v>15770.988</v>
       </c>
       <c r="G37">
         <v>3849.8</v>
@@ -4327,45 +4327,45 @@
         <v>1744.9</v>
       </c>
       <c r="M37">
-        <v>1162.234199</v>
+        <v>1870.4391768</v>
       </c>
       <c r="N37">
-        <v>582.6658009999999</v>
+        <v>-125.5391768000004</v>
       </c>
       <c r="O37">
-        <v>85.06920694599998</v>
+        <v>-18.32871981280006</v>
       </c>
       <c r="P37">
-        <v>497.5965940539999</v>
+        <v>-107.2104569872003</v>
       </c>
       <c r="Q37">
-        <v>3291.496594054</v>
+        <v>2686.6895430128</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07947576307367704</v>
+        <v>0.08007647442804083</v>
       </c>
       <c r="T37">
-        <v>0.7777312488147122</v>
+        <v>0.7916044902549846</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.146</v>
+        <v>0.1362008469240056</v>
       </c>
       <c r="W37">
-        <v>0.0647332</v>
+        <v>0.1024465795548129</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.501332521019715</v>
+        <v>0.9328825131781209</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08812971227367879</v>
+        <v>0.08885771227367879</v>
       </c>
       <c r="C38">
-        <v>14028.84010762305</v>
+        <v>13267.24753681334</v>
       </c>
       <c r="D38">
-        <v>25950.02810762305</v>
+        <v>25626.51853681334</v>
       </c>
       <c r="E38">
-        <v>802.4880000000012</v>
+        <v>1240.571000000002</v>
       </c>
       <c r="F38">
-        <v>15770.988</v>
+        <v>16209.071</v>
       </c>
       <c r="G38">
         <v>3849.8</v>
@@ -4409,37 +4409,37 @@
         <v>1744.9</v>
       </c>
       <c r="M38">
-        <v>1870.4391768</v>
+        <v>1922.3958206</v>
       </c>
       <c r="N38">
-        <v>-125.5391768000002</v>
+        <v>-177.4958206000003</v>
       </c>
       <c r="O38">
-        <v>-18.32871981280002</v>
+        <v>-25.91438980760005</v>
       </c>
       <c r="P38">
-        <v>-107.2104569872002</v>
+        <v>-151.5814307924003</v>
       </c>
       <c r="Q38">
-        <v>2686.6895430128</v>
+        <v>2642.3185692076</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08007647442804083</v>
+        <v>0.08062054545070815</v>
       </c>
       <c r="T38">
-        <v>0.7916044902549846</v>
+        <v>0.8041696408939526</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.1362008469240057</v>
+        <v>0.1325197429530866</v>
       </c>
       <c r="W38">
-        <v>0.1024465795548129</v>
+        <v>0.1028831584857639</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.932882513178121</v>
+        <v>0.9076694722814149</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08885771227367879</v>
+        <v>0.08958571227367879</v>
       </c>
       <c r="C39">
-        <v>13267.24753681334</v>
+        <v>12513.6217989202</v>
       </c>
       <c r="D39">
-        <v>25626.51853681334</v>
+        <v>25310.9757989202</v>
       </c>
       <c r="E39">
-        <v>1240.571000000002</v>
+        <v>1678.654000000002</v>
       </c>
       <c r="F39">
-        <v>16209.071</v>
+        <v>16647.154</v>
       </c>
       <c r="G39">
         <v>3849.8</v>
@@ -4491,37 +4491,37 @@
         <v>1744.9</v>
       </c>
       <c r="M39">
-        <v>1922.3958206</v>
+        <v>1974.3524644</v>
       </c>
       <c r="N39">
-        <v>-177.4958206000003</v>
+        <v>-229.4524644000003</v>
       </c>
       <c r="O39">
-        <v>-25.91438980760005</v>
+        <v>-33.50005980240004</v>
       </c>
       <c r="P39">
-        <v>-151.5814307924003</v>
+        <v>-195.9524045976002</v>
       </c>
       <c r="Q39">
-        <v>2642.3185692076</v>
+        <v>2597.9475954024</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08062054545070815</v>
+        <v>0.08118216715152601</v>
       </c>
       <c r="T39">
-        <v>0.8041696408939526</v>
+        <v>0.8171401189728873</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.1325197429530866</v>
+        <v>0.1290323812964264</v>
       </c>
       <c r="W39">
-        <v>0.1028831584857639</v>
+        <v>0.1032967595782438</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9076694722814149</v>
+        <v>0.8837834335371673</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08958571227367879</v>
+        <v>0.09031371227367879</v>
       </c>
       <c r="C40">
-        <v>12513.6217989202</v>
+        <v>11767.67218347413</v>
       </c>
       <c r="D40">
-        <v>25310.9757989202</v>
+        <v>25003.10918347413</v>
       </c>
       <c r="E40">
-        <v>1678.654000000002</v>
+        <v>2116.737000000001</v>
       </c>
       <c r="F40">
-        <v>16647.154</v>
+        <v>17085.237</v>
       </c>
       <c r="G40">
         <v>3849.8</v>
@@ -4573,37 +4573,37 @@
         <v>1744.9</v>
       </c>
       <c r="M40">
-        <v>1974.3524644</v>
+        <v>2026.3091082</v>
       </c>
       <c r="N40">
-        <v>-229.4524644000003</v>
+        <v>-281.4091082000002</v>
       </c>
       <c r="O40">
-        <v>-33.50005980240004</v>
+        <v>-41.08572979720003</v>
       </c>
       <c r="P40">
-        <v>-195.9524045976002</v>
+        <v>-240.3233784028002</v>
       </c>
       <c r="Q40">
-        <v>2597.9475954024</v>
+        <v>2553.5766215972</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08118216715152601</v>
+        <v>0.08176220267860021</v>
       </c>
       <c r="T40">
-        <v>0.8171401189728873</v>
+        <v>0.8305358586281805</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.1290323812964264</v>
+        <v>0.1257238586990821</v>
       </c>
       <c r="W40">
-        <v>0.1032967595782438</v>
+        <v>0.1036891503582889</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8837834335371673</v>
+        <v>0.861122319856727</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09031371227367879</v>
+        <v>0.0910417122736788</v>
       </c>
       <c r="C41">
-        <v>11767.67218347413</v>
+        <v>11029.12195410281</v>
       </c>
       <c r="D41">
-        <v>25003.10918347413</v>
+        <v>24702.64195410281</v>
       </c>
       <c r="E41">
-        <v>2116.737000000001</v>
+        <v>2554.820000000003</v>
       </c>
       <c r="F41">
-        <v>17085.237</v>
+        <v>17523.32</v>
       </c>
       <c r="G41">
         <v>3849.8</v>
@@ -4655,37 +4655,37 @@
         <v>1744.9</v>
       </c>
       <c r="M41">
-        <v>2026.3091082</v>
+        <v>2078.265752000001</v>
       </c>
       <c r="N41">
-        <v>-281.4091082000002</v>
+        <v>-333.3657520000006</v>
       </c>
       <c r="O41">
-        <v>-41.08572979720003</v>
+        <v>-48.67139979200009</v>
       </c>
       <c r="P41">
-        <v>-240.3233784028002</v>
+        <v>-284.6943522080005</v>
       </c>
       <c r="Q41">
-        <v>2553.5766215972</v>
+        <v>2509.205647792</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08176220267860021</v>
+        <v>0.08236157272324356</v>
       </c>
       <c r="T41">
-        <v>0.8305358586281805</v>
+        <v>0.8443781229386502</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.1257238586990821</v>
+        <v>0.1225807622316051</v>
       </c>
       <c r="W41">
-        <v>0.1036891503582889</v>
+        <v>0.1040619215993316</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.861122319856727</v>
+        <v>0.8395942618603087</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0910417122736788</v>
+        <v>0.09176971227367881</v>
       </c>
       <c r="C42">
-        <v>11029.12195410281</v>
+        <v>10297.70751885428</v>
       </c>
       <c r="D42">
-        <v>24702.64195410281</v>
+        <v>24409.31051885428</v>
       </c>
       <c r="E42">
-        <v>2554.820000000003</v>
+        <v>2992.903000000002</v>
       </c>
       <c r="F42">
-        <v>17523.32</v>
+        <v>17961.403</v>
       </c>
       <c r="G42">
         <v>3849.8</v>
@@ -4737,37 +4737,37 @@
         <v>1744.9</v>
       </c>
       <c r="M42">
-        <v>2078.265752000001</v>
+        <v>2130.2223958</v>
       </c>
       <c r="N42">
-        <v>-333.3657520000006</v>
+        <v>-385.3223958000003</v>
       </c>
       <c r="O42">
-        <v>-48.67139979200009</v>
+        <v>-56.25706978680005</v>
       </c>
       <c r="P42">
-        <v>-284.6943522080005</v>
+        <v>-329.0653260132003</v>
       </c>
       <c r="Q42">
-        <v>2509.205647792</v>
+        <v>2464.8346739868</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08236157272324356</v>
+        <v>0.08298126039651887</v>
       </c>
       <c r="T42">
-        <v>0.8443781229386502</v>
+        <v>0.8586896165477799</v>
       </c>
       <c r="U42">
         <v>0.1186</v>
       </c>
       <c r="V42">
-        <v>0.1225807622316051</v>
+        <v>0.1195909875430294</v>
       </c>
       <c r="W42">
-        <v>0.1040619215993316</v>
+        <v>0.1044165088773967</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8395942618603087</v>
+        <v>0.8191163530344476</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09176971227367881</v>
+        <v>0.1274847333640202</v>
       </c>
       <c r="C43">
-        <v>10297.70751885428</v>
+        <v>874.3314994079883</v>
       </c>
       <c r="D43">
-        <v>24409.31051885428</v>
+        <v>15424.01749940799</v>
       </c>
       <c r="E43">
-        <v>2992.903000000002</v>
+        <v>3430.986000000004</v>
       </c>
       <c r="F43">
-        <v>17961.403</v>
+        <v>18399.486</v>
       </c>
       <c r="G43">
         <v>3849.8</v>
@@ -4819,45 +4819,45 @@
         <v>1744.9</v>
       </c>
       <c r="M43">
-        <v>2130.2223958</v>
+        <v>3694.616788800001</v>
       </c>
       <c r="N43">
-        <v>-385.3223958000003</v>
+        <v>-1949.716788800001</v>
       </c>
       <c r="O43">
-        <v>-56.25706978680005</v>
+        <v>-284.6586511648001</v>
       </c>
       <c r="P43">
-        <v>-329.0653260132003</v>
+        <v>-1665.058137635201</v>
       </c>
       <c r="Q43">
-        <v>2464.8346739868</v>
+        <v>1128.841862364799</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08298126039651887</v>
+        <v>0.08442062883497851</v>
       </c>
       <c r="T43">
-        <v>0.8586896165477799</v>
+        <v>0.8919313818701736</v>
       </c>
       <c r="U43">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1195909875430294</v>
+        <v>0.06895313223614287</v>
       </c>
       <c r="W43">
-        <v>0.1044165088773967</v>
+        <v>0.1869542110469825</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8191163530344476</v>
+        <v>0.4722817276448142</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1274847333640202</v>
+        <v>0.1290347333640202</v>
       </c>
       <c r="C44">
-        <v>874.3314994079919</v>
+        <v>193.7149930583291</v>
       </c>
       <c r="D44">
-        <v>15424.01749940799</v>
+        <v>15181.48399305833</v>
       </c>
       <c r="E44">
-        <v>3430.986000000001</v>
+        <v>3869.069</v>
       </c>
       <c r="F44">
-        <v>18399.486</v>
+        <v>18837.569</v>
       </c>
       <c r="G44">
         <v>3849.8</v>
@@ -4901,37 +4901,37 @@
         <v>1744.9</v>
       </c>
       <c r="M44">
-        <v>3694.6167888</v>
+        <v>3782.5838552</v>
       </c>
       <c r="N44">
-        <v>-1949.7167888</v>
+        <v>-2037.6838552</v>
       </c>
       <c r="O44">
-        <v>-284.6586511648001</v>
+        <v>-297.5018428592</v>
       </c>
       <c r="P44">
-        <v>-1665.0581376352</v>
+        <v>-1740.1820123408</v>
       </c>
       <c r="Q44">
-        <v>1128.8418623648</v>
+        <v>1053.7179876592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08442062883497851</v>
+        <v>0.08509818372682024</v>
       </c>
       <c r="T44">
-        <v>0.8919313818701735</v>
+        <v>0.907579300850352</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06895313223614287</v>
+        <v>0.06734957102134886</v>
       </c>
       <c r="W44">
-        <v>0.1869542110469825</v>
+        <v>0.1872762061389132</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4722817276448142</v>
+        <v>0.4612984316530745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1290347333640202</v>
+        <v>0.1305847333640202</v>
       </c>
       <c r="C45">
-        <v>193.7149930583291</v>
+        <v>-479.3922023165542</v>
       </c>
       <c r="D45">
-        <v>15181.48399305833</v>
+        <v>14946.45979768345</v>
       </c>
       <c r="E45">
-        <v>3869.069</v>
+        <v>4307.152000000002</v>
       </c>
       <c r="F45">
-        <v>18837.569</v>
+        <v>19275.652</v>
       </c>
       <c r="G45">
         <v>3849.8</v>
@@ -4983,37 +4983,37 @@
         <v>1744.9</v>
       </c>
       <c r="M45">
-        <v>3782.5838552</v>
+        <v>3870.5509216</v>
       </c>
       <c r="N45">
-        <v>-2037.6838552</v>
+        <v>-2125.6509216</v>
       </c>
       <c r="O45">
-        <v>-297.5018428592</v>
+        <v>-310.3450345536</v>
       </c>
       <c r="P45">
-        <v>-1740.1820123408</v>
+        <v>-1815.3058870464</v>
       </c>
       <c r="Q45">
-        <v>1053.7179876592</v>
+        <v>978.5941129535997</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08509818372682024</v>
+        <v>0.08579993700765631</v>
       </c>
       <c r="T45">
-        <v>0.907579300850352</v>
+        <v>0.9237860740798227</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.06734957102134886</v>
+        <v>0.06581889895268184</v>
       </c>
       <c r="W45">
-        <v>0.1872762061389132</v>
+        <v>0.1875835650903015</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4612984316530745</v>
+        <v>0.4508143763882319</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1305847333640202</v>
+        <v>0.1321347333640202</v>
       </c>
       <c r="C46">
-        <v>-479.3922023165542</v>
+        <v>-1145.333524364429</v>
       </c>
       <c r="D46">
-        <v>14946.45979768345</v>
+        <v>14718.60147563557</v>
       </c>
       <c r="E46">
-        <v>4307.152000000002</v>
+        <v>4745.235000000001</v>
       </c>
       <c r="F46">
-        <v>19275.652</v>
+        <v>19713.735</v>
       </c>
       <c r="G46">
         <v>3849.8</v>
@@ -5065,37 +5065,37 @@
         <v>1744.9</v>
       </c>
       <c r="M46">
-        <v>3870.5509216</v>
+        <v>3958.517988</v>
       </c>
       <c r="N46">
-        <v>-2125.6509216</v>
+        <v>-2213.617988</v>
       </c>
       <c r="O46">
-        <v>-310.3450345536</v>
+        <v>-323.188226248</v>
       </c>
       <c r="P46">
-        <v>-1815.3058870464</v>
+        <v>-1890.429761752</v>
       </c>
       <c r="Q46">
-        <v>978.5941129535997</v>
+        <v>903.470238248</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08579993700765631</v>
+        <v>0.08652720858961371</v>
       </c>
       <c r="T46">
-        <v>0.9237860740798227</v>
+        <v>0.9405821845176376</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.06581889895268184</v>
+        <v>0.06435625675373335</v>
       </c>
       <c r="W46">
-        <v>0.1875835650903015</v>
+        <v>0.1878772636438504</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4508143763882319</v>
+        <v>0.4407962791351601</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1321347333640202</v>
+        <v>0.1336847333640202</v>
       </c>
       <c r="C47">
-        <v>-1145.333524364429</v>
+        <v>-1804.431782425261</v>
       </c>
       <c r="D47">
-        <v>14718.60147563557</v>
+        <v>14497.58621757474</v>
       </c>
       <c r="E47">
-        <v>4745.235000000001</v>
+        <v>5183.318000000003</v>
       </c>
       <c r="F47">
-        <v>19713.735</v>
+        <v>20151.818</v>
       </c>
       <c r="G47">
         <v>3849.8</v>
@@ -5147,37 +5147,37 @@
         <v>1744.9</v>
       </c>
       <c r="M47">
-        <v>3958.517988</v>
+        <v>4046.485054400001</v>
       </c>
       <c r="N47">
-        <v>-2213.617988</v>
+        <v>-2301.5850544</v>
       </c>
       <c r="O47">
-        <v>-323.188226248</v>
+        <v>-336.0314179424</v>
       </c>
       <c r="P47">
-        <v>-1890.429761752</v>
+        <v>-1965.553636457601</v>
       </c>
       <c r="Q47">
-        <v>903.470238248</v>
+        <v>828.3463635423996</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08652720858961371</v>
+        <v>0.08728141615608803</v>
       </c>
       <c r="T47">
-        <v>0.9405821845176376</v>
+        <v>0.9580003731198161</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.06435625675373335</v>
+        <v>0.06295720769386959</v>
       </c>
       <c r="W47">
-        <v>0.1878772636438504</v>
+        <v>0.188158192695071</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4407962791351601</v>
+        <v>0.4312137513278739</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1336847333640202</v>
+        <v>0.1352347333640202</v>
       </c>
       <c r="C48">
-        <v>-1804.431782425261</v>
+        <v>-2456.990683397296</v>
       </c>
       <c r="D48">
-        <v>14497.58621757474</v>
+        <v>14283.11031660271</v>
       </c>
       <c r="E48">
-        <v>5183.318000000003</v>
+        <v>5621.401000000002</v>
       </c>
       <c r="F48">
-        <v>20151.818</v>
+        <v>20589.901</v>
       </c>
       <c r="G48">
         <v>3849.8</v>
@@ -5229,37 +5229,37 @@
         <v>1744.9</v>
       </c>
       <c r="M48">
-        <v>4046.485054400001</v>
+        <v>4134.452120800001</v>
       </c>
       <c r="N48">
-        <v>-2301.5850544</v>
+        <v>-2389.5521208</v>
       </c>
       <c r="O48">
-        <v>-336.0314179424</v>
+        <v>-348.8746096368001</v>
       </c>
       <c r="P48">
-        <v>-1965.553636457601</v>
+        <v>-2040.677511163201</v>
       </c>
       <c r="Q48">
-        <v>828.3463635423996</v>
+        <v>753.2224888367996</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08728141615608803</v>
+        <v>0.08806408438544819</v>
       </c>
       <c r="T48">
-        <v>0.9580003731198161</v>
+        <v>0.9760758518579259</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.06295720769386959</v>
+        <v>0.06161769263655321</v>
       </c>
       <c r="W48">
-        <v>0.188158192695071</v>
+        <v>0.1884271673185801</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4312137513278739</v>
+        <v>0.4220389906613233</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1352347333640202</v>
+        <v>0.1367847333640202</v>
       </c>
       <c r="C49">
-        <v>-2456.990683397296</v>
+        <v>-3103.296224136473</v>
       </c>
       <c r="D49">
-        <v>14283.11031660271</v>
+        <v>14074.88777586353</v>
       </c>
       <c r="E49">
-        <v>5621.401000000002</v>
+        <v>6059.484000000004</v>
       </c>
       <c r="F49">
-        <v>20589.901</v>
+        <v>21027.984</v>
       </c>
       <c r="G49">
         <v>3849.8</v>
@@ -5311,37 +5311,37 @@
         <v>1744.9</v>
       </c>
       <c r="M49">
-        <v>4134.452120800001</v>
+        <v>4222.419187200001</v>
       </c>
       <c r="N49">
-        <v>-2389.5521208</v>
+        <v>-2477.519187200001</v>
       </c>
       <c r="O49">
-        <v>-348.8746096368001</v>
+        <v>-361.7178013312001</v>
       </c>
       <c r="P49">
-        <v>-2040.677511163201</v>
+        <v>-2115.801385868801</v>
       </c>
       <c r="Q49">
-        <v>753.2224888367996</v>
+        <v>678.0986141311992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08806408438544819</v>
+        <v>0.08887685523901451</v>
       </c>
       <c r="T49">
-        <v>0.9760758518579259</v>
+        <v>0.9948465413167321</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.06161769263655321</v>
+        <v>0.06033399070662501</v>
       </c>
       <c r="W49">
-        <v>0.1884271673185801</v>
+        <v>0.1886849346661097</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4220389906613233</v>
+        <v>0.4132465116892124</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1367847333640202</v>
+        <v>0.1383347333640202</v>
       </c>
       <c r="C50">
-        <v>-3103.296224136469</v>
+        <v>-3743.617963813493</v>
       </c>
       <c r="D50">
-        <v>14074.88777586353</v>
+        <v>13872.64903618651</v>
       </c>
       <c r="E50">
-        <v>6059.484</v>
+        <v>6497.567000000003</v>
       </c>
       <c r="F50">
-        <v>21027.984</v>
+        <v>21466.067</v>
       </c>
       <c r="G50">
         <v>3849.8</v>
@@ -5393,37 +5393,37 @@
         <v>1744.9</v>
       </c>
       <c r="M50">
-        <v>4222.4191872</v>
+        <v>4310.386253600001</v>
       </c>
       <c r="N50">
-        <v>-2477.5191872</v>
+        <v>-2565.486253600001</v>
       </c>
       <c r="O50">
-        <v>-361.7178013312</v>
+        <v>-374.5609930256001</v>
       </c>
       <c r="P50">
-        <v>-2115.8013858688</v>
+        <v>-2190.9252605744</v>
       </c>
       <c r="Q50">
-        <v>678.0986141312001</v>
+        <v>602.9747394255996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08887685523901451</v>
+        <v>0.08972149945938733</v>
       </c>
       <c r="T50">
-        <v>0.9948465413167321</v>
+        <v>1.014353336244511</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.06033399070662502</v>
+        <v>0.05910268477383675</v>
       </c>
       <c r="W50">
-        <v>0.1886849346661097</v>
+        <v>0.1889321808974136</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4132465116892126</v>
+        <v>0.4048129094098408</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1383347333640202</v>
+        <v>0.1398847333640202</v>
       </c>
       <c r="C51">
-        <v>-3743.617963813493</v>
+        <v>-4378.210188131572</v>
       </c>
       <c r="D51">
-        <v>13872.64903618651</v>
+        <v>13676.13981186843</v>
       </c>
       <c r="E51">
-        <v>6497.567000000003</v>
+        <v>6935.650000000001</v>
       </c>
       <c r="F51">
-        <v>21466.067</v>
+        <v>21904.15</v>
       </c>
       <c r="G51">
         <v>3849.8</v>
@@ -5475,37 +5475,37 @@
         <v>1744.9</v>
       </c>
       <c r="M51">
-        <v>4310.386253600001</v>
+        <v>4398.35332</v>
       </c>
       <c r="N51">
-        <v>-2565.486253600001</v>
+        <v>-2653.45332</v>
       </c>
       <c r="O51">
-        <v>-374.5609930256001</v>
+        <v>-387.40418472</v>
       </c>
       <c r="P51">
-        <v>-2190.9252605744</v>
+        <v>-2266.04913528</v>
       </c>
       <c r="Q51">
-        <v>602.9747394255996</v>
+        <v>527.8508647200001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08972149945938733</v>
+        <v>0.09059992944857509</v>
       </c>
       <c r="T51">
-        <v>1.014353336244511</v>
+        <v>1.034640402969401</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05910268477383675</v>
+        <v>0.05792063107836002</v>
       </c>
       <c r="W51">
-        <v>0.1889321808974136</v>
+        <v>0.1891695372794653</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4048129094098408</v>
+        <v>0.396716651221644</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1398847333640202</v>
+        <v>0.1414347333640202</v>
       </c>
       <c r="C52">
-        <v>-4378.210188131572</v>
+        <v>-5007.312975977755</v>
       </c>
       <c r="D52">
-        <v>13676.13981186843</v>
+        <v>13485.12002402224</v>
       </c>
       <c r="E52">
-        <v>6935.650000000001</v>
+        <v>7373.733</v>
       </c>
       <c r="F52">
-        <v>21904.15</v>
+        <v>22342.233</v>
       </c>
       <c r="G52">
         <v>3849.8</v>
@@ -5557,37 +5557,37 @@
         <v>1744.9</v>
       </c>
       <c r="M52">
-        <v>4398.35332</v>
+        <v>4486.3203864</v>
       </c>
       <c r="N52">
-        <v>-2653.45332</v>
+        <v>-2741.4203864</v>
       </c>
       <c r="O52">
-        <v>-387.40418472</v>
+        <v>-400.2473764143999</v>
       </c>
       <c r="P52">
-        <v>-2266.04913528</v>
+        <v>-2341.173009985599</v>
       </c>
       <c r="Q52">
-        <v>527.8508647200001</v>
+        <v>452.7269900144006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09059992944857509</v>
+        <v>0.09151421372303579</v>
       </c>
       <c r="T52">
-        <v>1.034640402969401</v>
+        <v>1.055755513234083</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05792063107836002</v>
+        <v>0.05678493242976473</v>
       </c>
       <c r="W52">
-        <v>0.1891695372794653</v>
+        <v>0.1893975855681033</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.396716651221644</v>
+        <v>0.388937893354553</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1414347333640202</v>
+        <v>0.1429847333640202</v>
       </c>
       <c r="C53">
-        <v>-5007.312975977755</v>
+        <v>-5631.153177915636</v>
       </c>
       <c r="D53">
-        <v>13485.12002402224</v>
+        <v>13299.36282208437</v>
       </c>
       <c r="E53">
-        <v>7373.733</v>
+        <v>7811.816000000003</v>
       </c>
       <c r="F53">
-        <v>22342.233</v>
+        <v>22780.316</v>
       </c>
       <c r="G53">
         <v>3849.8</v>
@@ -5639,37 +5639,37 @@
         <v>1744.9</v>
       </c>
       <c r="M53">
-        <v>4486.3203864</v>
+        <v>4574.2874528</v>
       </c>
       <c r="N53">
-        <v>-2741.4203864</v>
+        <v>-2829.3874528</v>
       </c>
       <c r="O53">
-        <v>-400.2473764143999</v>
+        <v>-413.0905681088</v>
       </c>
       <c r="P53">
-        <v>-2341.173009985599</v>
+        <v>-2416.2968846912</v>
       </c>
       <c r="Q53">
-        <v>452.7269900144006</v>
+        <v>377.6031153088002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09151421372303579</v>
+        <v>0.09246659317559905</v>
       </c>
       <c r="T53">
-        <v>1.055755513234083</v>
+        <v>1.077750419759793</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05678493242976473</v>
+        <v>0.0556929144984231</v>
       </c>
       <c r="W53">
-        <v>0.1893975855681033</v>
+        <v>0.1896168627687166</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.388937893354553</v>
+        <v>0.38145831848235</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1429847333640202</v>
+        <v>0.1445347333640202</v>
       </c>
       <c r="C54">
-        <v>-5631.153177915636</v>
+        <v>-6249.945314904726</v>
       </c>
       <c r="D54">
-        <v>13299.36282208437</v>
+        <v>13118.65368509527</v>
       </c>
       <c r="E54">
-        <v>7811.816000000003</v>
+        <v>8249.899000000001</v>
       </c>
       <c r="F54">
-        <v>22780.316</v>
+        <v>23218.399</v>
       </c>
       <c r="G54">
         <v>3849.8</v>
@@ -5721,37 +5721,37 @@
         <v>1744.9</v>
       </c>
       <c r="M54">
-        <v>4574.2874528</v>
+        <v>4662.254519200001</v>
       </c>
       <c r="N54">
-        <v>-2829.3874528</v>
+        <v>-2917.354519200001</v>
       </c>
       <c r="O54">
-        <v>-413.0905681088</v>
+        <v>-425.9337598032001</v>
       </c>
       <c r="P54">
-        <v>-2416.2968846912</v>
+        <v>-2491.4207593968</v>
       </c>
       <c r="Q54">
-        <v>377.6031153088002</v>
+        <v>302.4792406031997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09246659317559905</v>
+        <v>0.09345949941337775</v>
       </c>
       <c r="T54">
-        <v>1.077750419759793</v>
+        <v>1.100681279754682</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.0556929144984231</v>
+        <v>0.05464210479090568</v>
       </c>
       <c r="W54">
-        <v>0.1896168627687166</v>
+        <v>0.1898278653579862</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.38145831848235</v>
+        <v>0.374260991718532</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1445347333640202</v>
+        <v>0.1460847333640202</v>
       </c>
       <c r="C55">
-        <v>-6249.945314904726</v>
+        <v>-6863.89240473228</v>
       </c>
       <c r="D55">
-        <v>13118.65368509527</v>
+        <v>12942.78959526772</v>
       </c>
       <c r="E55">
-        <v>8249.899000000001</v>
+        <v>8687.982000000004</v>
       </c>
       <c r="F55">
-        <v>23218.399</v>
+        <v>23656.482</v>
       </c>
       <c r="G55">
         <v>3849.8</v>
@@ -5803,37 +5803,37 @@
         <v>1744.9</v>
       </c>
       <c r="M55">
-        <v>4662.254519200001</v>
+        <v>4750.221585600001</v>
       </c>
       <c r="N55">
-        <v>-2917.354519200001</v>
+        <v>-3005.321585600001</v>
       </c>
       <c r="O55">
-        <v>-425.9337598032001</v>
+        <v>-438.7769514976001</v>
       </c>
       <c r="P55">
-        <v>-2491.4207593968</v>
+        <v>-2566.544634102401</v>
       </c>
       <c r="Q55">
-        <v>302.4792406031997</v>
+        <v>227.3553658975993</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09345949941337775</v>
+        <v>0.09449557548758161</v>
       </c>
       <c r="T55">
-        <v>1.100681279754682</v>
+        <v>1.124609133662393</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.05464210479090568</v>
+        <v>0.05363021396144445</v>
       </c>
       <c r="W55">
-        <v>0.1898278653579862</v>
+        <v>0.190031053036542</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.374260991718532</v>
+        <v>0.3673302326126333</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1460847333640202</v>
+        <v>0.1476347333640202</v>
       </c>
       <c r="C56">
-        <v>-6863.89240473228</v>
+        <v>-7473.186722851293</v>
       </c>
       <c r="D56">
-        <v>12942.78959526772</v>
+        <v>12771.57827714871</v>
       </c>
       <c r="E56">
-        <v>8687.982000000004</v>
+        <v>9126.065000000002</v>
       </c>
       <c r="F56">
-        <v>23656.482</v>
+        <v>24094.565</v>
       </c>
       <c r="G56">
         <v>3849.8</v>
@@ -5885,37 +5885,37 @@
         <v>1744.9</v>
       </c>
       <c r="M56">
-        <v>4750.221585600001</v>
+        <v>4838.188652000001</v>
       </c>
       <c r="N56">
-        <v>-3005.321585600001</v>
+        <v>-3093.288652000001</v>
       </c>
       <c r="O56">
-        <v>-438.7769514976001</v>
+        <v>-451.6201431920001</v>
       </c>
       <c r="P56">
-        <v>-2566.544634102401</v>
+        <v>-2641.668508808001</v>
       </c>
       <c r="Q56">
-        <v>227.3553658975993</v>
+        <v>152.2314911919993</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09449557548758161</v>
+        <v>0.09557769938730565</v>
       </c>
       <c r="T56">
-        <v>1.124609133662393</v>
+        <v>1.14960044774378</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.05363021396144445</v>
+        <v>0.05265511916214546</v>
       </c>
       <c r="W56">
-        <v>0.190031053036542</v>
+        <v>0.1902268520722412</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3673302326126333</v>
+        <v>0.3606515011105854</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1476347333640202</v>
+        <v>0.1491847333640202</v>
       </c>
       <c r="C57">
-        <v>-7473.186722851293</v>
+        <v>-8078.010503619334</v>
       </c>
       <c r="D57">
-        <v>12771.57827714871</v>
+        <v>12604.83749638067</v>
       </c>
       <c r="E57">
-        <v>9126.065000000002</v>
+        <v>9564.148000000005</v>
       </c>
       <c r="F57">
-        <v>24094.565</v>
+        <v>24532.648</v>
       </c>
       <c r="G57">
         <v>3849.8</v>
@@ -5967,37 +5967,37 @@
         <v>1744.9</v>
       </c>
       <c r="M57">
-        <v>4838.188652000001</v>
+        <v>4926.155718400001</v>
       </c>
       <c r="N57">
-        <v>-3093.288652000001</v>
+        <v>-3181.255718400001</v>
       </c>
       <c r="O57">
-        <v>-451.6201431920001</v>
+        <v>-464.4633348864002</v>
       </c>
       <c r="P57">
-        <v>-2641.668508808001</v>
+        <v>-2716.792383513601</v>
       </c>
       <c r="Q57">
-        <v>152.2314911919993</v>
+        <v>77.10761648639937</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09557769938730565</v>
+        <v>0.09670901073701713</v>
       </c>
       <c r="T57">
-        <v>1.14960044774378</v>
+        <v>1.175727730647047</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.05265511916214546</v>
+        <v>0.05171484917710716</v>
       </c>
       <c r="W57">
-        <v>0.1902268520722412</v>
+        <v>0.1904156582852369</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3606515011105854</v>
+        <v>0.3542112957336107</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1491847333640202</v>
+        <v>0.1507347333640202</v>
       </c>
       <c r="C58">
-        <v>-8078.010503619334</v>
+        <v>-8678.536587314557</v>
       </c>
       <c r="D58">
-        <v>12604.83749638067</v>
+        <v>12442.39441268545</v>
       </c>
       <c r="E58">
-        <v>9564.148000000005</v>
+        <v>10002.231</v>
       </c>
       <c r="F58">
-        <v>24532.648</v>
+        <v>24970.731</v>
       </c>
       <c r="G58">
         <v>3849.8</v>
@@ -6049,37 +6049,37 @@
         <v>1744.9</v>
       </c>
       <c r="M58">
-        <v>4926.155718400001</v>
+        <v>5014.122784800001</v>
       </c>
       <c r="N58">
-        <v>-3181.255718400001</v>
+        <v>-3269.222784800001</v>
       </c>
       <c r="O58">
-        <v>-464.4633348864002</v>
+        <v>-477.3065265808001</v>
       </c>
       <c r="P58">
-        <v>-2716.792383513601</v>
+        <v>-2791.916258219201</v>
       </c>
       <c r="Q58">
-        <v>77.10761648639937</v>
+        <v>1.983741780799392</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09670901073701713</v>
+        <v>0.09789294121927335</v>
       </c>
       <c r="T58">
-        <v>1.175727730647047</v>
+        <v>1.203070236010932</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05171484917710716</v>
+        <v>0.05080757112136844</v>
       </c>
       <c r="W58">
-        <v>0.1904156582852369</v>
+        <v>0.1905978397188292</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3542112957336107</v>
+        <v>0.3479970624751263</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1507347333640202</v>
+        <v>0.1522847333640202</v>
       </c>
       <c r="C59">
-        <v>-8678.536587314557</v>
+        <v>-9274.92901775843</v>
       </c>
       <c r="D59">
-        <v>12442.39441268545</v>
+        <v>12284.08498224158</v>
       </c>
       <c r="E59">
-        <v>10002.231</v>
+        <v>10440.31400000001</v>
       </c>
       <c r="F59">
-        <v>24970.731</v>
+        <v>25408.81400000001</v>
       </c>
       <c r="G59">
         <v>3849.8</v>
@@ -6131,37 +6131,37 @@
         <v>1744.9</v>
       </c>
       <c r="M59">
-        <v>5014.122784800001</v>
+        <v>5102.089851200001</v>
       </c>
       <c r="N59">
-        <v>-3269.222784800001</v>
+        <v>-3357.189851200001</v>
       </c>
       <c r="O59">
-        <v>-477.3065265808001</v>
+        <v>-490.1497182752001</v>
       </c>
       <c r="P59">
-        <v>-2791.916258219201</v>
+        <v>-2867.040132924801</v>
       </c>
       <c r="Q59">
-        <v>1.983741780799392</v>
+        <v>-73.14013292480104</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09789294121927335</v>
+        <v>0.09913324934354177</v>
       </c>
       <c r="T59">
-        <v>1.203070236010932</v>
+        <v>1.231714765439764</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05080757112136844</v>
+        <v>0.04993157851582759</v>
       </c>
       <c r="W59">
-        <v>0.1905978397188292</v>
+        <v>0.1907737390340218</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3479970624751263</v>
+        <v>0.3419971131221068</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1522847333640202</v>
+        <v>0.1538347333640202</v>
       </c>
       <c r="C60">
-        <v>-9274.929017758423</v>
+        <v>-9867.343594888785</v>
       </c>
       <c r="D60">
-        <v>12284.08498224158</v>
+        <v>12129.75340511121</v>
       </c>
       <c r="E60">
-        <v>10440.314</v>
+        <v>10878.397</v>
       </c>
       <c r="F60">
-        <v>25408.814</v>
+        <v>25846.897</v>
       </c>
       <c r="G60">
         <v>3849.8</v>
@@ -6213,37 +6213,37 @@
         <v>1744.9</v>
       </c>
       <c r="M60">
-        <v>5102.089851199999</v>
+        <v>5190.0569176</v>
       </c>
       <c r="N60">
-        <v>-3357.189851199999</v>
+        <v>-3445.1569176</v>
       </c>
       <c r="O60">
-        <v>-490.1497182751999</v>
+        <v>-502.9929099696</v>
       </c>
       <c r="P60">
-        <v>-2867.040132924799</v>
+        <v>-2942.1640076304</v>
       </c>
       <c r="Q60">
-        <v>-73.14013292479922</v>
+        <v>-148.2640076303996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09913324934354176</v>
+        <v>0.1004340603031403</v>
       </c>
       <c r="T60">
-        <v>1.231714765439764</v>
+        <v>1.261756588987075</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04993157851582761</v>
+        <v>0.04908528057488137</v>
       </c>
       <c r="W60">
-        <v>0.1907737390340218</v>
+        <v>0.1909436756605638</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.341997113122107</v>
+        <v>0.3362005518827492</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1538347333640202</v>
+        <v>0.1553847333640202</v>
       </c>
       <c r="C61">
-        <v>-9867.343594888785</v>
+        <v>-10455.92838619619</v>
       </c>
       <c r="D61">
-        <v>12129.75340511121</v>
+        <v>11979.25161380381</v>
       </c>
       <c r="E61">
-        <v>10878.397</v>
+        <v>11316.48</v>
       </c>
       <c r="F61">
-        <v>25846.897</v>
+        <v>26284.98</v>
       </c>
       <c r="G61">
         <v>3849.8</v>
@@ -6295,37 +6295,37 @@
         <v>1744.9</v>
       </c>
       <c r="M61">
-        <v>5190.0569176</v>
+        <v>5278.023984</v>
       </c>
       <c r="N61">
-        <v>-3445.1569176</v>
+        <v>-3533.123984</v>
       </c>
       <c r="O61">
-        <v>-502.9929099696</v>
+        <v>-515.836101664</v>
       </c>
       <c r="P61">
-        <v>-2942.1640076304</v>
+        <v>-3017.287882336</v>
       </c>
       <c r="Q61">
-        <v>-148.2640076303996</v>
+        <v>-223.3878823360001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1004340603031403</v>
+        <v>0.1017999118107188</v>
       </c>
       <c r="T61">
-        <v>1.261756588987075</v>
+        <v>1.293300503711752</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.04908528057488137</v>
+        <v>0.04826719256530002</v>
       </c>
       <c r="W61">
-        <v>0.1909436756605638</v>
+        <v>0.1911079477328878</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3362005518827492</v>
+        <v>0.33059720935137</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1553847333640202</v>
+        <v>0.1569347333640202</v>
       </c>
       <c r="C62">
-        <v>-10455.92838619619</v>
+        <v>-11040.82420055247</v>
       </c>
       <c r="D62">
-        <v>11979.25161380381</v>
+        <v>11832.43879944753</v>
       </c>
       <c r="E62">
-        <v>11316.48</v>
+        <v>11754.563</v>
       </c>
       <c r="F62">
-        <v>26284.98</v>
+        <v>26723.063</v>
       </c>
       <c r="G62">
         <v>3849.8</v>
@@ -6377,37 +6377,37 @@
         <v>1744.9</v>
       </c>
       <c r="M62">
-        <v>5278.023984</v>
+        <v>5365.991050400001</v>
       </c>
       <c r="N62">
-        <v>-3533.123984</v>
+        <v>-3621.091050400001</v>
       </c>
       <c r="O62">
-        <v>-515.836101664</v>
+        <v>-528.6792933584001</v>
       </c>
       <c r="P62">
-        <v>-3017.287882336</v>
+        <v>-3092.411757041601</v>
       </c>
       <c r="Q62">
-        <v>-223.3878823360001</v>
+        <v>-298.5117570416005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1017999118107188</v>
+        <v>0.1032358069853527</v>
       </c>
       <c r="T62">
-        <v>1.293300503711752</v>
+        <v>1.326462055088976</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04826719256530002</v>
+        <v>0.04747592711340985</v>
       </c>
       <c r="W62">
-        <v>0.1911079477328878</v>
+        <v>0.1912668338356273</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.33059720935137</v>
+        <v>0.3251775829685606</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1569347333640202</v>
+        <v>0.1584847333640202</v>
       </c>
       <c r="C63">
-        <v>-11040.82420055247</v>
+        <v>-11622.16502761887</v>
       </c>
       <c r="D63">
-        <v>11832.43879944753</v>
+        <v>11689.18097238113</v>
       </c>
       <c r="E63">
-        <v>11754.563</v>
+        <v>12192.646</v>
       </c>
       <c r="F63">
-        <v>26723.063</v>
+        <v>27161.146</v>
       </c>
       <c r="G63">
         <v>3849.8</v>
@@ -6459,37 +6459,37 @@
         <v>1744.9</v>
       </c>
       <c r="M63">
-        <v>5365.991050400001</v>
+        <v>5453.9581168</v>
       </c>
       <c r="N63">
-        <v>-3621.091050400001</v>
+        <v>-3709.0581168</v>
       </c>
       <c r="O63">
-        <v>-528.6792933584001</v>
+        <v>-541.5224850528</v>
       </c>
       <c r="P63">
-        <v>-3092.411757041601</v>
+        <v>-3167.535631747201</v>
       </c>
       <c r="Q63">
-        <v>-298.5117570416005</v>
+        <v>-373.6356317472005</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1032358069853527</v>
+        <v>0.1047472755902304</v>
       </c>
       <c r="T63">
-        <v>1.326462055088976</v>
+        <v>1.361368951275528</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04747592711340985</v>
+        <v>0.04671018635351615</v>
       </c>
       <c r="W63">
-        <v>0.1912668338356273</v>
+        <v>0.191420594580214</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3251775829685606</v>
+        <v>0.3199327832432612</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1584847333640202</v>
+        <v>0.1600347333640202</v>
       </c>
       <c r="C64">
-        <v>-11622.16502761887</v>
+        <v>-12200.07844571596</v>
       </c>
       <c r="D64">
-        <v>11689.18097238113</v>
+        <v>11549.35055428405</v>
       </c>
       <c r="E64">
-        <v>12192.646</v>
+        <v>12630.729</v>
       </c>
       <c r="F64">
-        <v>27161.146</v>
+        <v>27599.229</v>
       </c>
       <c r="G64">
         <v>3849.8</v>
@@ -6541,37 +6541,37 @@
         <v>1744.9</v>
       </c>
       <c r="M64">
-        <v>5453.9581168</v>
+        <v>5541.925183200001</v>
       </c>
       <c r="N64">
-        <v>-3709.0581168</v>
+        <v>-3797.025183200001</v>
       </c>
       <c r="O64">
-        <v>-541.5224850528</v>
+        <v>-554.3656767472</v>
       </c>
       <c r="P64">
-        <v>-3167.535631747201</v>
+        <v>-3242.659506452801</v>
       </c>
       <c r="Q64">
-        <v>-373.6356317472005</v>
+        <v>-448.7595064528009</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1047472755902304</v>
+        <v>0.1063404452007771</v>
       </c>
       <c r="T64">
-        <v>1.361368951275528</v>
+        <v>1.398162706715407</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.04671018635351615</v>
+        <v>0.04596875482409525</v>
       </c>
       <c r="W64">
-        <v>0.191420594580214</v>
+        <v>0.1915694740313217</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3199327832432612</v>
+        <v>0.3148544850965428</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1600347333640202</v>
+        <v>0.1615847333640202</v>
       </c>
       <c r="C65">
-        <v>-12200.07844571596</v>
+        <v>-12774.68600076501</v>
       </c>
       <c r="D65">
-        <v>11549.35055428405</v>
+        <v>11412.82599923499</v>
       </c>
       <c r="E65">
-        <v>12630.729</v>
+        <v>13068.812</v>
       </c>
       <c r="F65">
-        <v>27599.229</v>
+        <v>28037.312</v>
       </c>
       <c r="G65">
         <v>3849.8</v>
@@ -6623,37 +6623,37 @@
         <v>1744.9</v>
       </c>
       <c r="M65">
-        <v>5541.925183200001</v>
+        <v>5629.8922496</v>
       </c>
       <c r="N65">
-        <v>-3797.025183200001</v>
+        <v>-3884.9922496</v>
       </c>
       <c r="O65">
-        <v>-554.3656767472</v>
+        <v>-567.2088684416</v>
       </c>
       <c r="P65">
-        <v>-3242.659506452801</v>
+        <v>-3317.783381158401</v>
       </c>
       <c r="Q65">
-        <v>-448.7595064528009</v>
+        <v>-523.8833811584004</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1063404452007771</v>
+        <v>0.1080221242341321</v>
       </c>
       <c r="T65">
-        <v>1.398162706715407</v>
+        <v>1.437000559679724</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04596875482409525</v>
+        <v>0.04525049302996877</v>
       </c>
       <c r="W65">
-        <v>0.1915694740313217</v>
+        <v>0.1917137009995823</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3148544850965428</v>
+        <v>0.3099348837669094</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1615847333640202</v>
+        <v>0.1631347333640202</v>
       </c>
       <c r="C66">
-        <v>-12774.68600076501</v>
+        <v>-13346.10355866676</v>
       </c>
       <c r="D66">
-        <v>11412.82599923499</v>
+        <v>11279.49144133325</v>
       </c>
       <c r="E66">
-        <v>13068.812</v>
+        <v>13506.895</v>
       </c>
       <c r="F66">
-        <v>28037.312</v>
+        <v>28475.395</v>
       </c>
       <c r="G66">
         <v>3849.8</v>
@@ -6705,37 +6705,37 @@
         <v>1744.9</v>
       </c>
       <c r="M66">
-        <v>5629.8922496</v>
+        <v>5717.859316000001</v>
       </c>
       <c r="N66">
-        <v>-3884.9922496</v>
+        <v>-3972.959316000001</v>
       </c>
       <c r="O66">
-        <v>-567.2088684416</v>
+        <v>-580.0520601360001</v>
       </c>
       <c r="P66">
-        <v>-3317.783381158401</v>
+        <v>-3392.907255864001</v>
       </c>
       <c r="Q66">
-        <v>-523.8833811584004</v>
+        <v>-599.0072558640009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1080221242341321</v>
+        <v>0.1097998992122501</v>
       </c>
       <c r="T66">
-        <v>1.437000559679724</v>
+        <v>1.478057718527716</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.04525049302996877</v>
+        <v>0.04455433159873847</v>
       </c>
       <c r="W66">
-        <v>0.1917137009995823</v>
+        <v>0.1918534902149733</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3099348837669094</v>
+        <v>0.30516665478588</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1631347333640202</v>
+        <v>0.1646847333640202</v>
       </c>
       <c r="C67">
-        <v>-13346.10355866676</v>
+        <v>-13914.44163326444</v>
       </c>
       <c r="D67">
-        <v>11279.49144133325</v>
+        <v>11149.23636673556</v>
       </c>
       <c r="E67">
-        <v>13506.895</v>
+        <v>13944.978</v>
       </c>
       <c r="F67">
-        <v>28475.395</v>
+        <v>28913.478</v>
       </c>
       <c r="G67">
         <v>3849.8</v>
@@ -6787,37 +6787,37 @@
         <v>1744.9</v>
       </c>
       <c r="M67">
-        <v>5717.859316000001</v>
+        <v>5805.826382400001</v>
       </c>
       <c r="N67">
-        <v>-3972.959316000001</v>
+        <v>-4060.9263824</v>
       </c>
       <c r="O67">
-        <v>-580.0520601360001</v>
+        <v>-592.8952518304001</v>
       </c>
       <c r="P67">
-        <v>-3392.907255864001</v>
+        <v>-3468.0311305696</v>
       </c>
       <c r="Q67">
-        <v>-599.0072558640009</v>
+        <v>-674.1311305696004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1097998992122501</v>
+        <v>0.111682249189081</v>
       </c>
       <c r="T67">
-        <v>1.478057718527716</v>
+        <v>1.521530004366767</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.04455433159873847</v>
+        <v>0.04387926596845457</v>
       </c>
       <c r="W67">
-        <v>0.1918534902149733</v>
+        <v>0.1919890433935343</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.30516665478588</v>
+        <v>0.3005429175921546</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1646847333640202</v>
+        <v>0.1662347333640202</v>
       </c>
       <c r="C68">
-        <v>-13914.44163326444</v>
+        <v>-14479.80569184261</v>
       </c>
       <c r="D68">
-        <v>11149.23636673556</v>
+        <v>11021.95530815739</v>
       </c>
       <c r="E68">
-        <v>13944.978</v>
+        <v>14383.06100000001</v>
       </c>
       <c r="F68">
-        <v>28913.478</v>
+        <v>29351.56100000001</v>
       </c>
       <c r="G68">
         <v>3849.8</v>
@@ -6869,37 +6869,37 @@
         <v>1744.9</v>
       </c>
       <c r="M68">
-        <v>5805.826382400001</v>
+        <v>5893.793448800001</v>
       </c>
       <c r="N68">
-        <v>-4060.9263824</v>
+        <v>-4148.893448800001</v>
       </c>
       <c r="O68">
-        <v>-592.8952518304001</v>
+        <v>-605.7384435248001</v>
       </c>
       <c r="P68">
-        <v>-3468.0311305696</v>
+        <v>-3543.155005275201</v>
       </c>
       <c r="Q68">
-        <v>-674.1311305696004</v>
+        <v>-749.2550052752013</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.111682249189081</v>
+        <v>0.1136786809826895</v>
       </c>
       <c r="T68">
-        <v>1.521530004366767</v>
+        <v>1.567636974196063</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.04387926596845457</v>
+        <v>0.04322435155101494</v>
       </c>
       <c r="W68">
-        <v>0.1919890433935343</v>
+        <v>0.1921205502085562</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3005429175921546</v>
+        <v>0.2960572024042118</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1662347333640202</v>
+        <v>0.1677847333640202</v>
       </c>
       <c r="C69">
-        <v>-14479.80569184261</v>
+        <v>-15042.2964399364</v>
       </c>
       <c r="D69">
-        <v>11021.95530815739</v>
+        <v>10897.54756006361</v>
       </c>
       <c r="E69">
-        <v>14383.06100000001</v>
+        <v>14821.144</v>
       </c>
       <c r="F69">
-        <v>29351.56100000001</v>
+        <v>29789.644</v>
       </c>
       <c r="G69">
         <v>3849.8</v>
@@ -6951,37 +6951,37 @@
         <v>1744.9</v>
       </c>
       <c r="M69">
-        <v>5893.793448800001</v>
+        <v>5981.760515200001</v>
       </c>
       <c r="N69">
-        <v>-4148.893448800001</v>
+        <v>-4236.8605152</v>
       </c>
       <c r="O69">
-        <v>-605.7384435248001</v>
+        <v>-618.5816352191999</v>
       </c>
       <c r="P69">
-        <v>-3543.155005275201</v>
+        <v>-3618.2788799808</v>
       </c>
       <c r="Q69">
-        <v>-749.2550052752013</v>
+        <v>-824.3788799807999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1136786809826895</v>
+        <v>0.1157998897633986</v>
       </c>
       <c r="T69">
-        <v>1.567636974196063</v>
+        <v>1.61662562963969</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.04322435155101494</v>
+        <v>0.04258869932232354</v>
       </c>
       <c r="W69">
-        <v>0.1921205502085562</v>
+        <v>0.1922481891760774</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2960572024042118</v>
+        <v>0.2917034200159148</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1677847333640202</v>
+        <v>0.1693347333640202</v>
       </c>
       <c r="C70">
-        <v>-15042.2964399364</v>
+        <v>-15602.01008706771</v>
       </c>
       <c r="D70">
-        <v>10897.54756006361</v>
+        <v>10775.91691293229</v>
       </c>
       <c r="E70">
-        <v>14821.144</v>
+        <v>15259.22700000001</v>
       </c>
       <c r="F70">
-        <v>29789.644</v>
+        <v>30227.72700000001</v>
       </c>
       <c r="G70">
         <v>3849.8</v>
@@ -7033,37 +7033,37 @@
         <v>1744.9</v>
       </c>
       <c r="M70">
-        <v>5981.760515200001</v>
+        <v>6069.727581600001</v>
       </c>
       <c r="N70">
-        <v>-4236.8605152</v>
+        <v>-4324.8275816</v>
       </c>
       <c r="O70">
-        <v>-618.5816352191999</v>
+        <v>-631.4248269136</v>
       </c>
       <c r="P70">
-        <v>-3618.2788799808</v>
+        <v>-3693.4027546864</v>
       </c>
       <c r="Q70">
-        <v>-824.3788799807999</v>
+        <v>-899.5027546864003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1157998897633986</v>
+        <v>0.1180579507235082</v>
       </c>
       <c r="T70">
-        <v>1.61662562963969</v>
+        <v>1.668774843499035</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.04258869932232354</v>
+        <v>0.04197147179591305</v>
       </c>
       <c r="W70">
-        <v>0.1922481891760774</v>
+        <v>0.1923721284633806</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2917034200159148</v>
+        <v>0.2874758342185827</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1693347333640202</v>
+        <v>0.1708847333640202</v>
       </c>
       <c r="C71">
-        <v>-15602.01008706771</v>
+        <v>-16159.03859488221</v>
       </c>
       <c r="D71">
-        <v>10775.91691293229</v>
+        <v>10656.9714051178</v>
       </c>
       <c r="E71">
-        <v>15259.22700000001</v>
+        <v>15697.31</v>
       </c>
       <c r="F71">
-        <v>30227.72700000001</v>
+        <v>30665.81</v>
       </c>
       <c r="G71">
         <v>3849.8</v>
@@ -7115,37 +7115,37 @@
         <v>1744.9</v>
       </c>
       <c r="M71">
-        <v>6069.727581600001</v>
+        <v>6157.694648000002</v>
       </c>
       <c r="N71">
-        <v>-4324.8275816</v>
+        <v>-4412.794648000001</v>
       </c>
       <c r="O71">
-        <v>-631.4248269136</v>
+        <v>-644.2680186080001</v>
       </c>
       <c r="P71">
-        <v>-3693.4027546864</v>
+        <v>-3768.526629392001</v>
       </c>
       <c r="Q71">
-        <v>-899.5027546864003</v>
+        <v>-974.6266293920007</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1180579507235082</v>
+        <v>0.1204665490809585</v>
       </c>
       <c r="T71">
-        <v>1.668774843499035</v>
+        <v>1.724400671615669</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04197147179591305</v>
+        <v>0.04137187934168572</v>
       </c>
       <c r="W71">
-        <v>0.1923721284633806</v>
+        <v>0.1924925266281895</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2874758342185827</v>
+        <v>0.2833690365868886</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1708847333640202</v>
+        <v>0.1724347333640202</v>
       </c>
       <c r="C72">
-        <v>-16159.03859488221</v>
+        <v>-16713.46990903186</v>
       </c>
       <c r="D72">
-        <v>10656.9714051178</v>
+        <v>10540.62309096814</v>
       </c>
       <c r="E72">
-        <v>15697.31</v>
+        <v>16135.393</v>
       </c>
       <c r="F72">
-        <v>30665.81</v>
+        <v>31103.893</v>
       </c>
       <c r="G72">
         <v>3849.8</v>
@@ -7197,37 +7197,37 @@
         <v>1744.9</v>
       </c>
       <c r="M72">
-        <v>6157.694648000002</v>
+        <v>6245.661714400001</v>
       </c>
       <c r="N72">
-        <v>-4412.794648000001</v>
+        <v>-4500.761714400001</v>
       </c>
       <c r="O72">
-        <v>-644.2680186080001</v>
+        <v>-657.1112103024002</v>
       </c>
       <c r="P72">
-        <v>-3768.526629392001</v>
+        <v>-3843.650504097601</v>
       </c>
       <c r="Q72">
-        <v>-974.6266293920007</v>
+        <v>-1049.750504097601</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1204665490809585</v>
+        <v>0.123041257669957</v>
       </c>
       <c r="T72">
-        <v>1.724400671615669</v>
+        <v>1.783862763740348</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04137187934168572</v>
+        <v>0.04078917681574649</v>
       </c>
       <c r="W72">
-        <v>0.1924925266281895</v>
+        <v>0.1926095332953981</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2833690365868886</v>
+        <v>0.2793779233955238</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1724347333640202</v>
+        <v>0.1739847333640202</v>
       </c>
       <c r="C73">
-        <v>-16713.46990903186</v>
+        <v>-17265.38817603204</v>
       </c>
       <c r="D73">
-        <v>10540.62309096814</v>
+        <v>10426.78782396797</v>
       </c>
       <c r="E73">
-        <v>16135.393</v>
+        <v>16573.476</v>
       </c>
       <c r="F73">
-        <v>31103.893</v>
+        <v>31541.976</v>
       </c>
       <c r="G73">
         <v>3849.8</v>
@@ -7279,37 +7279,37 @@
         <v>1744.9</v>
       </c>
       <c r="M73">
-        <v>6245.6617144</v>
+        <v>6333.628780800001</v>
       </c>
       <c r="N73">
-        <v>-4500.7617144</v>
+        <v>-4588.7287808</v>
       </c>
       <c r="O73">
-        <v>-657.1112103023999</v>
+        <v>-669.9544019968</v>
       </c>
       <c r="P73">
-        <v>-3843.6505040976</v>
+        <v>-3918.7743788032</v>
       </c>
       <c r="Q73">
-        <v>-1049.7505040976</v>
+        <v>-1124.8743788032</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.123041257669957</v>
+        <v>0.1257998740153126</v>
       </c>
       <c r="T73">
-        <v>1.783862763740347</v>
+        <v>1.847572148159645</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04078917681574649</v>
+        <v>0.04022266047108335</v>
       </c>
       <c r="W73">
-        <v>0.1926095332953981</v>
+        <v>0.1927232897774065</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.279377923395524</v>
+        <v>0.275497674459475</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1739847333640202</v>
+        <v>0.1755347333640202</v>
       </c>
       <c r="C74">
-        <v>-17265.38817603204</v>
+        <v>-17814.87394621677</v>
       </c>
       <c r="D74">
-        <v>10426.78782396797</v>
+        <v>10315.38505378323</v>
       </c>
       <c r="E74">
-        <v>16573.476</v>
+        <v>17011.559</v>
       </c>
       <c r="F74">
-        <v>31541.976</v>
+        <v>31980.059</v>
       </c>
       <c r="G74">
         <v>3849.8</v>
@@ -7361,37 +7361,37 @@
         <v>1744.9</v>
       </c>
       <c r="M74">
-        <v>6333.628780800001</v>
+        <v>6421.5958472</v>
       </c>
       <c r="N74">
-        <v>-4588.7287808</v>
+        <v>-4676.695847200001</v>
       </c>
       <c r="O74">
-        <v>-669.9544019968</v>
+        <v>-682.7975936912001</v>
       </c>
       <c r="P74">
-        <v>-3918.7743788032</v>
+        <v>-3993.898253508801</v>
       </c>
       <c r="Q74">
-        <v>-1124.8743788032</v>
+        <v>-1199.998253508801</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1257998740153126</v>
+        <v>0.1287628323121761</v>
       </c>
       <c r="T74">
-        <v>1.847572148159645</v>
+        <v>1.916000746239632</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04022266047108335</v>
+        <v>0.0396716651221644</v>
       </c>
       <c r="W74">
-        <v>0.1927232897774065</v>
+        <v>0.1928339296434694</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.275497674459475</v>
+        <v>0.2717237337134547</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1755347333640202</v>
+        <v>0.1770847333640202</v>
       </c>
       <c r="C75">
-        <v>-17814.87394621677</v>
+        <v>-18362.00436382101</v>
       </c>
       <c r="D75">
-        <v>10315.38505378323</v>
+        <v>10206.33763617899</v>
       </c>
       <c r="E75">
-        <v>17011.559</v>
+        <v>17449.642</v>
       </c>
       <c r="F75">
-        <v>31980.059</v>
+        <v>32418.142</v>
       </c>
       <c r="G75">
         <v>3849.8</v>
@@ -7443,37 +7443,37 @@
         <v>1744.9</v>
       </c>
       <c r="M75">
-        <v>6421.5958472</v>
+        <v>6509.562913600001</v>
       </c>
       <c r="N75">
-        <v>-4676.695847200001</v>
+        <v>-4764.662913600001</v>
       </c>
       <c r="O75">
-        <v>-682.7975936912001</v>
+        <v>-695.6407853856001</v>
       </c>
       <c r="P75">
-        <v>-3993.898253508801</v>
+        <v>-4069.022128214401</v>
       </c>
       <c r="Q75">
-        <v>-1199.998253508801</v>
+        <v>-1275.122128214401</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1287628323121761</v>
+        <v>0.131953710478029</v>
       </c>
       <c r="T75">
-        <v>1.916000746239632</v>
+        <v>1.989693082633464</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0396716651221644</v>
+        <v>0.03913556153943245</v>
       </c>
       <c r="W75">
-        <v>0.1928339296434694</v>
+        <v>0.192941579242882</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2717237337134547</v>
+        <v>0.2680517913659756</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1770847333640202</v>
+        <v>0.1786347333640202</v>
       </c>
       <c r="C76">
-        <v>-18362.00436382101</v>
+        <v>-18906.85334513243</v>
       </c>
       <c r="D76">
-        <v>10206.33763617899</v>
+        <v>10099.57165486758</v>
       </c>
       <c r="E76">
-        <v>17449.642</v>
+        <v>17887.72500000001</v>
       </c>
       <c r="F76">
-        <v>32418.142</v>
+        <v>32856.22500000001</v>
       </c>
       <c r="G76">
         <v>3849.8</v>
@@ -7525,37 +7525,37 @@
         <v>1744.9</v>
       </c>
       <c r="M76">
-        <v>6509.562913600001</v>
+        <v>6597.529980000001</v>
       </c>
       <c r="N76">
-        <v>-4764.662913600001</v>
+        <v>-4852.629980000002</v>
       </c>
       <c r="O76">
-        <v>-695.6407853856001</v>
+        <v>-708.4839770800002</v>
       </c>
       <c r="P76">
-        <v>-4069.022128214401</v>
+        <v>-4144.146002920002</v>
       </c>
       <c r="Q76">
-        <v>-1275.122128214401</v>
+        <v>-1350.246002920002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.131953710478029</v>
+        <v>0.1353998588971502</v>
       </c>
       <c r="T76">
-        <v>1.989693082633464</v>
+        <v>2.069280805938803</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03913556153943245</v>
+        <v>0.03861375405224001</v>
       </c>
       <c r="W76">
-        <v>0.192941579242882</v>
+        <v>0.1930463581863102</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2680517913659756</v>
+        <v>0.2644777674810959</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1786347333640202</v>
+        <v>0.1801847333640202</v>
       </c>
       <c r="C77">
-        <v>-18906.85334513243</v>
+        <v>-19449.49174557737</v>
       </c>
       <c r="D77">
-        <v>10099.57165486758</v>
+        <v>9995.016254422631</v>
       </c>
       <c r="E77">
-        <v>17887.72500000001</v>
+        <v>18325.808</v>
       </c>
       <c r="F77">
-        <v>32856.22500000001</v>
+        <v>33294.308</v>
       </c>
       <c r="G77">
         <v>3849.8</v>
@@ -7607,37 +7607,37 @@
         <v>1744.9</v>
       </c>
       <c r="M77">
-        <v>6597.529980000001</v>
+        <v>6685.497046400001</v>
       </c>
       <c r="N77">
-        <v>-4852.629980000002</v>
+        <v>-4940.5970464</v>
       </c>
       <c r="O77">
-        <v>-708.4839770800002</v>
+        <v>-721.3271687744</v>
       </c>
       <c r="P77">
-        <v>-4144.146002920002</v>
+        <v>-4219.2698776256</v>
       </c>
       <c r="Q77">
-        <v>-1350.246002920002</v>
+        <v>-1425.3698776256</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1353998588971502</v>
+        <v>0.1391331863511981</v>
       </c>
       <c r="T77">
-        <v>2.069280805938803</v>
+        <v>2.155500839519587</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.03861375405224001</v>
+        <v>0.03810567834102633</v>
       </c>
       <c r="W77">
-        <v>0.1930463581863102</v>
+        <v>0.1931483797891219</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2644777674810959</v>
+        <v>0.2609977968563448</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1801847333640202</v>
+        <v>0.1817347333640202</v>
       </c>
       <c r="C78">
-        <v>-19449.49174557737</v>
+        <v>-19989.98751653467</v>
       </c>
       <c r="D78">
-        <v>9995.016254422631</v>
+        <v>9892.603483465331</v>
       </c>
       <c r="E78">
-        <v>18325.808</v>
+        <v>18763.891</v>
       </c>
       <c r="F78">
-        <v>33294.308</v>
+        <v>33732.391</v>
       </c>
       <c r="G78">
         <v>3849.8</v>
@@ -7689,37 +7689,37 @@
         <v>1744.9</v>
       </c>
       <c r="M78">
-        <v>6685.497046400001</v>
+        <v>6773.464112800001</v>
       </c>
       <c r="N78">
-        <v>-4940.5970464</v>
+        <v>-5028.564112800001</v>
       </c>
       <c r="O78">
-        <v>-721.3271687744</v>
+        <v>-734.1703604688</v>
       </c>
       <c r="P78">
-        <v>-4219.2698776256</v>
+        <v>-4294.393752331201</v>
       </c>
       <c r="Q78">
-        <v>-1425.3698776256</v>
+        <v>-1500.493752331201</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1391331863511981</v>
+        <v>0.1431911509751632</v>
       </c>
       <c r="T78">
-        <v>2.155500839519587</v>
+        <v>2.249218267324786</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03810567834102633</v>
+        <v>0.03761079940153247</v>
       </c>
       <c r="W78">
-        <v>0.1931483797891219</v>
+        <v>0.1932477514801723</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2609977968563448</v>
+        <v>0.2576082150789897</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1817347333640202</v>
+        <v>0.1832847333640202</v>
       </c>
       <c r="C79">
-        <v>-19989.98751653467</v>
+        <v>-20528.40585260656</v>
       </c>
       <c r="D79">
-        <v>9892.603483465331</v>
+        <v>9792.268147393446</v>
       </c>
       <c r="E79">
-        <v>18763.891</v>
+        <v>19201.974</v>
       </c>
       <c r="F79">
-        <v>33732.391</v>
+        <v>34170.474</v>
       </c>
       <c r="G79">
         <v>3849.8</v>
@@ -7771,37 +7771,37 @@
         <v>1744.9</v>
       </c>
       <c r="M79">
-        <v>6773.464112800001</v>
+        <v>6861.431179200001</v>
       </c>
       <c r="N79">
-        <v>-5028.564112800001</v>
+        <v>-5116.531179200001</v>
       </c>
       <c r="O79">
-        <v>-734.1703604688</v>
+        <v>-747.0135521632001</v>
       </c>
       <c r="P79">
-        <v>-4294.393752331201</v>
+        <v>-4369.517627036801</v>
       </c>
       <c r="Q79">
-        <v>-1500.493752331201</v>
+        <v>-1575.617627036801</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1431911509751632</v>
+        <v>0.1476180214740343</v>
       </c>
       <c r="T79">
-        <v>2.249218267324786</v>
+        <v>2.351455461294094</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.03761079940153247</v>
+        <v>0.0371286096656154</v>
       </c>
       <c r="W79">
-        <v>0.1932477514801723</v>
+        <v>0.1933445751791444</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2576082150789897</v>
+        <v>0.2543055456548999</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1832847333640202</v>
+        <v>0.1848347333640202</v>
       </c>
       <c r="C80">
-        <v>-20528.40585260656</v>
+        <v>-21064.80933001745</v>
       </c>
       <c r="D80">
-        <v>9792.268147393446</v>
+        <v>9693.947669982554</v>
       </c>
       <c r="E80">
-        <v>19201.974</v>
+        <v>19640.057</v>
       </c>
       <c r="F80">
-        <v>34170.474</v>
+        <v>34608.557</v>
       </c>
       <c r="G80">
         <v>3849.8</v>
@@ -7853,37 +7853,37 @@
         <v>1744.9</v>
       </c>
       <c r="M80">
-        <v>6861.431179200001</v>
+        <v>6949.3982456</v>
       </c>
       <c r="N80">
-        <v>-5116.531179200001</v>
+        <v>-5204.4982456</v>
       </c>
       <c r="O80">
-        <v>-747.0135521632001</v>
+        <v>-759.8567438575999</v>
       </c>
       <c r="P80">
-        <v>-4369.517627036801</v>
+        <v>-4444.6415017424</v>
       </c>
       <c r="Q80">
-        <v>-1575.617627036801</v>
+        <v>-1650.7415017424</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1476180214740343</v>
+        <v>0.1524664986870835</v>
       </c>
       <c r="T80">
-        <v>2.351455461294094</v>
+        <v>2.463429530879528</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.0371286096656154</v>
+        <v>0.03665862726478483</v>
       </c>
       <c r="W80">
-        <v>0.1933445751791444</v>
+        <v>0.1934389476452312</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2543055456548999</v>
+        <v>0.2510864881149646</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1848347333640202</v>
+        <v>0.1863847333640202</v>
       </c>
       <c r="C81">
-        <v>-21064.80933001745</v>
+        <v>-21599.25803675796</v>
       </c>
       <c r="D81">
-        <v>9693.947669982554</v>
+        <v>9597.581963242048</v>
       </c>
       <c r="E81">
-        <v>19640.057</v>
+        <v>20078.14000000001</v>
       </c>
       <c r="F81">
-        <v>34608.557</v>
+        <v>35046.64000000001</v>
       </c>
       <c r="G81">
         <v>3849.8</v>
@@ -7935,37 +7935,37 @@
         <v>1744.9</v>
       </c>
       <c r="M81">
-        <v>6949.3982456</v>
+        <v>7037.365312000002</v>
       </c>
       <c r="N81">
-        <v>-5204.4982456</v>
+        <v>-5292.465312000002</v>
       </c>
       <c r="O81">
-        <v>-759.8567438575999</v>
+        <v>-772.6999355520003</v>
       </c>
       <c r="P81">
-        <v>-4444.6415017424</v>
+        <v>-4519.765376448002</v>
       </c>
       <c r="Q81">
-        <v>-1650.7415017424</v>
+        <v>-1725.865376448002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1524664986870835</v>
+        <v>0.1577998236214377</v>
       </c>
       <c r="T81">
-        <v>2.463429530879528</v>
+        <v>2.586601007423504</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.03665862726478483</v>
+        <v>0.036200394423975</v>
       </c>
       <c r="W81">
-        <v>0.1934389476452312</v>
+        <v>0.1935309607996658</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2510864881149646</v>
+        <v>0.2479479070135274</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1863847333640202</v>
+        <v>0.1879347333640202</v>
       </c>
       <c r="C82">
-        <v>-21599.25803675796</v>
+        <v>-22131.80969504286</v>
       </c>
       <c r="D82">
-        <v>9597.581963242048</v>
+        <v>9503.113304957145</v>
       </c>
       <c r="E82">
-        <v>20078.14000000001</v>
+        <v>20516.22300000001</v>
       </c>
       <c r="F82">
-        <v>35046.64000000001</v>
+        <v>35484.72300000001</v>
       </c>
       <c r="G82">
         <v>3849.8</v>
@@ -8017,37 +8017,37 @@
         <v>1744.9</v>
       </c>
       <c r="M82">
-        <v>7037.365312000002</v>
+        <v>7125.332378400001</v>
       </c>
       <c r="N82">
-        <v>-5292.465312000002</v>
+        <v>-5380.432378400001</v>
       </c>
       <c r="O82">
-        <v>-772.6999355520003</v>
+        <v>-785.5431272464001</v>
       </c>
       <c r="P82">
-        <v>-4519.765376448002</v>
+        <v>-4594.889251153601</v>
       </c>
       <c r="Q82">
-        <v>-1725.865376448002</v>
+        <v>-1800.9892511536</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1577998236214377</v>
+        <v>0.1636945511804608</v>
       </c>
       <c r="T82">
-        <v>2.586601007423504</v>
+        <v>2.722737902551057</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.036200394423975</v>
+        <v>0.0357534759742963</v>
       </c>
       <c r="W82">
-        <v>0.1935309607996658</v>
+        <v>0.1936207020243613</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2479479070135274</v>
+        <v>0.2448868217417556</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1879347333640202</v>
+        <v>0.1894847333640202</v>
       </c>
       <c r="C83">
-        <v>-22131.80969504286</v>
+        <v>-22662.5197766075</v>
       </c>
       <c r="D83">
-        <v>9503.113304957145</v>
+        <v>9410.486223392509</v>
       </c>
       <c r="E83">
-        <v>20516.22300000001</v>
+        <v>20954.306</v>
       </c>
       <c r="F83">
-        <v>35484.72300000001</v>
+        <v>35922.806</v>
       </c>
       <c r="G83">
         <v>3849.8</v>
@@ -8099,37 +8099,37 @@
         <v>1744.9</v>
       </c>
       <c r="M83">
-        <v>7125.332378400001</v>
+        <v>7213.299444800001</v>
       </c>
       <c r="N83">
-        <v>-5380.432378400001</v>
+        <v>-5468.399444800001</v>
       </c>
       <c r="O83">
-        <v>-785.5431272464001</v>
+        <v>-798.3863189408002</v>
       </c>
       <c r="P83">
-        <v>-4594.889251153601</v>
+        <v>-4670.013125859201</v>
       </c>
       <c r="Q83">
-        <v>-1800.9892511536</v>
+        <v>-1876.113125859201</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1636945511804608</v>
+        <v>0.1702442484682641</v>
       </c>
       <c r="T83">
-        <v>2.722737902551057</v>
+        <v>2.874001119359449</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0357534759742963</v>
+        <v>0.03531745797460977</v>
       </c>
       <c r="W83">
-        <v>0.1936207020243613</v>
+        <v>0.1937082544386984</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2448868217417556</v>
+        <v>0.2419003970863682</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1894847333640202</v>
+        <v>0.1910347333640202</v>
       </c>
       <c r="C84">
-        <v>-22662.5197766075</v>
+        <v>-23191.44161132642</v>
       </c>
       <c r="D84">
-        <v>9410.486223392509</v>
+        <v>9319.64738867358</v>
       </c>
       <c r="E84">
-        <v>20954.306</v>
+        <v>21392.389</v>
       </c>
       <c r="F84">
-        <v>35922.806</v>
+        <v>36360.889</v>
       </c>
       <c r="G84">
         <v>3849.8</v>
@@ -8181,37 +8181,37 @@
         <v>1744.9</v>
       </c>
       <c r="M84">
-        <v>7213.299444800001</v>
+        <v>7301.2665112</v>
       </c>
       <c r="N84">
-        <v>-5468.399444800001</v>
+        <v>-5556.3665112</v>
       </c>
       <c r="O84">
-        <v>-798.3863189408002</v>
+        <v>-811.2295106352</v>
       </c>
       <c r="P84">
-        <v>-4670.013125859201</v>
+        <v>-4745.1370005648</v>
       </c>
       <c r="Q84">
-        <v>-1876.113125859201</v>
+        <v>-1951.237000564799</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1702442484682641</v>
+        <v>0.1775644983781621</v>
       </c>
       <c r="T84">
-        <v>2.874001119359449</v>
+        <v>3.043060008733535</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03531745797460977</v>
+        <v>0.034891946432747</v>
       </c>
       <c r="W84">
-        <v>0.1937082544386984</v>
+        <v>0.1937936971563044</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2419003970863682</v>
+        <v>0.2389859344708699</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1910347333640202</v>
+        <v>0.1925847333640202</v>
       </c>
       <c r="C85">
-        <v>-23191.44161132642</v>
+        <v>-23718.62648960136</v>
       </c>
       <c r="D85">
-        <v>9319.64738867358</v>
+        <v>9230.545510398646</v>
       </c>
       <c r="E85">
-        <v>21392.389</v>
+        <v>21830.47200000001</v>
       </c>
       <c r="F85">
-        <v>36360.889</v>
+        <v>36798.97200000001</v>
       </c>
       <c r="G85">
         <v>3849.8</v>
@@ -8263,37 +8263,37 @@
         <v>1744.9</v>
       </c>
       <c r="M85">
-        <v>7301.2665112</v>
+        <v>7389.233577600002</v>
       </c>
       <c r="N85">
-        <v>-5556.3665112</v>
+        <v>-5644.333577600002</v>
       </c>
       <c r="O85">
-        <v>-811.2295106352</v>
+        <v>-824.0727023296002</v>
       </c>
       <c r="P85">
-        <v>-4745.1370005648</v>
+        <v>-4820.260875270402</v>
       </c>
       <c r="Q85">
-        <v>-1951.237000564799</v>
+        <v>-2026.360875270402</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1775644983781621</v>
+        <v>0.1857997795267972</v>
       </c>
       <c r="T85">
-        <v>3.043060008733535</v>
+        <v>3.233251259279381</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.034891946432747</v>
+        <v>0.03447656611807143</v>
       </c>
       <c r="W85">
-        <v>0.1937936971563044</v>
+        <v>0.1938771055234912</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2389859344708699</v>
+        <v>0.2361408638224071</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1925847333640202</v>
+        <v>0.1941347333640202</v>
       </c>
       <c r="C86">
-        <v>-23718.62648960135</v>
+        <v>-24244.12375893128</v>
       </c>
       <c r="D86">
-        <v>9230.54551039865</v>
+        <v>9143.131241068719</v>
       </c>
       <c r="E86">
-        <v>21830.472</v>
+        <v>22268.555</v>
       </c>
       <c r="F86">
-        <v>36798.972</v>
+        <v>37237.055</v>
       </c>
       <c r="G86">
         <v>3849.8</v>
@@ -8345,37 +8345,37 @@
         <v>1744.9</v>
       </c>
       <c r="M86">
-        <v>7389.233577600001</v>
+        <v>7477.200644</v>
       </c>
       <c r="N86">
-        <v>-5644.3335776</v>
+        <v>-5732.300644000001</v>
       </c>
       <c r="O86">
-        <v>-824.0727023296</v>
+        <v>-836.9158940240001</v>
       </c>
       <c r="P86">
-        <v>-4820.2608752704</v>
+        <v>-4895.384749976</v>
       </c>
       <c r="Q86">
-        <v>-2026.3608752704</v>
+        <v>-2101.484749976</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1857997795267971</v>
+        <v>0.1951330981619169</v>
       </c>
       <c r="T86">
-        <v>3.233251259279379</v>
+        <v>3.448801343231338</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03447656611807143</v>
+        <v>0.03407095945785884</v>
       </c>
       <c r="W86">
-        <v>0.1938771055234912</v>
+        <v>0.193958551340862</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2361408638224072</v>
+        <v>0.2333627360127317</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1941347333640202</v>
+        <v>0.1956847333640202</v>
       </c>
       <c r="C87">
-        <v>-24244.12375893128</v>
+        <v>-24767.98091504691</v>
       </c>
       <c r="D87">
-        <v>9143.131241068719</v>
+        <v>9057.357084953086</v>
       </c>
       <c r="E87">
-        <v>22268.555</v>
+        <v>22706.638</v>
       </c>
       <c r="F87">
-        <v>37237.055</v>
+        <v>37675.138</v>
       </c>
       <c r="G87">
         <v>3849.8</v>
@@ -8427,37 +8427,37 @@
         <v>1744.9</v>
       </c>
       <c r="M87">
-        <v>7477.200644</v>
+        <v>7565.1677104</v>
       </c>
       <c r="N87">
-        <v>-5732.300644000001</v>
+        <v>-5820.267710399999</v>
       </c>
       <c r="O87">
-        <v>-836.9158940240001</v>
+        <v>-849.7590857183999</v>
       </c>
       <c r="P87">
-        <v>-4895.384749976</v>
+        <v>-4970.5086246816</v>
       </c>
       <c r="Q87">
-        <v>-2101.484749976</v>
+        <v>-2176.6086246816</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1951330981619169</v>
+        <v>0.2057997480306253</v>
       </c>
       <c r="T87">
-        <v>3.448801343231338</v>
+        <v>3.69514429631929</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03407095945785884</v>
+        <v>0.03367478551067443</v>
       </c>
       <c r="W87">
-        <v>0.193958551340862</v>
+        <v>0.1940381030694566</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2333627360127317</v>
+        <v>0.2306492158265373</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1956847333640202</v>
+        <v>0.1972347333640202</v>
       </c>
       <c r="C88">
-        <v>-24767.98091504691</v>
+        <v>-25290.24368796309</v>
       </c>
       <c r="D88">
-        <v>9057.357084953086</v>
+        <v>8973.177312036914</v>
       </c>
       <c r="E88">
-        <v>22706.638</v>
+        <v>23144.72100000001</v>
       </c>
       <c r="F88">
-        <v>37675.138</v>
+        <v>38113.22100000001</v>
       </c>
       <c r="G88">
         <v>3849.8</v>
@@ -8509,37 +8509,37 @@
         <v>1744.9</v>
       </c>
       <c r="M88">
-        <v>7565.1677104</v>
+        <v>7653.134776800001</v>
       </c>
       <c r="N88">
-        <v>-5820.267710399999</v>
+        <v>-5908.234776800002</v>
       </c>
       <c r="O88">
-        <v>-849.7590857183999</v>
+        <v>-862.6022774128002</v>
       </c>
       <c r="P88">
-        <v>-4970.5086246816</v>
+        <v>-5045.632499387201</v>
       </c>
       <c r="Q88">
-        <v>-2176.6086246816</v>
+        <v>-2251.732499387201</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2057997480306253</v>
+        <v>0.218107420956058</v>
       </c>
       <c r="T88">
-        <v>3.69514429631929</v>
+        <v>3.979386165266928</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03367478551067443</v>
+        <v>0.03328771901055173</v>
       </c>
       <c r="W88">
-        <v>0.1940381030694566</v>
+        <v>0.1941158260226812</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2306492158265373</v>
+        <v>0.2279980754147378</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1972347333640202</v>
+        <v>0.1987847333640202</v>
       </c>
       <c r="C89">
-        <v>-25290.24368796309</v>
+        <v>-25810.95612327665</v>
       </c>
       <c r="D89">
-        <v>8973.177312036914</v>
+        <v>8890.547876723354</v>
       </c>
       <c r="E89">
-        <v>23144.72100000001</v>
+        <v>23582.804</v>
       </c>
       <c r="F89">
-        <v>38113.22100000001</v>
+        <v>38551.304</v>
       </c>
       <c r="G89">
         <v>3849.8</v>
@@ -8591,37 +8591,37 @@
         <v>1744.9</v>
       </c>
       <c r="M89">
-        <v>7653.134776800001</v>
+        <v>7741.101843200001</v>
       </c>
       <c r="N89">
-        <v>-5908.234776800002</v>
+        <v>-5996.2018432</v>
       </c>
       <c r="O89">
-        <v>-862.6022774128002</v>
+        <v>-875.4454691072</v>
       </c>
       <c r="P89">
-        <v>-5045.632499387201</v>
+        <v>-5120.756374092801</v>
       </c>
       <c r="Q89">
-        <v>-2251.732499387201</v>
+        <v>-2326.856374092801</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.218107420956058</v>
+        <v>0.2324663727023962</v>
       </c>
       <c r="T89">
-        <v>3.979386165266928</v>
+        <v>4.311001679039173</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03328771901055173</v>
+        <v>0.03290944947634092</v>
       </c>
       <c r="W89">
-        <v>0.1941158260226812</v>
+        <v>0.1941917825451508</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2279980754147378</v>
+        <v>0.225407188194116</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1987847333640202</v>
+        <v>0.2003347333640202</v>
       </c>
       <c r="C90">
-        <v>-25810.95612327665</v>
+        <v>-26330.16065901356</v>
       </c>
       <c r="D90">
-        <v>8890.547876723354</v>
+        <v>8809.426340986438</v>
       </c>
       <c r="E90">
-        <v>23582.804</v>
+        <v>24020.887</v>
       </c>
       <c r="F90">
-        <v>38551.304</v>
+        <v>38989.387</v>
       </c>
       <c r="G90">
         <v>3849.8</v>
@@ -8673,37 +8673,37 @@
         <v>1744.9</v>
       </c>
       <c r="M90">
-        <v>7741.101843200001</v>
+        <v>7829.068909600001</v>
       </c>
       <c r="N90">
-        <v>-5996.2018432</v>
+        <v>-6084.168909600001</v>
       </c>
       <c r="O90">
-        <v>-875.4454691072</v>
+        <v>-888.2886608016</v>
       </c>
       <c r="P90">
-        <v>-5120.756374092801</v>
+        <v>-5195.880248798401</v>
       </c>
       <c r="Q90">
-        <v>-2326.856374092801</v>
+        <v>-2401.980248798401</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2324663727023962</v>
+        <v>0.2494360429480685</v>
       </c>
       <c r="T90">
-        <v>4.311001679039173</v>
+        <v>4.702910922588188</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03290944947634092</v>
+        <v>0.03253968038110114</v>
       </c>
       <c r="W90">
-        <v>0.1941917825451508</v>
+        <v>0.1942660321794749</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.225407188194116</v>
+        <v>0.2228745231582269</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2003347333640202</v>
+        <v>0.2018847333640202</v>
       </c>
       <c r="C91">
-        <v>-26330.16065901356</v>
+        <v>-26847.89819830695</v>
       </c>
       <c r="D91">
-        <v>8809.426340986438</v>
+        <v>8729.771801693054</v>
       </c>
       <c r="E91">
-        <v>24020.887</v>
+        <v>24458.97</v>
       </c>
       <c r="F91">
-        <v>38989.387</v>
+        <v>39427.47</v>
       </c>
       <c r="G91">
         <v>3849.8</v>
@@ -8755,37 +8755,37 @@
         <v>1744.9</v>
       </c>
       <c r="M91">
-        <v>7829.068909600001</v>
+        <v>7917.035976</v>
       </c>
       <c r="N91">
-        <v>-6084.168909600001</v>
+        <v>-6172.135976</v>
       </c>
       <c r="O91">
-        <v>-888.2886608016</v>
+        <v>-901.1318524959999</v>
       </c>
       <c r="P91">
-        <v>-5195.880248798401</v>
+        <v>-5271.004123504</v>
       </c>
       <c r="Q91">
-        <v>-2401.980248798401</v>
+        <v>-2477.104123504</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2494360429480685</v>
+        <v>0.2697996472428754</v>
       </c>
       <c r="T91">
-        <v>4.702910922588188</v>
+        <v>5.173202014847008</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.03253968038110114</v>
+        <v>0.03217812837686668</v>
       </c>
       <c r="W91">
-        <v>0.1942660321794749</v>
+        <v>0.1943386318219252</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2228745231582269</v>
+        <v>0.22039813956758</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2018847333640202</v>
+        <v>0.2034347333640202</v>
       </c>
       <c r="C92">
-        <v>-26847.89819830695</v>
+        <v>-27364.20817816748</v>
       </c>
       <c r="D92">
-        <v>8729.771801693054</v>
+        <v>8651.544821832527</v>
       </c>
       <c r="E92">
-        <v>24458.97</v>
+        <v>24897.05300000001</v>
       </c>
       <c r="F92">
-        <v>39427.47</v>
+        <v>39865.55300000001</v>
       </c>
       <c r="G92">
         <v>3849.8</v>
@@ -8837,37 +8837,37 @@
         <v>1744.9</v>
       </c>
       <c r="M92">
-        <v>7917.035976</v>
+        <v>8005.003042400002</v>
       </c>
       <c r="N92">
-        <v>-6172.135976</v>
+        <v>-6260.103042400002</v>
       </c>
       <c r="O92">
-        <v>-901.1318524959999</v>
+        <v>-913.9750441904002</v>
       </c>
       <c r="P92">
-        <v>-5271.004123504</v>
+        <v>-5346.127998209602</v>
       </c>
       <c r="Q92">
-        <v>-2477.104123504</v>
+        <v>-2552.227998209602</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2697996472428754</v>
+        <v>0.2946884969365283</v>
       </c>
       <c r="T92">
-        <v>5.173202014847008</v>
+        <v>5.748002238718898</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.03217812837686668</v>
+        <v>0.03182452257052748</v>
       </c>
       <c r="W92">
-        <v>0.1943386318219252</v>
+        <v>0.1944096358678381</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.22039813956758</v>
+        <v>0.2179761819899142</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2034347333640202</v>
+        <v>0.2049847333640202</v>
       </c>
       <c r="C93">
-        <v>-27364.20817816748</v>
+        <v>-27879.12863458917</v>
       </c>
       <c r="D93">
-        <v>8651.544821832527</v>
+        <v>8574.707365410834</v>
       </c>
       <c r="E93">
-        <v>24897.05300000001</v>
+        <v>25335.13600000001</v>
       </c>
       <c r="F93">
-        <v>39865.55300000001</v>
+        <v>40303.63600000001</v>
       </c>
       <c r="G93">
         <v>3849.8</v>
@@ -8919,37 +8919,37 @@
         <v>1744.9</v>
       </c>
       <c r="M93">
-        <v>8005.003042400002</v>
+        <v>8092.970108800001</v>
       </c>
       <c r="N93">
-        <v>-6260.103042400002</v>
+        <v>-6348.070108800001</v>
       </c>
       <c r="O93">
-        <v>-913.9750441904002</v>
+        <v>-926.8182358848001</v>
       </c>
       <c r="P93">
-        <v>-5346.127998209602</v>
+        <v>-5421.251872915201</v>
       </c>
       <c r="Q93">
-        <v>-2552.227998209602</v>
+        <v>-2627.351872915201</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2946884969365283</v>
+        <v>0.3257995590535944</v>
       </c>
       <c r="T93">
-        <v>5.748002238718898</v>
+        <v>6.466502518558761</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.03182452257052748</v>
+        <v>0.03147860384693479</v>
       </c>
       <c r="W93">
-        <v>0.1944096358678381</v>
+        <v>0.1944790963475355</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2179761819899142</v>
+        <v>0.215606875663937</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2049847333640202</v>
+        <v>0.2065347333640202</v>
       </c>
       <c r="C94">
-        <v>-27879.12863458917</v>
+        <v>-28392.69626421635</v>
       </c>
       <c r="D94">
-        <v>8574.707365410834</v>
+        <v>8499.222735783651</v>
       </c>
       <c r="E94">
-        <v>25335.13600000001</v>
+        <v>25773.219</v>
       </c>
       <c r="F94">
-        <v>40303.63600000001</v>
+        <v>40741.719</v>
       </c>
       <c r="G94">
         <v>3849.8</v>
@@ -9001,37 +9001,37 @@
         <v>1744.9</v>
       </c>
       <c r="M94">
-        <v>8092.970108800001</v>
+        <v>8180.937175200002</v>
       </c>
       <c r="N94">
-        <v>-6348.070108800001</v>
+        <v>-6436.037175200001</v>
       </c>
       <c r="O94">
-        <v>-926.8182358848001</v>
+        <v>-939.6614275792001</v>
       </c>
       <c r="P94">
-        <v>-5421.251872915201</v>
+        <v>-5496.375747620801</v>
       </c>
       <c r="Q94">
-        <v>-2627.351872915201</v>
+        <v>-2702.475747620801</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3257995590535944</v>
+        <v>0.3657994960612507</v>
       </c>
       <c r="T94">
-        <v>6.466502518558761</v>
+        <v>7.390288592638585</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.03147860384693479</v>
+        <v>0.03114012423567743</v>
       </c>
       <c r="W94">
-        <v>0.1944790963475355</v>
+        <v>0.194547063053476</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.215606875663937</v>
+        <v>0.2132885221621742</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2065347333640202</v>
+        <v>0.2080847333640202</v>
       </c>
       <c r="C95">
-        <v>-28392.69626421635</v>
+        <v>-28904.94648278186</v>
       </c>
       <c r="D95">
-        <v>8499.222735783651</v>
+        <v>8425.055517218147</v>
       </c>
       <c r="E95">
-        <v>25773.219</v>
+        <v>26211.302</v>
       </c>
       <c r="F95">
-        <v>40741.719</v>
+        <v>41179.802</v>
       </c>
       <c r="G95">
         <v>3849.8</v>
@@ -9083,37 +9083,37 @@
         <v>1744.9</v>
       </c>
       <c r="M95">
-        <v>8180.937175200002</v>
+        <v>8268.904241600001</v>
       </c>
       <c r="N95">
-        <v>-6436.037175200001</v>
+        <v>-6524.004241600001</v>
       </c>
       <c r="O95">
-        <v>-939.6614275792001</v>
+        <v>-952.5046192736002</v>
       </c>
       <c r="P95">
-        <v>-5496.375747620801</v>
+        <v>-5571.499622326402</v>
       </c>
       <c r="Q95">
-        <v>-2702.475747620801</v>
+        <v>-2777.599622326401</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3657994960612507</v>
+        <v>0.4191327454047926</v>
       </c>
       <c r="T95">
-        <v>7.390288592638585</v>
+        <v>8.622003358078352</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.03114012423567743</v>
+        <v>0.0308088463182766</v>
       </c>
       <c r="W95">
-        <v>0.194547063053476</v>
+        <v>0.19461358365929</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2132885221621742</v>
+        <v>0.2110194953306617</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2080847333640202</v>
+        <v>0.2096347333640202</v>
       </c>
       <c r="C96">
-        <v>-28904.94648278186</v>
+        <v>-29415.91348051196</v>
       </c>
       <c r="D96">
-        <v>8425.055517218147</v>
+        <v>8352.171519488045</v>
       </c>
       <c r="E96">
-        <v>26211.302</v>
+        <v>26649.38500000001</v>
       </c>
       <c r="F96">
-        <v>41179.802</v>
+        <v>41617.88500000001</v>
       </c>
       <c r="G96">
         <v>3849.8</v>
@@ -9165,37 +9165,37 @@
         <v>1744.9</v>
       </c>
       <c r="M96">
-        <v>8268.904241600001</v>
+        <v>8356.871308000002</v>
       </c>
       <c r="N96">
-        <v>-6524.004241600001</v>
+        <v>-6611.971308000002</v>
       </c>
       <c r="O96">
-        <v>-952.5046192736002</v>
+        <v>-965.3478109680002</v>
       </c>
       <c r="P96">
-        <v>-5571.499622326402</v>
+        <v>-5646.623497032002</v>
       </c>
       <c r="Q96">
-        <v>-2777.599622326401</v>
+        <v>-2852.723497032002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4191327454047926</v>
+        <v>0.4937992944857514</v>
       </c>
       <c r="T96">
-        <v>8.622003358078352</v>
+        <v>10.34640402969403</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0308088463182766</v>
+        <v>0.03048454267282106</v>
       </c>
       <c r="W96">
-        <v>0.19461358365929</v>
+        <v>0.1946787038312975</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2110194953306617</v>
+        <v>0.2087982374850758</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2096347333640202</v>
+        <v>0.2111847333640202</v>
       </c>
       <c r="C97">
-        <v>-29415.91348051196</v>
+        <v>-29925.63027468018</v>
       </c>
       <c r="D97">
-        <v>8352.171519488045</v>
+        <v>8280.537725319826</v>
       </c>
       <c r="E97">
-        <v>26649.38500000001</v>
+        <v>27087.46800000001</v>
       </c>
       <c r="F97">
-        <v>41617.88500000001</v>
+        <v>42055.96800000001</v>
       </c>
       <c r="G97">
         <v>3849.8</v>
@@ -9247,37 +9247,37 @@
         <v>1744.9</v>
       </c>
       <c r="M97">
-        <v>8356.871308000002</v>
+        <v>8444.838374400002</v>
       </c>
       <c r="N97">
-        <v>-6611.971308000002</v>
+        <v>-6699.938374400002</v>
       </c>
       <c r="O97">
-        <v>-965.3478109680002</v>
+        <v>-978.1910026624003</v>
       </c>
       <c r="P97">
-        <v>-5646.623497032002</v>
+        <v>-5721.747371737602</v>
       </c>
       <c r="Q97">
-        <v>-2852.723497032002</v>
+        <v>-2927.847371737602</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4937992944857514</v>
+        <v>0.6057991181071894</v>
       </c>
       <c r="T97">
-        <v>10.34640402969403</v>
+        <v>12.93300503711754</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.03048454267282106</v>
+        <v>0.03016699535331251</v>
       </c>
       <c r="W97">
-        <v>0.1946787038312975</v>
+        <v>0.1947424673330549</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2087982374850758</v>
+        <v>0.2066232558446062</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2111847333640202</v>
+        <v>0.2127347333640202</v>
       </c>
       <c r="C98">
-        <v>-29925.63027468017</v>
+        <v>-30434.12875947967</v>
       </c>
       <c r="D98">
-        <v>8280.537725319826</v>
+        <v>8210.122240520324</v>
       </c>
       <c r="E98">
-        <v>27087.468</v>
+        <v>27525.551</v>
       </c>
       <c r="F98">
-        <v>42055.968</v>
+        <v>42494.051</v>
       </c>
       <c r="G98">
         <v>3849.8</v>
@@ -9329,37 +9329,37 @@
         <v>1744.9</v>
       </c>
       <c r="M98">
-        <v>8444.8383744</v>
+        <v>8532.805440800001</v>
       </c>
       <c r="N98">
-        <v>-6699.938374400001</v>
+        <v>-6787.905440800001</v>
       </c>
       <c r="O98">
-        <v>-978.1910026624</v>
+        <v>-991.0341943568001</v>
       </c>
       <c r="P98">
-        <v>-5721.747371737601</v>
+        <v>-5796.871246443201</v>
       </c>
       <c r="Q98">
-        <v>-2927.8473717376</v>
+        <v>-3002.971246443201</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.605799118107188</v>
+        <v>0.7924654908095842</v>
       </c>
       <c r="T98">
-        <v>12.93300503711751</v>
+        <v>17.24400671615668</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.03016699535331251</v>
+        <v>0.02985599540121651</v>
       </c>
       <c r="W98">
-        <v>0.1947424673330549</v>
+        <v>0.1948049161234357</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2066232558446062</v>
+        <v>0.2044931191864143</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2127347333640202</v>
+        <v>0.2142847333640202</v>
       </c>
       <c r="C99">
-        <v>-30434.12875947967</v>
+        <v>-30941.43975337251</v>
       </c>
       <c r="D99">
-        <v>8210.122240520324</v>
+        <v>8140.894246627498</v>
       </c>
       <c r="E99">
-        <v>27525.551</v>
+        <v>27963.63400000001</v>
       </c>
       <c r="F99">
-        <v>42494.051</v>
+        <v>42932.13400000001</v>
       </c>
       <c r="G99">
         <v>3849.8</v>
@@ -9411,37 +9411,37 @@
         <v>1744.9</v>
       </c>
       <c r="M99">
-        <v>8532.805440800001</v>
+        <v>8620.772507200001</v>
       </c>
       <c r="N99">
-        <v>-6787.905440800001</v>
+        <v>-6875.872507200002</v>
       </c>
       <c r="O99">
-        <v>-991.0341943568001</v>
+        <v>-1003.8773860512</v>
       </c>
       <c r="P99">
-        <v>-5796.871246443201</v>
+        <v>-5871.995121148801</v>
       </c>
       <c r="Q99">
-        <v>-3002.971246443201</v>
+        <v>-3078.095121148801</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7924654908095842</v>
+        <v>1.165798236214376</v>
       </c>
       <c r="T99">
-        <v>17.24400671615668</v>
+        <v>25.86601007423501</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.02985599540121651</v>
+        <v>0.02955134238691837</v>
       </c>
       <c r="W99">
-        <v>0.1948049161234357</v>
+        <v>0.1948660904487068</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2044931191864143</v>
+        <v>0.2024064547049204</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2142847333640202</v>
+        <v>0.2158347333640202</v>
       </c>
       <c r="C100">
-        <v>-30941.43975337251</v>
+        <v>-31447.59304406334</v>
       </c>
       <c r="D100">
-        <v>8140.894246627498</v>
+        <v>8072.823955936668</v>
       </c>
       <c r="E100">
-        <v>27963.63400000001</v>
+        <v>28401.717</v>
       </c>
       <c r="F100">
-        <v>42932.13400000001</v>
+        <v>43370.217</v>
       </c>
       <c r="G100">
         <v>3849.8</v>
@@ -9493,37 +9493,37 @@
         <v>1744.9</v>
       </c>
       <c r="M100">
-        <v>8620.772507200001</v>
+        <v>8708.739573600002</v>
       </c>
       <c r="N100">
-        <v>-6875.872507200002</v>
+        <v>-6963.839573600002</v>
       </c>
       <c r="O100">
-        <v>-1003.8773860512</v>
+        <v>-1016.7205777456</v>
       </c>
       <c r="P100">
-        <v>-5871.995121148801</v>
+        <v>-5947.118995854402</v>
       </c>
       <c r="Q100">
-        <v>-3078.095121148801</v>
+        <v>-3153.218995854402</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.165798236214376</v>
+        <v>2.285796472428752</v>
       </c>
       <c r="T100">
-        <v>25.86601007423501</v>
+        <v>51.73202014847003</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.02955134238691837</v>
+        <v>0.0292528439789697</v>
       </c>
       <c r="W100">
-        <v>0.1948660904487068</v>
+        <v>0.1949260289290229</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2024064547049204</v>
+        <v>0.2003619450614363</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2158347333640202</v>
-      </c>
-      <c r="C101">
-        <v>-31447.59304406334</v>
-      </c>
-      <c r="D101">
-        <v>8072.823955936668</v>
-      </c>
-      <c r="E101">
-        <v>28401.717</v>
-      </c>
-      <c r="F101">
-        <v>43370.217</v>
-      </c>
-      <c r="G101">
-        <v>3849.8</v>
-      </c>
-      <c r="H101">
-        <v>28839.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4538.8</v>
-      </c>
-      <c r="K101">
-        <v>2793.9</v>
-      </c>
-      <c r="L101">
-        <v>1744.9</v>
-      </c>
-      <c r="M101">
-        <v>8708.739573600002</v>
-      </c>
-      <c r="N101">
-        <v>-6963.839573600002</v>
-      </c>
-      <c r="O101">
-        <v>-1016.7205777456</v>
-      </c>
-      <c r="P101">
-        <v>-5947.118995854402</v>
-      </c>
-      <c r="Q101">
-        <v>-3153.218995854402</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.285796472428752</v>
-      </c>
-      <c r="T101">
-        <v>51.73202014847003</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0292528439789697</v>
-      </c>
-      <c r="W101">
-        <v>0.1949260289290229</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2003619450614363</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
